--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -115,11 +115,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,60 +641,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7560.75</v>
+        <v>7514.5</v>
       </c>
       <c r="C2" t="n">
-        <v>7570.5</v>
+        <v>7544.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7509.75</v>
+        <v>7405</v>
       </c>
       <c r="E2" t="n">
-        <v>7518.5</v>
+        <v>7424.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-42.75</v>
+        <v>-94</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0125</v>
       </c>
       <c r="H2" t="n">
-        <v>60.75</v>
+        <v>139.5</v>
       </c>
       <c r="I2" t="n">
-        <v>7375.5</v>
+        <v>7449</v>
       </c>
       <c r="J2" t="n">
-        <v>7471.25</v>
+        <v>7446.94</v>
       </c>
       <c r="K2" t="n">
-        <v>7509</v>
+        <v>7488.12</v>
       </c>
       <c r="L2" t="n">
-        <v>7546.75</v>
+        <v>7529.31</v>
       </c>
       <c r="M2" t="n">
-        <v>7613.5</v>
+        <v>7548.88</v>
       </c>
       <c r="N2" t="n">
-        <v>7680.25</v>
+        <v>7568.44</v>
       </c>
       <c r="O2" t="n">
-        <v>7689</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>7631.25</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -713,146 +717,142 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>7440.5</v>
+      </c>
+      <c r="C3" t="n">
         <v>7514.5</v>
       </c>
-      <c r="C3" t="n">
-        <v>7544.5</v>
-      </c>
       <c r="D3" t="n">
-        <v>7405</v>
+        <v>7436.25</v>
       </c>
       <c r="E3" t="n">
-        <v>7424.5</v>
+        <v>7508.43</v>
       </c>
       <c r="F3" t="n">
-        <v>-94</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0125</v>
+        <v>0.0113</v>
       </c>
       <c r="H3" t="n">
-        <v>139.5</v>
+        <v>78.25</v>
       </c>
       <c r="I3" t="n">
-        <v>7449</v>
+        <v>7265.5</v>
       </c>
       <c r="J3" t="n">
-        <v>7446.94</v>
+        <v>7259.88</v>
       </c>
       <c r="K3" t="n">
-        <v>7488.12</v>
+        <v>7354.75</v>
       </c>
       <c r="L3" t="n">
-        <v>7529.31</v>
+        <v>7449.62</v>
       </c>
       <c r="M3" t="n">
-        <v>7548.88</v>
+        <v>7494.25</v>
       </c>
       <c r="N3" t="n">
-        <v>7568.44</v>
+        <v>7538.88</v>
       </c>
       <c r="O3" t="n">
-        <v>7631.25</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
+        <v>7684</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7440.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C4" t="n">
-        <v>7514.5</v>
+        <v>7599.25</v>
       </c>
       <c r="D4" t="n">
-        <v>7436.25</v>
+        <v>7513</v>
       </c>
       <c r="E4" t="n">
-        <v>7508.43</v>
+        <v>7541.25</v>
       </c>
       <c r="F4" t="n">
-        <v>83.93000000000001</v>
+        <v>32.82</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0044</v>
       </c>
       <c r="H4" t="n">
-        <v>78.25</v>
+        <v>86.25</v>
       </c>
       <c r="I4" t="n">
-        <v>7265.5</v>
+        <v>7358</v>
       </c>
       <c r="J4" t="n">
-        <v>7259.88</v>
+        <v>7446.71</v>
       </c>
       <c r="K4" t="n">
-        <v>7354.75</v>
+        <v>7469.31</v>
       </c>
       <c r="L4" t="n">
-        <v>7449.62</v>
+        <v>7491.9</v>
       </c>
       <c r="M4" t="n">
-        <v>7494.25</v>
+        <v>7547.56</v>
       </c>
       <c r="N4" t="n">
-        <v>7538.88</v>
+        <v>7603.21</v>
       </c>
       <c r="O4" t="n">
-        <v>7684</v>
+        <v>7592.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -863,7 +863,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -876,172 +876,166 @@
       <c r="U4" s="8" t="n">
         <v/>
       </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7543.25</v>
+        <v>7541.25</v>
       </c>
       <c r="C5" t="n">
-        <v>7599.25</v>
+        <v>7549.5</v>
       </c>
       <c r="D5" t="n">
-        <v>7513</v>
+        <v>7415.25</v>
       </c>
       <c r="E5" t="n">
-        <v>7541.25</v>
+        <v>7437.5</v>
       </c>
       <c r="F5" t="n">
-        <v>32.82</v>
+        <v>-103.75</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0138</v>
       </c>
       <c r="H5" t="n">
-        <v>86.25</v>
+        <v>134.25</v>
       </c>
       <c r="I5" t="n">
-        <v>7358</v>
+        <v>7426.75</v>
       </c>
       <c r="J5" t="n">
-        <v>7446.71</v>
+        <v>7447.56</v>
       </c>
       <c r="K5" t="n">
-        <v>7469.31</v>
+        <v>7498.12</v>
       </c>
       <c r="L5" t="n">
-        <v>7491.9</v>
+        <v>7548.69</v>
       </c>
       <c r="M5" t="n">
-        <v>7547.56</v>
+        <v>7584.38</v>
       </c>
       <c r="N5" t="n">
-        <v>7603.21</v>
+        <v>7620.06</v>
       </c>
       <c r="O5" t="n">
-        <v>7592.75</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+        <v>7685.5</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7541.25</v>
+        <v>7449.25</v>
       </c>
       <c r="C6" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D6" t="n">
-        <v>7415.25</v>
+        <v>7404.25</v>
       </c>
       <c r="E6" t="n">
-        <v>7437.5</v>
+        <v>7428.25</v>
       </c>
       <c r="F6" t="n">
-        <v>-103.75</v>
+        <v>-9.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.0012</v>
       </c>
       <c r="H6" t="n">
-        <v>134.25</v>
+        <v>92.25</v>
       </c>
       <c r="I6" t="n">
-        <v>7426.75</v>
+        <v>7281</v>
       </c>
       <c r="J6" t="n">
-        <v>7447.56</v>
+        <v>7280.81</v>
       </c>
       <c r="K6" t="n">
-        <v>7498.12</v>
+        <v>7370.38</v>
       </c>
       <c r="L6" t="n">
-        <v>7548.69</v>
+        <v>7459.94</v>
       </c>
       <c r="M6" t="n">
-        <v>7584.38</v>
+        <v>7504.62</v>
       </c>
       <c r="N6" t="n">
-        <v>7620.06</v>
+        <v>7549.31</v>
       </c>
       <c r="O6" t="n">
-        <v>7685.5</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7683.75</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1053,7 +1047,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1063,50 +1057,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7449.25</v>
+        <v>7476.25</v>
       </c>
       <c r="C7" t="n">
-        <v>7496.5</v>
+        <v>7496</v>
       </c>
       <c r="D7" t="n">
-        <v>7404.25</v>
+        <v>7390.5</v>
       </c>
       <c r="E7" t="n">
-        <v>7428.25</v>
+        <v>7423.25</v>
       </c>
       <c r="F7" t="n">
-        <v>-9.25</v>
+        <v>-5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.0007</v>
       </c>
       <c r="H7" t="n">
-        <v>92.25</v>
+        <v>105.5</v>
       </c>
       <c r="I7" t="n">
-        <v>7281</v>
+        <v>7312</v>
       </c>
       <c r="J7" t="n">
-        <v>7280.81</v>
+        <v>7324.94</v>
       </c>
       <c r="K7" t="n">
-        <v>7370.38</v>
+        <v>7382.12</v>
       </c>
       <c r="L7" t="n">
-        <v>7459.94</v>
+        <v>7439.31</v>
       </c>
       <c r="M7" t="n">
-        <v>7504.62</v>
+        <v>7474.38</v>
       </c>
       <c r="N7" t="n">
-        <v>7549.31</v>
+        <v>7509.44</v>
       </c>
       <c r="O7" t="n">
-        <v>7683.75</v>
+        <v>7588.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1122,8 +1116,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1131,7 +1127,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1141,50 +1137,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7476.25</v>
+        <v>7431</v>
       </c>
       <c r="C8" t="n">
-        <v>7496</v>
+        <v>7459.5</v>
       </c>
       <c r="D8" t="n">
-        <v>7390.5</v>
+        <v>7357.25</v>
       </c>
       <c r="E8" t="n">
-        <v>7423.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F8" t="n">
-        <v>-5</v>
+        <v>-21.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0029</v>
       </c>
       <c r="H8" t="n">
-        <v>105.5</v>
+        <v>102.25</v>
       </c>
       <c r="I8" t="n">
-        <v>7312</v>
+        <v>7285</v>
       </c>
       <c r="J8" t="n">
-        <v>7324.94</v>
+        <v>7307.75</v>
       </c>
       <c r="K8" t="n">
-        <v>7382.12</v>
+        <v>7370.5</v>
       </c>
       <c r="L8" t="n">
-        <v>7439.31</v>
+        <v>7433.25</v>
       </c>
       <c r="M8" t="n">
-        <v>7474.38</v>
+        <v>7476</v>
       </c>
       <c r="N8" t="n">
-        <v>7509.44</v>
+        <v>7518.75</v>
       </c>
       <c r="O8" t="n">
-        <v>7588.75</v>
+        <v>7601.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1192,18 +1188,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1211,7 +1207,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="10" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1221,50 +1217,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7431</v>
+        <v>7398</v>
       </c>
       <c r="C9" t="n">
-        <v>7459.5</v>
+        <v>7505</v>
       </c>
       <c r="D9" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E9" t="n">
-        <v>7401.75</v>
+        <v>7500.25</v>
       </c>
       <c r="F9" t="n">
-        <v>-21.5</v>
+        <v>98.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0133</v>
       </c>
       <c r="H9" t="n">
-        <v>102.25</v>
+        <v>107</v>
       </c>
       <c r="I9" t="n">
-        <v>7285</v>
+        <v>7255</v>
       </c>
       <c r="J9" t="n">
-        <v>7307.75</v>
+        <v>7296.19</v>
       </c>
       <c r="K9" t="n">
-        <v>7370.5</v>
+        <v>7350.62</v>
       </c>
       <c r="L9" t="n">
-        <v>7433.25</v>
+        <v>7405.06</v>
       </c>
       <c r="M9" t="n">
-        <v>7476</v>
+        <v>7452.88</v>
       </c>
       <c r="N9" t="n">
-        <v>7518.75</v>
+        <v>7500.69</v>
       </c>
       <c r="O9" t="n">
-        <v>7601.5</v>
+        <v>7561.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,79 +1268,85 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="10" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7398</v>
+        <v>7495.5</v>
       </c>
       <c r="C10" t="n">
-        <v>7505</v>
+        <v>7567.75</v>
       </c>
       <c r="D10" t="n">
-        <v>7398</v>
+        <v>7481.75</v>
       </c>
       <c r="E10" t="n">
-        <v>7500.25</v>
+        <v>7548.25</v>
       </c>
       <c r="F10" t="n">
-        <v>98.5</v>
+        <v>48</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0064</v>
       </c>
       <c r="H10" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="I10" t="n">
-        <v>7255</v>
+        <v>7291</v>
       </c>
       <c r="J10" t="n">
-        <v>7296.19</v>
+        <v>7417.62</v>
       </c>
       <c r="K10" t="n">
-        <v>7350.62</v>
+        <v>7446.75</v>
       </c>
       <c r="L10" t="n">
-        <v>7405.06</v>
+        <v>7475.88</v>
       </c>
       <c r="M10" t="n">
-        <v>7452.88</v>
+        <v>7553.75</v>
       </c>
       <c r="N10" t="n">
-        <v>7500.69</v>
+        <v>7631.62</v>
       </c>
       <c r="O10" t="n">
-        <v>7561.75</v>
+        <v>7612</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,25 +1357,23 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="11" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="10" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1387,50 +1387,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7495.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C11" t="n">
-        <v>7567.75</v>
+        <v>7579</v>
       </c>
       <c r="D11" t="n">
-        <v>7481.75</v>
+        <v>7505.75</v>
       </c>
       <c r="E11" t="n">
-        <v>7548.25</v>
+        <v>7543.5</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>-4.75</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0064</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>86</v>
+        <v>73.25</v>
       </c>
       <c r="I11" t="n">
-        <v>7291</v>
+        <v>7395.75</v>
       </c>
       <c r="J11" t="n">
-        <v>7417.62</v>
+        <v>7474</v>
       </c>
       <c r="K11" t="n">
-        <v>7446.75</v>
+        <v>7505.25</v>
       </c>
       <c r="L11" t="n">
-        <v>7475.88</v>
+        <v>7536.5</v>
       </c>
       <c r="M11" t="n">
-        <v>7553.75</v>
+        <v>7591.25</v>
       </c>
       <c r="N11" t="n">
-        <v>7631.62</v>
+        <v>7646</v>
       </c>
       <c r="O11" t="n">
-        <v>7612</v>
+        <v>7653.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1441,15 +1441,13 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1457,64 +1455,64 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="10" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7543.25</v>
+        <v>7536</v>
       </c>
       <c r="C12" t="n">
-        <v>7579</v>
+        <v>7593.75</v>
       </c>
       <c r="D12" t="n">
-        <v>7505.75</v>
+        <v>7479.5</v>
       </c>
       <c r="E12" t="n">
-        <v>7543.5</v>
+        <v>7528.25</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.75</v>
+        <v>-15.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="H12" t="n">
-        <v>73.25</v>
+        <v>114.25</v>
       </c>
       <c r="I12" t="n">
-        <v>7395.75</v>
+        <v>7432.5</v>
       </c>
       <c r="J12" t="n">
-        <v>7474</v>
+        <v>7470.81</v>
       </c>
       <c r="K12" t="n">
-        <v>7505.25</v>
+        <v>7506.88</v>
       </c>
       <c r="L12" t="n">
-        <v>7536.5</v>
+        <v>7542.94</v>
       </c>
       <c r="M12" t="n">
-        <v>7591.25</v>
+        <v>7580.12</v>
       </c>
       <c r="N12" t="n">
-        <v>7646</v>
+        <v>7617.31</v>
       </c>
       <c r="O12" t="n">
-        <v>7653.75</v>
+        <v>7652.25</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1522,16 +1520,20 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1539,64 +1541,64 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="10" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C13" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D13" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E13" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I13" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J13" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K13" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L13" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M13" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N13" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O13" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1604,19 +1606,17 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1625,148 +1625,146 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="10" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C14" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D14" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E14" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F14" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H14" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I14" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J14" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K14" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L14" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M14" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N14" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O14" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="10" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C15" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D15" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E15" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F15" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H15" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I15" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J15" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K15" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L15" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M15" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N15" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O15" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1795,7 +1793,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="10" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1805,132 +1803,134 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C16" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D16" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E16" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F16" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H16" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I16" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J16" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K16" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L16" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M16" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N16" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O16" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="10" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C17" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D17" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E17" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H17" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I17" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J17" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K17" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L17" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M17" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N17" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O17" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1941,7 +1941,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1957,7 +1957,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="10" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1971,216 +1971,216 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C18" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D18" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E18" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F18" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H18" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I18" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J18" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K18" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L18" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M18" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N18" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O18" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="10" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C19" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D19" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E19" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H19" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I19" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J19" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K19" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L19" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M19" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N19" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O19" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="10" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C20" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D20" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E20" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F20" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H20" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I20" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J20" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K20" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L20" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M20" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N20" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O20" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2191,7 +2191,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="11" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2207,148 +2207,150 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="10" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C21" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D21" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E21" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F21" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H21" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I21" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J21" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K21" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L21" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M21" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N21" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O21" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="10" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C22" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D22" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E22" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F22" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H22" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I22" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J22" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K22" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L22" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M22" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N22" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O22" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2377,146 +2379,144 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="10" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C23" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D23" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E23" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F23" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H23" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I23" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J23" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K23" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L23" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M23" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N23" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O23" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="10" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C24" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D24" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E24" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I24" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J24" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K24" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L24" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M24" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N24" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O24" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2527,9 +2527,9 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2537,15 +2537,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -2557,50 +2559,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C25" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D25" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E25" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F25" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H25" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I25" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J25" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K25" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L25" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M25" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N25" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O25" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2608,28 +2610,26 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2643,65 +2643,69 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C26" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D26" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E26" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H26" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I26" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J26" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K26" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L26" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M26" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N26" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O26" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2715,81 +2719,71 @@
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C27" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D27" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E27" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F27" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H27" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I27" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J27" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K27" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L27" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M27" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N27" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O27" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7687.25</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2801,60 +2795,64 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="10" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C28" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D28" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E28" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F28" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H28" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I28" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J28" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K28" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L28" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M28" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N28" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O28" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2870,16 +2868,20 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="10" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2893,50 +2895,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C29" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D29" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E29" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F29" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H29" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I29" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J29" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K29" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L29" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M29" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N29" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O29" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2947,25 +2949,21 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="10" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2979,67 +2977,75 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C30" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D30" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E30" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H30" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I30" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J30" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K30" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L30" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M30" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N30" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O30" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3047,154 +3053,150 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="10" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C31" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D31" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E31" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H31" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I31" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J31" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K31" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L31" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M31" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N31" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O31" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="10" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C32" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D32" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E32" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F32" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H32" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I32" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J32" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K32" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L32" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M32" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N32" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O32" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3205,82 +3207,80 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="11" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="10" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C33" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D33" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E33" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F33" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H33" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I33" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J33" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K33" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L33" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M33" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N33" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O33" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,23 +3291,25 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="11" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="10" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3321,50 +3323,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C34" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D34" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E34" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F34" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H34" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I34" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J34" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K34" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L34" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M34" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N34" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O34" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3375,7 +3377,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="11" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3390,67 +3392,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C35" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D35" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E35" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F35" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H35" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I35" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J35" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K35" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L35" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M35" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N35" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O35" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3461,80 +3461,78 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C36" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D36" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E36" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F36" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H36" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I36" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J36" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K36" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L36" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M36" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N36" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O36" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3542,12 +3540,14 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3559,64 +3559,64 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C37" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D37" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E37" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F37" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H37" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I37" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J37" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K37" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L37" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M37" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N37" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O37" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3624,83 +3624,81 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C38" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D38" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E38" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F38" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H38" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I38" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J38" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K38" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L38" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M38" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N38" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O38" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3711,95 +3709,101 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C39" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D39" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E39" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H39" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I39" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J39" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K39" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L39" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M39" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N39" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O39" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3807,152 +3811,148 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C40" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D40" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E40" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F40" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H40" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I40" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J40" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K40" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L40" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M40" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N40" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O40" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C41" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D41" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E41" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F41" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H41" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I41" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J41" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K41" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L41" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M41" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N41" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O41" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3963,80 +3963,78 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="11" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C42" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D42" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E42" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F42" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H42" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I42" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J42" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K42" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L42" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M42" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N42" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O42" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4047,95 +4045,101 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C43" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D43" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E43" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F43" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H43" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I43" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J43" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K43" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L43" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M43" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N43" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O43" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4143,73 +4147,73 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C44" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D44" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E44" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F44" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H44" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I44" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J44" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K44" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L44" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M44" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N44" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O44" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -4220,10 +4224,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4231,7 +4233,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4245,308 +4247,306 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C45" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D45" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E45" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F45" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H45" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I45" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J45" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K45" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L45" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M45" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N45" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O45" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
       </c>
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C46" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D46" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E46" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H46" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I46" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J46" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K46" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L46" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M46" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N46" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O46" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C47" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D47" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E47" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F47" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H47" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I47" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J47" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K47" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L47" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M47" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N47" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O47" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C48" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D48" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E48" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F48" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H48" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I48" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J48" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K48" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L48" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M48" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N48" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O48" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4554,18 +4554,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4573,64 +4573,64 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C49" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D49" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E49" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F49" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H49" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I49" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J49" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K49" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L49" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M49" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N49" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O49" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4638,83 +4638,81 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C50" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D50" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E50" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F50" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H50" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I50" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J50" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K50" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L50" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M50" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N50" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O50" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4725,78 +4723,78 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C51" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D51" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E51" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H51" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I51" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J51" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K51" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L51" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M51" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N51" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O51" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4807,78 +4805,80 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C52" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E52" t="n">
         <v>7722</v>
       </c>
-      <c r="C52" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D52" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E52" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F52" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H52" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I52" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J52" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K52" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L52" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M52" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N52" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O52" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4886,12 +4886,14 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -4899,70 +4901,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C53" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D53" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E53" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F53" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H53" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I53" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J53" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K53" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L53" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M53" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N53" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O53" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4980,10 +4982,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4991,74 +4991,78 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C54" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D54" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E54" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F54" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H54" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I54" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J54" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K54" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L54" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M54" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N54" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O54" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
@@ -5077,146 +5081,142 @@
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C55" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D55" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E55" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H55" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I55" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J55" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K55" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L55" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M55" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N55" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O55" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="10" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C56" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D56" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E56" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F56" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H56" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I56" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J56" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K56" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L56" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M56" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N56" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O56" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5227,80 +5227,84 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="11" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="10" t="inlineStr">
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C57" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D57" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E57" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F57" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H57" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I57" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J57" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K57" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L57" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M57" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N57" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O57" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5311,84 +5315,78 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C58" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D58" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H58" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I58" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J58" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K58" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L58" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M58" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N58" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O58" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5396,12 +5394,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5413,64 +5413,60 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="10" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C59" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D59" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E59" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F59" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H59" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I59" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J59" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K59" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L59" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M59" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N59" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O59" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5497,7 +5493,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="10" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5507,50 +5503,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C60" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D60" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E60" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F60" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H60" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I60" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J60" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K60" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L60" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M60" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N60" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O60" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5577,7 +5573,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="10" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5587,50 +5583,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C61" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D61" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E61" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H61" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I61" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J61" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K61" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L61" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M61" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N61" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O61" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5638,143 +5634,63 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="10" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>7599.5</v>
-      </c>
-      <c r="C62" t="n">
-        <v>7683.5</v>
-      </c>
-      <c r="D62" t="n">
-        <v>7594.25</v>
-      </c>
-      <c r="E62" t="n">
-        <v>7659.5</v>
-      </c>
-      <c r="F62" t="n">
-        <v>61</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="H62" t="n">
-        <v>89.25</v>
-      </c>
-      <c r="I62" t="n">
-        <v>7504.75</v>
-      </c>
-      <c r="J62" t="n">
-        <v>7504.06</v>
-      </c>
-      <c r="K62" t="n">
-        <v>7558.12</v>
-      </c>
-      <c r="L62" t="n">
-        <v>7612.19</v>
-      </c>
-      <c r="M62" t="n">
-        <v>7638.88</v>
-      </c>
-      <c r="N62" t="n">
-        <v>7665.56</v>
-      </c>
-      <c r="O62" t="n">
-        <v>7747</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
+      <c r="I62" s="13" t="n">
         <v>7505</v>
       </c>
-      <c r="J63" s="13" t="n">
+      <c r="J62" s="13" t="n">
         <v>7580.56</v>
       </c>
-      <c r="K63" s="13" t="n">
+      <c r="K62" s="13" t="n">
         <v>7614.88</v>
       </c>
-      <c r="L63" s="13" t="n">
+      <c r="L62" s="13" t="n">
         <v>7649.19</v>
       </c>
-      <c r="M63" s="13" t="n">
+      <c r="M62" s="13" t="n">
         <v>7704.12</v>
       </c>
-      <c r="N63" s="13" t="n">
+      <c r="N62" s="13" t="n">
         <v>7759.06</v>
       </c>
-      <c r="O63" s="13" t="n">
+      <c r="O62" s="13" t="n">
         <v>7772.75</v>
       </c>
     </row>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -109,17 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,74 +641,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>7440.5</v>
+      </c>
+      <c r="C2" t="n">
         <v>7514.5</v>
       </c>
-      <c r="C2" t="n">
-        <v>7544.5</v>
-      </c>
       <c r="D2" t="n">
-        <v>7405</v>
+        <v>7436.25</v>
       </c>
       <c r="E2" t="n">
-        <v>7424.5</v>
+        <v>7508.43</v>
       </c>
       <c r="F2" t="n">
-        <v>-94</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0125</v>
+        <v>0.0113</v>
       </c>
       <c r="H2" t="n">
-        <v>139.5</v>
+        <v>78.25</v>
       </c>
       <c r="I2" t="n">
-        <v>7449</v>
+        <v>7265.5</v>
       </c>
       <c r="J2" t="n">
-        <v>7446.94</v>
+        <v>7259.88</v>
       </c>
       <c r="K2" t="n">
-        <v>7488.12</v>
+        <v>7354.75</v>
       </c>
       <c r="L2" t="n">
-        <v>7529.31</v>
+        <v>7449.62</v>
       </c>
       <c r="M2" t="n">
-        <v>7548.88</v>
+        <v>7494.25</v>
       </c>
       <c r="N2" t="n">
-        <v>7568.44</v>
+        <v>7538.88</v>
       </c>
       <c r="O2" t="n">
-        <v>7631.25</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
+        <v>7684</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -717,58 +713,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7440.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C3" t="n">
-        <v>7514.5</v>
+        <v>7599.25</v>
       </c>
       <c r="D3" t="n">
-        <v>7436.25</v>
+        <v>7513</v>
       </c>
       <c r="E3" t="n">
-        <v>7508.43</v>
+        <v>7541.25</v>
       </c>
       <c r="F3" t="n">
-        <v>83.93000000000001</v>
+        <v>32.82</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0044</v>
       </c>
       <c r="H3" t="n">
-        <v>78.25</v>
+        <v>86.25</v>
       </c>
       <c r="I3" t="n">
-        <v>7265.5</v>
+        <v>7358</v>
       </c>
       <c r="J3" t="n">
-        <v>7259.88</v>
+        <v>7446.71</v>
       </c>
       <c r="K3" t="n">
-        <v>7354.75</v>
+        <v>7469.31</v>
       </c>
       <c r="L3" t="n">
-        <v>7449.62</v>
+        <v>7491.9</v>
       </c>
       <c r="M3" t="n">
-        <v>7494.25</v>
+        <v>7547.56</v>
       </c>
       <c r="N3" t="n">
-        <v>7538.88</v>
+        <v>7603.21</v>
       </c>
       <c r="O3" t="n">
-        <v>7684</v>
+        <v>7592.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,7 +779,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -792,172 +792,162 @@
       <c r="U3" s="8" t="n">
         <v/>
       </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7543.25</v>
+        <v>7541.25</v>
       </c>
       <c r="C4" t="n">
-        <v>7599.25</v>
+        <v>7549.5</v>
       </c>
       <c r="D4" t="n">
-        <v>7513</v>
+        <v>7415.25</v>
       </c>
       <c r="E4" t="n">
-        <v>7541.25</v>
+        <v>7437.5</v>
       </c>
       <c r="F4" t="n">
-        <v>32.82</v>
+        <v>-103.75</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0138</v>
       </c>
       <c r="H4" t="n">
-        <v>86.25</v>
+        <v>134.25</v>
       </c>
       <c r="I4" t="n">
-        <v>7358</v>
+        <v>7426.75</v>
       </c>
       <c r="J4" t="n">
-        <v>7446.71</v>
+        <v>7447.56</v>
       </c>
       <c r="K4" t="n">
-        <v>7469.31</v>
+        <v>7498.12</v>
       </c>
       <c r="L4" t="n">
-        <v>7491.9</v>
+        <v>7548.69</v>
       </c>
       <c r="M4" t="n">
-        <v>7547.56</v>
+        <v>7584.38</v>
       </c>
       <c r="N4" t="n">
-        <v>7603.21</v>
+        <v>7620.06</v>
       </c>
       <c r="O4" t="n">
-        <v>7592.75</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+        <v>7685.5</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7541.25</v>
+        <v>7449.25</v>
       </c>
       <c r="C5" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D5" t="n">
-        <v>7415.25</v>
+        <v>7404.25</v>
       </c>
       <c r="E5" t="n">
-        <v>7437.5</v>
+        <v>7428.25</v>
       </c>
       <c r="F5" t="n">
-        <v>-103.75</v>
+        <v>-9.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.0012</v>
       </c>
       <c r="H5" t="n">
-        <v>134.25</v>
+        <v>92.25</v>
       </c>
       <c r="I5" t="n">
-        <v>7426.75</v>
+        <v>7281</v>
       </c>
       <c r="J5" t="n">
-        <v>7447.56</v>
+        <v>7280.81</v>
       </c>
       <c r="K5" t="n">
-        <v>7498.12</v>
+        <v>7370.38</v>
       </c>
       <c r="L5" t="n">
-        <v>7548.69</v>
+        <v>7459.94</v>
       </c>
       <c r="M5" t="n">
-        <v>7584.38</v>
+        <v>7504.62</v>
       </c>
       <c r="N5" t="n">
-        <v>7620.06</v>
+        <v>7549.31</v>
       </c>
       <c r="O5" t="n">
-        <v>7685.5</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>7683.75</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -969,7 +959,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -979,50 +969,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7449.25</v>
+        <v>7476.25</v>
       </c>
       <c r="C6" t="n">
-        <v>7496.5</v>
+        <v>7496</v>
       </c>
       <c r="D6" t="n">
-        <v>7404.25</v>
+        <v>7390.5</v>
       </c>
       <c r="E6" t="n">
-        <v>7428.25</v>
+        <v>7423.25</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.25</v>
+        <v>-5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.0007</v>
       </c>
       <c r="H6" t="n">
-        <v>92.25</v>
+        <v>105.5</v>
       </c>
       <c r="I6" t="n">
-        <v>7281</v>
+        <v>7312</v>
       </c>
       <c r="J6" t="n">
-        <v>7280.81</v>
+        <v>7324.94</v>
       </c>
       <c r="K6" t="n">
-        <v>7370.38</v>
+        <v>7382.12</v>
       </c>
       <c r="L6" t="n">
-        <v>7459.94</v>
+        <v>7439.31</v>
       </c>
       <c r="M6" t="n">
-        <v>7504.62</v>
+        <v>7474.38</v>
       </c>
       <c r="N6" t="n">
-        <v>7549.31</v>
+        <v>7509.44</v>
       </c>
       <c r="O6" t="n">
-        <v>7683.75</v>
+        <v>7588.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1033,13 +1023,15 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1047,7 +1039,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1057,50 +1049,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7476.25</v>
+        <v>7431</v>
       </c>
       <c r="C7" t="n">
-        <v>7496</v>
+        <v>7459.5</v>
       </c>
       <c r="D7" t="n">
-        <v>7390.5</v>
+        <v>7357.25</v>
       </c>
       <c r="E7" t="n">
-        <v>7423.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F7" t="n">
-        <v>-5</v>
+        <v>-21.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0029</v>
       </c>
       <c r="H7" t="n">
-        <v>105.5</v>
+        <v>102.25</v>
       </c>
       <c r="I7" t="n">
-        <v>7312</v>
+        <v>7285</v>
       </c>
       <c r="J7" t="n">
-        <v>7324.94</v>
+        <v>7307.75</v>
       </c>
       <c r="K7" t="n">
-        <v>7382.12</v>
+        <v>7370.5</v>
       </c>
       <c r="L7" t="n">
-        <v>7439.31</v>
+        <v>7433.25</v>
       </c>
       <c r="M7" t="n">
-        <v>7474.38</v>
+        <v>7476</v>
       </c>
       <c r="N7" t="n">
-        <v>7509.44</v>
+        <v>7518.75</v>
       </c>
       <c r="O7" t="n">
-        <v>7588.75</v>
+        <v>7601.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,18 +1100,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1127,7 +1119,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1137,50 +1129,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7431</v>
+        <v>7398</v>
       </c>
       <c r="C8" t="n">
-        <v>7459.5</v>
+        <v>7505</v>
       </c>
       <c r="D8" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E8" t="n">
-        <v>7401.75</v>
+        <v>7500.25</v>
       </c>
       <c r="F8" t="n">
-        <v>-21.5</v>
+        <v>98.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0133</v>
       </c>
       <c r="H8" t="n">
-        <v>102.25</v>
+        <v>107</v>
       </c>
       <c r="I8" t="n">
-        <v>7285</v>
+        <v>7255</v>
       </c>
       <c r="J8" t="n">
-        <v>7307.75</v>
+        <v>7296.19</v>
       </c>
       <c r="K8" t="n">
-        <v>7370.5</v>
+        <v>7350.62</v>
       </c>
       <c r="L8" t="n">
-        <v>7433.25</v>
+        <v>7405.06</v>
       </c>
       <c r="M8" t="n">
-        <v>7476</v>
+        <v>7452.88</v>
       </c>
       <c r="N8" t="n">
-        <v>7518.75</v>
+        <v>7500.69</v>
       </c>
       <c r="O8" t="n">
-        <v>7601.5</v>
+        <v>7561.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,79 +1180,85 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7398</v>
+        <v>7495.5</v>
       </c>
       <c r="C9" t="n">
-        <v>7505</v>
+        <v>7567.75</v>
       </c>
       <c r="D9" t="n">
-        <v>7398</v>
+        <v>7481.75</v>
       </c>
       <c r="E9" t="n">
-        <v>7500.25</v>
+        <v>7548.25</v>
       </c>
       <c r="F9" t="n">
-        <v>98.5</v>
+        <v>48</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0064</v>
       </c>
       <c r="H9" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="I9" t="n">
-        <v>7255</v>
+        <v>7291</v>
       </c>
       <c r="J9" t="n">
-        <v>7296.19</v>
+        <v>7417.62</v>
       </c>
       <c r="K9" t="n">
-        <v>7350.62</v>
+        <v>7446.75</v>
       </c>
       <c r="L9" t="n">
-        <v>7405.06</v>
+        <v>7475.88</v>
       </c>
       <c r="M9" t="n">
-        <v>7452.88</v>
+        <v>7553.75</v>
       </c>
       <c r="N9" t="n">
-        <v>7500.69</v>
+        <v>7631.62</v>
       </c>
       <c r="O9" t="n">
-        <v>7561.75</v>
+        <v>7612</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,25 +1269,23 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1303,50 +1299,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7495.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C10" t="n">
-        <v>7567.75</v>
+        <v>7579</v>
       </c>
       <c r="D10" t="n">
-        <v>7481.75</v>
+        <v>7505.75</v>
       </c>
       <c r="E10" t="n">
-        <v>7548.25</v>
+        <v>7543.5</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>-4.75</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0064</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>86</v>
+        <v>73.25</v>
       </c>
       <c r="I10" t="n">
-        <v>7291</v>
+        <v>7395.75</v>
       </c>
       <c r="J10" t="n">
-        <v>7417.62</v>
+        <v>7474</v>
       </c>
       <c r="K10" t="n">
-        <v>7446.75</v>
+        <v>7505.25</v>
       </c>
       <c r="L10" t="n">
-        <v>7475.88</v>
+        <v>7536.5</v>
       </c>
       <c r="M10" t="n">
-        <v>7553.75</v>
+        <v>7591.25</v>
       </c>
       <c r="N10" t="n">
-        <v>7631.62</v>
+        <v>7646</v>
       </c>
       <c r="O10" t="n">
-        <v>7612</v>
+        <v>7653.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,15 +1353,13 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1373,64 +1367,64 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7543.25</v>
+        <v>7536</v>
       </c>
       <c r="C11" t="n">
-        <v>7579</v>
+        <v>7593.75</v>
       </c>
       <c r="D11" t="n">
-        <v>7505.75</v>
+        <v>7479.5</v>
       </c>
       <c r="E11" t="n">
-        <v>7543.5</v>
+        <v>7528.25</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.75</v>
+        <v>-15.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="H11" t="n">
-        <v>73.25</v>
+        <v>114.25</v>
       </c>
       <c r="I11" t="n">
-        <v>7395.75</v>
+        <v>7432.5</v>
       </c>
       <c r="J11" t="n">
-        <v>7474</v>
+        <v>7470.81</v>
       </c>
       <c r="K11" t="n">
-        <v>7505.25</v>
+        <v>7506.88</v>
       </c>
       <c r="L11" t="n">
-        <v>7536.5</v>
+        <v>7542.94</v>
       </c>
       <c r="M11" t="n">
-        <v>7591.25</v>
+        <v>7580.12</v>
       </c>
       <c r="N11" t="n">
-        <v>7646</v>
+        <v>7617.31</v>
       </c>
       <c r="O11" t="n">
-        <v>7653.75</v>
+        <v>7652.25</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1438,16 +1432,20 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1455,64 +1453,64 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C12" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D12" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E12" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I12" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J12" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K12" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L12" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M12" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N12" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O12" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1520,19 +1518,17 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U12" s="8" t="n">
@@ -1541,83 +1537,85 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C13" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D13" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E13" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F13" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H13" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I13" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J13" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K13" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L13" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M13" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N13" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O13" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1625,64 +1623,60 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C14" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D14" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E14" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F14" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H14" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I14" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J14" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K14" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L14" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M14" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N14" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O14" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1697,7 +1691,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1711,7 +1705,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1721,132 +1715,134 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C15" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D15" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E15" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F15" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H15" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I15" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J15" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K15" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L15" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M15" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N15" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O15" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C16" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D16" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E16" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H16" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I16" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J16" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K16" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L16" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M16" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N16" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O16" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1857,7 +1853,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1873,7 +1869,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1887,69 +1883,71 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C17" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D17" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E17" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F17" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H17" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I17" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J17" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K17" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L17" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M17" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N17" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O17" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1957,146 +1955,144 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C18" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D18" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E18" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H18" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I18" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J18" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K18" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L18" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M18" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N18" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O18" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C19" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D19" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E19" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F19" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H19" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I19" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J19" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K19" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L19" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M19" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N19" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O19" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2107,7 +2103,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2123,83 +2119,85 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C20" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D20" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E20" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F20" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H20" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I20" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J20" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K20" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L20" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M20" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N20" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O20" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2207,64 +2205,64 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C21" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D21" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E21" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F21" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H21" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I21" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J21" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K21" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L21" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M21" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N21" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O21" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2279,7 +2277,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2293,146 +2291,144 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C22" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D22" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E22" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F22" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H22" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I22" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J22" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K22" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L22" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M22" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N22" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O22" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C23" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D23" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E23" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I23" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J23" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K23" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L23" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M23" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N23" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O23" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2445,7 +2441,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2453,15 +2449,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -2473,50 +2471,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C24" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D24" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E24" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F24" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H24" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I24" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J24" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K24" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L24" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M24" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N24" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O24" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2524,28 +2522,26 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2559,56 +2555,60 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C25" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D25" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E25" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H25" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I25" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J25" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K25" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L25" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M25" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N25" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O25" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2631,81 +2631,71 @@
       </c>
       <c r="W25" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C26" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D26" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E26" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H26" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I26" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J26" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K26" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L26" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M26" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N26" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O26" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>7687.25</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2717,60 +2707,64 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C27" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D27" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E27" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H27" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I27" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J27" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K27" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L27" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M27" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N27" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O27" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2781,21 +2775,25 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2809,50 +2807,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C28" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D28" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E28" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F28" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H28" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I28" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J28" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K28" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L28" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M28" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N28" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O28" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2865,23 +2863,19 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2895,67 +2889,75 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C29" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D29" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E29" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H29" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I29" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J29" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K29" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L29" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M29" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N29" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O29" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2963,154 +2965,150 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C30" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D30" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E30" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F30" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H30" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I30" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J30" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K30" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L30" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M30" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N30" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O30" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C31" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D31" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E31" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F31" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H31" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I31" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J31" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K31" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L31" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M31" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N31" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O31" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3121,82 +3119,80 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C32" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D32" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E32" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F32" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H32" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I32" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J32" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K32" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L32" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M32" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N32" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O32" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3207,23 +3203,25 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3237,50 +3235,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C33" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D33" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E33" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F33" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H33" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I33" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J33" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K33" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L33" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M33" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N33" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O33" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,7 +3289,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3306,67 +3304,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C34" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D34" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E34" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F34" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H34" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I34" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J34" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K34" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L34" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M34" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N34" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O34" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3377,80 +3373,78 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C35" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D35" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E35" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F35" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H35" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I35" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J35" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K35" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L35" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M35" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N35" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O35" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3458,12 +3452,14 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3475,64 +3471,64 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C36" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D36" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E36" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F36" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H36" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I36" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J36" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K36" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L36" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M36" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N36" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O36" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3540,83 +3536,81 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C37" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D37" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E37" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F37" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H37" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I37" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J37" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K37" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L37" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M37" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N37" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O37" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3627,95 +3621,101 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C38" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D38" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E38" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F38" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H38" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I38" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J38" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K38" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L38" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M38" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N38" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O38" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3723,152 +3723,148 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C39" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D39" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E39" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H39" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I39" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J39" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K39" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L39" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M39" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N39" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O39" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C40" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D40" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E40" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F40" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H40" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I40" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J40" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K40" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L40" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M40" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N40" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O40" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3879,80 +3875,78 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C41" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D41" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E41" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F41" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H41" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I41" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J41" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K41" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L41" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M41" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N41" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O41" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3965,93 +3959,99 @@
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C42" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D42" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E42" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F42" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H42" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I42" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J42" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K42" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L42" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M42" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N42" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O42" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4059,87 +4059,85 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C43" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D43" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E43" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F43" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H43" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I43" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J43" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K43" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L43" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M43" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N43" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O43" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4147,7 +4145,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4161,308 +4159,306 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C44" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D44" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E44" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F44" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H44" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I44" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J44" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K44" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L44" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M44" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N44" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O44" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
       </c>
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C45" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D45" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E45" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H45" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I45" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J45" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K45" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L45" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M45" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N45" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O45" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C46" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D46" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E46" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F46" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H46" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I46" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J46" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K46" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L46" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M46" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N46" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O46" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C47" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D47" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E47" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F47" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H47" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I47" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J47" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K47" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L47" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M47" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N47" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O47" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4470,18 +4466,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4489,64 +4485,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C48" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D48" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E48" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F48" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H48" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I48" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J48" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K48" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L48" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M48" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N48" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O48" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4554,83 +4550,81 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C49" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D49" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E49" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F49" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H49" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I49" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J49" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K49" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L49" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M49" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N49" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O49" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4641,78 +4635,78 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C50" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D50" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E50" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H50" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I50" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J50" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K50" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L50" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M50" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N50" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O50" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4723,78 +4717,80 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C51" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D51" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E51" t="n">
         <v>7722</v>
       </c>
-      <c r="C51" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D51" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E51" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F51" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H51" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I51" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J51" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K51" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L51" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M51" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N51" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O51" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4802,12 +4798,14 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
@@ -4815,70 +4813,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C52" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D52" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E52" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F52" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H52" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I52" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J52" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K52" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L52" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M52" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N52" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O52" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4891,15 +4889,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4907,77 +4903,81 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C53" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D53" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E53" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F53" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H53" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I53" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J53" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K53" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L53" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M53" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N53" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O53" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4993,146 +4993,142 @@
       </c>
       <c r="W53" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C54" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D54" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E54" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H54" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I54" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J54" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K54" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L54" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M54" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N54" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O54" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C55" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D55" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E55" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F55" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H55" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I55" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J55" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K55" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L55" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M55" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N55" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O55" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5143,80 +5139,84 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C56" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D56" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E56" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F56" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H56" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I56" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J56" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K56" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L56" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M56" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N56" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O56" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5229,82 +5229,76 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W56" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C57" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D57" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H57" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I57" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J57" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K57" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L57" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M57" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N57" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O57" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5312,12 +5306,14 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5329,64 +5325,60 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C58" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D58" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H58" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I58" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J58" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K58" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L58" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M58" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N58" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O58" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5399,7 +5391,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5413,7 +5405,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5423,50 +5415,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C59" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D59" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E59" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H59" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I59" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J59" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K59" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L59" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M59" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N59" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O59" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5479,7 +5471,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5493,7 +5485,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5503,50 +5495,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C60" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D60" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E60" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F60" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H60" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I60" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J60" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K60" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L60" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M60" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N60" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O60" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5554,79 +5546,85 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C61" t="n">
-        <v>7683.5</v>
+        <v>7719.75</v>
       </c>
       <c r="D61" t="n">
-        <v>7594.25</v>
+        <v>7661.25</v>
       </c>
       <c r="E61" t="n">
-        <v>7659.5</v>
+        <v>7700</v>
       </c>
       <c r="F61" t="n">
-        <v>61</v>
+        <v>40.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0053</v>
       </c>
       <c r="H61" t="n">
-        <v>89.25</v>
+        <v>58.5</v>
       </c>
       <c r="I61" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J61" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K61" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L61" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M61" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N61" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O61" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5637,25 +5635,23 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5673,25 +5669,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>7505</v>
+        <v>7602.75</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>7580.56</v>
+        <v>7646.25</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>7614.88</v>
+        <v>7670.75</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>7649.19</v>
+        <v>7695.25</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>7704.12</v>
+        <v>7729.25</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>7759.06</v>
+        <v>7763.25</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>7772.75</v>
+        <v>7778.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5585,25 +5585,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7609.25</v>
+        <v>7699.25</v>
       </c>
       <c r="C61" t="n">
-        <v>7719.75</v>
+        <v>7701</v>
       </c>
       <c r="D61" t="n">
-        <v>7661.25</v>
+        <v>7692</v>
       </c>
       <c r="E61" t="n">
-        <v>7700</v>
+        <v>7694</v>
       </c>
       <c r="F61" t="n">
-        <v>40.5</v>
+        <v>34.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.0045</v>
       </c>
       <c r="H61" t="n">
-        <v>58.5</v>
+        <v>9</v>
       </c>
       <c r="I61" t="n">
         <v>7505</v>
@@ -5669,25 +5669,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>7602.75</v>
+        <v>7683</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>7646.25</v>
+        <v>7683.75</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>7670.75</v>
+        <v>7689.5</v>
       </c>
       <c r="L62" s="13" t="n">
         <v>7695.25</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>7729.25</v>
+        <v>7698.5</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>7763.25</v>
+        <v>7701.75</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>7778.25</v>
+        <v>7710</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5591,19 +5591,19 @@
         <v>7701</v>
       </c>
       <c r="D61" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="E61" t="n">
-        <v>7694</v>
+        <v>7694.25</v>
       </c>
       <c r="F61" t="n">
-        <v>34.5</v>
+        <v>34.75</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>0.0045</v>
       </c>
       <c r="H61" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I61" t="n">
         <v>7505</v>
@@ -5669,25 +5669,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>7683</v>
+        <v>7679</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>7683.75</v>
+        <v>7682.62</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>7689.5</v>
+        <v>7688.75</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>7695.25</v>
+        <v>7694.88</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>7698.5</v>
+        <v>7699.75</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>7701.75</v>
+        <v>7704.62</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>7710</v>
+        <v>7712</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5591,19 +5591,19 @@
         <v>7701</v>
       </c>
       <c r="D61" t="n">
-        <v>7690</v>
+        <v>7688.5</v>
       </c>
       <c r="E61" t="n">
-        <v>7694.25</v>
+        <v>7688.75</v>
       </c>
       <c r="F61" t="n">
-        <v>34.75</v>
+        <v>29.25</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0038</v>
       </c>
       <c r="H61" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="I61" t="n">
         <v>7505</v>
@@ -5669,25 +5669,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>7679</v>
+        <v>7676</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>7682.62</v>
+        <v>7673.25</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>7688.75</v>
+        <v>7682.5</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>7694.88</v>
+        <v>7691.75</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>7699.75</v>
+        <v>7695</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>7704.62</v>
+        <v>7698.25</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>7712</v>
+        <v>7713.5</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5585,25 +5585,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7699.25</v>
+        <v>7609.25</v>
       </c>
       <c r="C61" t="n">
-        <v>7701</v>
+        <v>7652</v>
       </c>
       <c r="D61" t="n">
-        <v>7688.5</v>
+        <v>7593.75</v>
       </c>
       <c r="E61" t="n">
-        <v>7688.75</v>
+        <v>7625</v>
       </c>
       <c r="F61" t="n">
-        <v>29.25</v>
+        <v>-34.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0045</v>
       </c>
       <c r="H61" t="n">
-        <v>12.5</v>
+        <v>58.25</v>
       </c>
       <c r="I61" t="n">
         <v>7505</v>
@@ -5632,19 +5632,19 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5656,11 +5656,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5669,25 +5665,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>7676</v>
+        <v>7535.5</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>7673.25</v>
+        <v>7567.81</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>7682.5</v>
+        <v>7595.88</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>7691.75</v>
+        <v>7623.94</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>7695</v>
+        <v>7654.12</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>7698.25</v>
+        <v>7684.31</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>7713.5</v>
+        <v>7710.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7440.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C2" t="n">
-        <v>7514.5</v>
+        <v>7599.25</v>
       </c>
       <c r="D2" t="n">
-        <v>7436.25</v>
+        <v>7513</v>
       </c>
       <c r="E2" t="n">
-        <v>7508.43</v>
+        <v>7541.25</v>
       </c>
       <c r="F2" t="n">
-        <v>83.93000000000001</v>
+        <v>32.82</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0044</v>
       </c>
       <c r="H2" t="n">
-        <v>78.25</v>
+        <v>86.25</v>
       </c>
       <c r="I2" t="n">
-        <v>7265.5</v>
+        <v>7358</v>
       </c>
       <c r="J2" t="n">
-        <v>7259.88</v>
+        <v>7446.71</v>
       </c>
       <c r="K2" t="n">
-        <v>7354.75</v>
+        <v>7469.31</v>
       </c>
       <c r="L2" t="n">
-        <v>7449.62</v>
+        <v>7491.9</v>
       </c>
       <c r="M2" t="n">
-        <v>7494.25</v>
+        <v>7547.56</v>
       </c>
       <c r="N2" t="n">
-        <v>7538.88</v>
+        <v>7603.21</v>
       </c>
       <c r="O2" t="n">
-        <v>7684</v>
+        <v>7592.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -708,98 +708,98 @@
       <c r="U2" s="8" t="n">
         <v/>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7543.25</v>
+        <v>7541.25</v>
       </c>
       <c r="C3" t="n">
-        <v>7599.25</v>
+        <v>7549.5</v>
       </c>
       <c r="D3" t="n">
-        <v>7513</v>
+        <v>7415.25</v>
       </c>
       <c r="E3" t="n">
-        <v>7541.25</v>
+        <v>7437.5</v>
       </c>
       <c r="F3" t="n">
-        <v>32.82</v>
+        <v>-103.75</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0138</v>
       </c>
       <c r="H3" t="n">
-        <v>86.25</v>
+        <v>134.25</v>
       </c>
       <c r="I3" t="n">
-        <v>7358</v>
+        <v>7426.75</v>
       </c>
       <c r="J3" t="n">
-        <v>7446.71</v>
+        <v>7447.56</v>
       </c>
       <c r="K3" t="n">
-        <v>7469.31</v>
+        <v>7498.12</v>
       </c>
       <c r="L3" t="n">
-        <v>7491.9</v>
+        <v>7548.69</v>
       </c>
       <c r="M3" t="n">
-        <v>7547.56</v>
+        <v>7584.38</v>
       </c>
       <c r="N3" t="n">
-        <v>7603.21</v>
+        <v>7620.06</v>
       </c>
       <c r="O3" t="n">
-        <v>7592.75</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+        <v>7685.5</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -807,69 +807,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7541.25</v>
+        <v>7449.25</v>
       </c>
       <c r="C4" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D4" t="n">
-        <v>7415.25</v>
+        <v>7404.25</v>
       </c>
       <c r="E4" t="n">
-        <v>7437.5</v>
+        <v>7428.25</v>
       </c>
       <c r="F4" t="n">
-        <v>-103.75</v>
+        <v>-9.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.0012</v>
       </c>
       <c r="H4" t="n">
-        <v>134.25</v>
+        <v>92.25</v>
       </c>
       <c r="I4" t="n">
-        <v>7426.75</v>
+        <v>7281</v>
       </c>
       <c r="J4" t="n">
-        <v>7447.56</v>
+        <v>7280.81</v>
       </c>
       <c r="K4" t="n">
-        <v>7498.12</v>
+        <v>7370.38</v>
       </c>
       <c r="L4" t="n">
-        <v>7548.69</v>
+        <v>7459.94</v>
       </c>
       <c r="M4" t="n">
-        <v>7584.38</v>
+        <v>7504.62</v>
       </c>
       <c r="N4" t="n">
-        <v>7620.06</v>
+        <v>7549.31</v>
       </c>
       <c r="O4" t="n">
-        <v>7685.5</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7683.75</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -891,50 +885,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7449.25</v>
+        <v>7476.25</v>
       </c>
       <c r="C5" t="n">
-        <v>7496.5</v>
+        <v>7496</v>
       </c>
       <c r="D5" t="n">
-        <v>7404.25</v>
+        <v>7390.5</v>
       </c>
       <c r="E5" t="n">
-        <v>7428.25</v>
+        <v>7423.25</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.25</v>
+        <v>-5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.0007</v>
       </c>
       <c r="H5" t="n">
-        <v>92.25</v>
+        <v>105.5</v>
       </c>
       <c r="I5" t="n">
-        <v>7281</v>
+        <v>7312</v>
       </c>
       <c r="J5" t="n">
-        <v>7280.81</v>
+        <v>7324.94</v>
       </c>
       <c r="K5" t="n">
-        <v>7370.38</v>
+        <v>7382.12</v>
       </c>
       <c r="L5" t="n">
-        <v>7459.94</v>
+        <v>7439.31</v>
       </c>
       <c r="M5" t="n">
-        <v>7504.62</v>
+        <v>7474.38</v>
       </c>
       <c r="N5" t="n">
-        <v>7549.31</v>
+        <v>7509.44</v>
       </c>
       <c r="O5" t="n">
-        <v>7683.75</v>
+        <v>7588.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -950,8 +944,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -969,50 +965,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7476.25</v>
+        <v>7431</v>
       </c>
       <c r="C6" t="n">
-        <v>7496</v>
+        <v>7459.5</v>
       </c>
       <c r="D6" t="n">
-        <v>7390.5</v>
+        <v>7357.25</v>
       </c>
       <c r="E6" t="n">
-        <v>7423.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F6" t="n">
-        <v>-5</v>
+        <v>-21.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0029</v>
       </c>
       <c r="H6" t="n">
-        <v>105.5</v>
+        <v>102.25</v>
       </c>
       <c r="I6" t="n">
-        <v>7312</v>
+        <v>7285</v>
       </c>
       <c r="J6" t="n">
-        <v>7324.94</v>
+        <v>7307.75</v>
       </c>
       <c r="K6" t="n">
-        <v>7382.12</v>
+        <v>7370.5</v>
       </c>
       <c r="L6" t="n">
-        <v>7439.31</v>
+        <v>7433.25</v>
       </c>
       <c r="M6" t="n">
-        <v>7474.38</v>
+        <v>7476</v>
       </c>
       <c r="N6" t="n">
-        <v>7509.44</v>
+        <v>7518.75</v>
       </c>
       <c r="O6" t="n">
-        <v>7588.75</v>
+        <v>7601.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,18 +1016,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1049,50 +1045,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7431</v>
+        <v>7398</v>
       </c>
       <c r="C7" t="n">
-        <v>7459.5</v>
+        <v>7505</v>
       </c>
       <c r="D7" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E7" t="n">
-        <v>7401.75</v>
+        <v>7500.25</v>
       </c>
       <c r="F7" t="n">
-        <v>-21.5</v>
+        <v>98.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0133</v>
       </c>
       <c r="H7" t="n">
-        <v>102.25</v>
+        <v>107</v>
       </c>
       <c r="I7" t="n">
-        <v>7285</v>
+        <v>7255</v>
       </c>
       <c r="J7" t="n">
-        <v>7307.75</v>
+        <v>7296.19</v>
       </c>
       <c r="K7" t="n">
-        <v>7370.5</v>
+        <v>7350.62</v>
       </c>
       <c r="L7" t="n">
-        <v>7433.25</v>
+        <v>7405.06</v>
       </c>
       <c r="M7" t="n">
-        <v>7476</v>
+        <v>7452.88</v>
       </c>
       <c r="N7" t="n">
-        <v>7518.75</v>
+        <v>7500.69</v>
       </c>
       <c r="O7" t="n">
-        <v>7601.5</v>
+        <v>7561.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1100,22 +1096,24 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1124,55 +1122,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7398</v>
+        <v>7495.5</v>
       </c>
       <c r="C8" t="n">
-        <v>7505</v>
+        <v>7567.75</v>
       </c>
       <c r="D8" t="n">
-        <v>7398</v>
+        <v>7481.75</v>
       </c>
       <c r="E8" t="n">
-        <v>7500.25</v>
+        <v>7548.25</v>
       </c>
       <c r="F8" t="n">
-        <v>98.5</v>
+        <v>48</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0064</v>
       </c>
       <c r="H8" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="I8" t="n">
-        <v>7255</v>
+        <v>7291</v>
       </c>
       <c r="J8" t="n">
-        <v>7296.19</v>
+        <v>7417.62</v>
       </c>
       <c r="K8" t="n">
-        <v>7350.62</v>
+        <v>7446.75</v>
       </c>
       <c r="L8" t="n">
-        <v>7405.06</v>
+        <v>7475.88</v>
       </c>
       <c r="M8" t="n">
-        <v>7452.88</v>
+        <v>7553.75</v>
       </c>
       <c r="N8" t="n">
-        <v>7500.69</v>
+        <v>7631.62</v>
       </c>
       <c r="O8" t="n">
-        <v>7561.75</v>
+        <v>7612</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1190,13 +1192,11 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1215,50 +1215,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7495.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C9" t="n">
-        <v>7567.75</v>
+        <v>7579</v>
       </c>
       <c r="D9" t="n">
-        <v>7481.75</v>
+        <v>7505.75</v>
       </c>
       <c r="E9" t="n">
-        <v>7548.25</v>
+        <v>7543.5</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>-4.75</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0064</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>86</v>
+        <v>73.25</v>
       </c>
       <c r="I9" t="n">
-        <v>7291</v>
+        <v>7395.75</v>
       </c>
       <c r="J9" t="n">
-        <v>7417.62</v>
+        <v>7474</v>
       </c>
       <c r="K9" t="n">
-        <v>7446.75</v>
+        <v>7505.25</v>
       </c>
       <c r="L9" t="n">
-        <v>7475.88</v>
+        <v>7536.5</v>
       </c>
       <c r="M9" t="n">
-        <v>7553.75</v>
+        <v>7591.25</v>
       </c>
       <c r="N9" t="n">
-        <v>7631.62</v>
+        <v>7646</v>
       </c>
       <c r="O9" t="n">
-        <v>7612</v>
+        <v>7653.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,13 +1271,11 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1292,57 +1290,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7543.25</v>
+        <v>7536</v>
       </c>
       <c r="C10" t="n">
-        <v>7579</v>
+        <v>7593.75</v>
       </c>
       <c r="D10" t="n">
-        <v>7505.75</v>
+        <v>7479.5</v>
       </c>
       <c r="E10" t="n">
-        <v>7543.5</v>
+        <v>7528.25</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.75</v>
+        <v>-15.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>73.25</v>
+        <v>114.25</v>
       </c>
       <c r="I10" t="n">
-        <v>7395.75</v>
+        <v>7432.5</v>
       </c>
       <c r="J10" t="n">
-        <v>7474</v>
+        <v>7470.81</v>
       </c>
       <c r="K10" t="n">
-        <v>7505.25</v>
+        <v>7506.88</v>
       </c>
       <c r="L10" t="n">
-        <v>7536.5</v>
+        <v>7542.94</v>
       </c>
       <c r="M10" t="n">
-        <v>7591.25</v>
+        <v>7580.12</v>
       </c>
       <c r="N10" t="n">
-        <v>7646</v>
+        <v>7617.31</v>
       </c>
       <c r="O10" t="n">
-        <v>7653.75</v>
+        <v>7652.25</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1350,16 +1348,20 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1374,57 +1376,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C11" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D11" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E11" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I11" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J11" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K11" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L11" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M11" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N11" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O11" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1432,19 +1434,17 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U11" s="8" t="n">
@@ -1460,77 +1460,79 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C12" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D12" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E12" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F12" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H12" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I12" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J12" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K12" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L12" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M12" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N12" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O12" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1542,59 +1544,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C13" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D13" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E13" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F13" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I13" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J13" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K13" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L13" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M13" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N13" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O13" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1633,72 +1631,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C14" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D14" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E14" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F14" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H14" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I14" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J14" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K14" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L14" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M14" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N14" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O14" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1710,55 +1706,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C15" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D15" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E15" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H15" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I15" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J15" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K15" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L15" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M15" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N15" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O15" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1799,70 +1799,72 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C16" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D16" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E16" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F16" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H16" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I16" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J16" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K16" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L16" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M16" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N16" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O16" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1874,81 +1876,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C17" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D17" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E17" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F17" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H17" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I17" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J17" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K17" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L17" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M17" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N17" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O17" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1960,55 +1956,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C18" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D18" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E18" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F18" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H18" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I18" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J18" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K18" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L18" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M18" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N18" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O18" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2042,77 +2042,79 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C19" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D19" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E19" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F19" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H19" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I19" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J19" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K19" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L19" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M19" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N19" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O19" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2126,57 +2128,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C20" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D20" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E20" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F20" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H20" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I20" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J20" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K20" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L20" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M20" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N20" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O20" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2210,81 +2212,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C21" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D21" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E21" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F21" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H21" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I21" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J21" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K21" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L21" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M21" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N21" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O21" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2296,55 +2292,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C22" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D22" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E22" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I22" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J22" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K22" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L22" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M22" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N22" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O22" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,9 +2355,9 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2365,15 +2365,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -2385,50 +2387,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C23" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D23" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E23" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F23" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H23" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I23" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J23" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K23" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L23" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M23" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N23" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O23" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2436,23 +2438,21 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2471,65 +2471,69 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C24" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D24" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E24" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H24" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I24" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J24" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K24" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L24" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M24" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N24" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O24" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2541,83 +2545,73 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C25" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D25" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E25" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F25" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H25" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I25" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J25" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K25" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L25" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M25" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N25" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O25" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7687.25</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2634,55 +2628,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C26" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D26" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E26" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H26" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I26" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J26" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K26" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L26" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M26" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N26" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O26" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2698,11 +2696,15 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2721,50 +2723,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C27" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D27" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E27" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F27" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H27" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I27" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J27" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K27" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L27" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M27" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N27" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O27" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2775,20 +2777,16 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2807,67 +2805,75 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C28" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D28" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E28" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F28" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H28" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I28" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J28" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K28" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L28" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M28" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N28" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O28" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2882,86 +2888,82 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C29" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D29" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E29" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F29" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H29" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I29" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J29" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K29" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L29" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M29" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N29" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O29" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
@@ -2972,57 +2974,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C30" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D30" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E30" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F30" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H30" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I30" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J30" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K30" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L30" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M30" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N30" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O30" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3040,14 +3042,12 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3058,57 +3058,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C31" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D31" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E31" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F31" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H31" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I31" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J31" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K31" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L31" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M31" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N31" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O31" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3126,11 +3126,13 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3149,50 +3151,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C32" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D32" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E32" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F32" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H32" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I32" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J32" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K32" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L32" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M32" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N32" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O32" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3218,67 +3220,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C33" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D33" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E33" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F33" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H33" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I33" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J33" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K33" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L33" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M33" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N33" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O33" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,78 +3291,76 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C34" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D34" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E34" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F34" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H34" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I34" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J34" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K34" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L34" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M34" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N34" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O34" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3370,12 +3368,14 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3394,57 +3394,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C35" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D35" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E35" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F35" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H35" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I35" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J35" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K35" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L35" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M35" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N35" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O35" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3452,22 +3452,24 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3476,59 +3478,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C36" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D36" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E36" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F36" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H36" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I36" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J36" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K36" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L36" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M36" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N36" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O36" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3541,18 +3539,14 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3562,72 +3556,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C37" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D37" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E37" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F37" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H37" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I37" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J37" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K37" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L37" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M37" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N37" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O37" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3642,81 +3646,77 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C38" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D38" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E38" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F38" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H38" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I38" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J38" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K38" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L38" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M38" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N38" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O38" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3730,57 +3730,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C39" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D39" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E39" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F39" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H39" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I39" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J39" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K39" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L39" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M39" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N39" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O39" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3798,12 +3798,14 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3812,59 +3814,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C40" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D40" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E40" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F40" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H40" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I40" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J40" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K40" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L40" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M40" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N40" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O40" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3875,20 +3873,16 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3898,72 +3892,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C41" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D41" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E41" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F41" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H41" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I41" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J41" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K41" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L41" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M41" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N41" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O41" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3978,66 +3982,66 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C42" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D42" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E42" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F42" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H42" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I42" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J42" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K42" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L42" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M42" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N42" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O42" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -4048,10 +4052,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4073,74 +4075,74 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C43" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D43" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E43" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F43" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H43" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I43" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J43" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K43" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L43" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M43" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N43" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O43" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
       </c>
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4152,81 +4154,81 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C44" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D44" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E44" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F44" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H44" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I44" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J44" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K44" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L44" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M44" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N44" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O44" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4238,79 +4240,77 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C45" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D45" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E45" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F45" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H45" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I45" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J45" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K45" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L45" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M45" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N45" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O45" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4324,57 +4324,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C46" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D46" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E46" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F46" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H46" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I46" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J46" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K46" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L46" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M46" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N46" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O46" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4382,18 +4382,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4408,57 +4408,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C47" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D47" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E47" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F47" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H47" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I47" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J47" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K47" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L47" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M47" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N47" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O47" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4466,21 +4466,23 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4490,59 +4492,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C48" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D48" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E48" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F48" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H48" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I48" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J48" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K48" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L48" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M48" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N48" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O48" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4555,18 +4553,14 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4576,55 +4570,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C49" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D49" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E49" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H49" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I49" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J49" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K49" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L49" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M49" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N49" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O49" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4637,76 +4635,78 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C50" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D50" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E50" t="n">
         <v>7722</v>
       </c>
-      <c r="C50" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D50" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E50" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F50" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H50" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I50" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J50" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K50" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L50" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M50" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N50" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O50" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4714,12 +4714,14 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
@@ -4727,70 +4729,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C51" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D51" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E51" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F51" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H51" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I51" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J51" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K51" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L51" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M51" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N51" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O51" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4808,10 +4810,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4826,67 +4826,71 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C52" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D52" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E52" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F52" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H52" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I52" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J52" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K52" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L52" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M52" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N52" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O52" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
@@ -4903,88 +4907,80 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C53" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D53" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E53" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H53" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I53" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J53" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K53" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L53" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M53" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N53" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O53" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4996,55 +4992,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C54" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E54" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F54" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H54" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I54" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J54" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K54" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L54" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M54" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N54" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O54" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5062,14 +5062,18 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
@@ -5078,57 +5082,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C55" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D55" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E55" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F55" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H55" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I55" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J55" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K55" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L55" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M55" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N55" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O55" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5139,25 +5143,19 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
@@ -5166,57 +5164,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C56" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D56" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E56" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H56" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I56" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J56" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K56" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L56" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M56" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N56" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O56" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5224,12 +5222,14 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5246,59 +5246,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C57" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D57" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E57" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F57" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H57" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I57" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J57" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K57" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L57" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M57" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N57" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O57" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5335,50 +5331,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C58" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D58" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E58" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H58" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I58" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J58" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K58" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L58" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M58" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N58" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O58" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5415,50 +5411,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C59" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D59" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E59" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H59" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I59" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J59" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K59" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L59" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M59" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N59" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O59" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5466,22 +5462,24 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
@@ -5490,55 +5488,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C60" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D60" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E60" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F60" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H60" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I60" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J60" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K60" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L60" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M60" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N60" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O60" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5546,24 +5548,22 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
@@ -5572,59 +5572,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7609.25</v>
+        <v>7699.25</v>
       </c>
       <c r="C61" t="n">
-        <v>7652</v>
+        <v>7701</v>
       </c>
       <c r="D61" t="n">
-        <v>7593.75</v>
+        <v>7643.5</v>
       </c>
       <c r="E61" t="n">
-        <v>7625</v>
+        <v>7663.75</v>
       </c>
       <c r="F61" t="n">
-        <v>-34.5</v>
+        <v>38.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0045</v>
+        <v>0.0051</v>
       </c>
       <c r="H61" t="n">
-        <v>58.25</v>
+        <v>57.5</v>
       </c>
       <c r="I61" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J61" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K61" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L61" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M61" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N61" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O61" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5632,21 +5628,23 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5656,7 +5654,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5665,25 +5667,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>7535.5</v>
+        <v>7586</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>7567.81</v>
+        <v>7602</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>7595.88</v>
+        <v>7635</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>7623.94</v>
+        <v>7668</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>7654.12</v>
+        <v>7692.5</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>7684.31</v>
+        <v>7717</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>7710.25</v>
+        <v>7758.5</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5581,25 +5581,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7699.25</v>
+        <v>7663.25</v>
       </c>
       <c r="C61" t="n">
-        <v>7701</v>
+        <v>7667.75</v>
       </c>
       <c r="D61" t="n">
-        <v>7643.5</v>
+        <v>7660</v>
       </c>
       <c r="E61" t="n">
-        <v>7663.75</v>
+        <v>7662.25</v>
       </c>
       <c r="F61" t="n">
-        <v>38.75</v>
+        <v>37.25</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0049</v>
       </c>
       <c r="H61" t="n">
-        <v>57.5</v>
+        <v>7.75</v>
       </c>
       <c r="I61" t="n">
         <v>7535.5</v>
@@ -5641,10 +5641,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5667,25 +5665,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>7586</v>
+        <v>7652.25</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>7602</v>
+        <v>7653.69</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>7635</v>
+        <v>7658.38</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>7668</v>
+        <v>7663.06</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>7692.5</v>
+        <v>7666.12</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>7717</v>
+        <v>7669.19</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>7758.5</v>
+        <v>7675.5</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5581,25 +5581,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7663.25</v>
+        <v>7631</v>
       </c>
       <c r="C61" t="n">
-        <v>7667.75</v>
+        <v>7633.25</v>
       </c>
       <c r="D61" t="n">
-        <v>7660</v>
+        <v>7576.75</v>
       </c>
       <c r="E61" t="n">
-        <v>7662.25</v>
+        <v>7589.25</v>
       </c>
       <c r="F61" t="n">
-        <v>37.25</v>
+        <v>-35.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.0047</v>
       </c>
       <c r="H61" t="n">
-        <v>7.75</v>
+        <v>56.5</v>
       </c>
       <c r="I61" t="n">
         <v>7535.5</v>
@@ -5628,62 +5628,142 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>7663.25</v>
+      </c>
+      <c r="C62" t="n">
+        <v>7678</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7658.75</v>
+      </c>
+      <c r="E62" t="n">
+        <v>7670.5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="H62" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="I62" t="n">
+        <v>7520.25</v>
+      </c>
+      <c r="J62" t="n">
+        <v>7524.88</v>
+      </c>
+      <c r="K62" t="n">
+        <v>7561</v>
+      </c>
+      <c r="L62" t="n">
+        <v>7597.12</v>
+      </c>
+      <c r="M62" t="n">
+        <v>7617.5</v>
+      </c>
+      <c r="N62" t="n">
+        <v>7637.88</v>
+      </c>
+      <c r="O62" t="n">
+        <v>7689.75</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>7652.25</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>7653.69</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>7658.38</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>7663.06</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>7666.12</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>7669.19</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>7675.5</v>
+      <c r="I63" s="13" t="n">
+        <v>7639.5</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>7652.31</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>7660.88</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>7669.44</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>7680.12</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>7690.81</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>7697.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5664,22 +5664,22 @@
         <v>7663.25</v>
       </c>
       <c r="C62" t="n">
-        <v>7678</v>
+        <v>7681.5</v>
       </c>
       <c r="D62" t="n">
         <v>7658.75</v>
       </c>
       <c r="E62" t="n">
-        <v>7670.5</v>
+        <v>7675.75</v>
       </c>
       <c r="F62" t="n">
-        <v>81.25</v>
+        <v>86.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0114</v>
       </c>
       <c r="H62" t="n">
-        <v>19.25</v>
+        <v>22.75</v>
       </c>
       <c r="I62" t="n">
         <v>7520.25</v>
@@ -5745,25 +5745,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>7639.5</v>
+        <v>7636</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>7652.31</v>
+        <v>7655.81</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>7660.88</v>
+        <v>7664.38</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>7669.44</v>
+        <v>7672.94</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>7680.12</v>
+        <v>7687.12</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>7690.81</v>
+        <v>7701.31</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>7697.25</v>
+        <v>7704.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5664,22 +5664,22 @@
         <v>7663.25</v>
       </c>
       <c r="C62" t="n">
-        <v>7681.5</v>
+        <v>7683.5</v>
       </c>
       <c r="D62" t="n">
         <v>7658.75</v>
       </c>
       <c r="E62" t="n">
-        <v>7675.75</v>
+        <v>7683.25</v>
       </c>
       <c r="F62" t="n">
-        <v>86.5</v>
+        <v>94</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0114</v>
+        <v>0.0124</v>
       </c>
       <c r="H62" t="n">
-        <v>22.75</v>
+        <v>24.75</v>
       </c>
       <c r="I62" t="n">
         <v>7520.25</v>
@@ -5745,25 +5745,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>7636</v>
+        <v>7634</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>7655.81</v>
+        <v>7664.56</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>7664.38</v>
+        <v>7670.88</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>7672.94</v>
+        <v>7677.19</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>7687.12</v>
+        <v>7695.62</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>7701.31</v>
+        <v>7714.06</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>7704.25</v>
+        <v>7708.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5664,22 +5664,22 @@
         <v>7663.25</v>
       </c>
       <c r="C62" t="n">
-        <v>7683.5</v>
+        <v>7689.25</v>
       </c>
       <c r="D62" t="n">
         <v>7658.75</v>
       </c>
       <c r="E62" t="n">
-        <v>7683.25</v>
+        <v>7685.5</v>
       </c>
       <c r="F62" t="n">
-        <v>94</v>
+        <v>96.25</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0124</v>
+        <v>0.0127</v>
       </c>
       <c r="H62" t="n">
-        <v>24.75</v>
+        <v>30.5</v>
       </c>
       <c r="I62" t="n">
         <v>7520.25</v>
@@ -5745,25 +5745,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>7634</v>
+        <v>7628.25</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>7664.56</v>
+        <v>7660.75</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>7670.88</v>
+        <v>7670.25</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>7677.19</v>
+        <v>7679.75</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>7695.62</v>
+        <v>7700.75</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>7714.06</v>
+        <v>7721.75</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>7708.25</v>
+        <v>7719.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -109,17 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,81 +641,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7543.25</v>
+        <v>7541.25</v>
       </c>
       <c r="C2" t="n">
-        <v>7599.25</v>
+        <v>7549.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7513</v>
+        <v>7415.25</v>
       </c>
       <c r="E2" t="n">
-        <v>7541.25</v>
+        <v>7437.5</v>
       </c>
       <c r="F2" t="n">
-        <v>32.82</v>
+        <v>-103.75</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0138</v>
       </c>
       <c r="H2" t="n">
-        <v>86.25</v>
+        <v>134.25</v>
       </c>
       <c r="I2" t="n">
-        <v>7358</v>
+        <v>7426.75</v>
       </c>
       <c r="J2" t="n">
-        <v>7446.71</v>
+        <v>7447.56</v>
       </c>
       <c r="K2" t="n">
-        <v>7469.31</v>
+        <v>7498.12</v>
       </c>
       <c r="L2" t="n">
-        <v>7491.9</v>
+        <v>7548.69</v>
       </c>
       <c r="M2" t="n">
-        <v>7547.56</v>
+        <v>7584.38</v>
       </c>
       <c r="N2" t="n">
-        <v>7603.21</v>
+        <v>7620.06</v>
       </c>
       <c r="O2" t="n">
-        <v>7592.75</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>7685.5</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -723,69 +725,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7541.25</v>
+        <v>7449.25</v>
       </c>
       <c r="C3" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D3" t="n">
-        <v>7415.25</v>
+        <v>7404.25</v>
       </c>
       <c r="E3" t="n">
-        <v>7437.5</v>
+        <v>7428.25</v>
       </c>
       <c r="F3" t="n">
-        <v>-103.75</v>
+        <v>-9.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.0012</v>
       </c>
       <c r="H3" t="n">
-        <v>134.25</v>
+        <v>92.25</v>
       </c>
       <c r="I3" t="n">
-        <v>7426.75</v>
+        <v>7281</v>
       </c>
       <c r="J3" t="n">
-        <v>7447.56</v>
+        <v>7280.81</v>
       </c>
       <c r="K3" t="n">
-        <v>7498.12</v>
+        <v>7370.38</v>
       </c>
       <c r="L3" t="n">
-        <v>7548.69</v>
+        <v>7459.94</v>
       </c>
       <c r="M3" t="n">
-        <v>7584.38</v>
+        <v>7504.62</v>
       </c>
       <c r="N3" t="n">
-        <v>7620.06</v>
+        <v>7549.31</v>
       </c>
       <c r="O3" t="n">
-        <v>7685.5</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>7683.75</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -797,7 +793,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -807,50 +803,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7449.25</v>
+        <v>7476.25</v>
       </c>
       <c r="C4" t="n">
-        <v>7496.5</v>
+        <v>7496</v>
       </c>
       <c r="D4" t="n">
-        <v>7404.25</v>
+        <v>7390.5</v>
       </c>
       <c r="E4" t="n">
-        <v>7428.25</v>
+        <v>7423.25</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.25</v>
+        <v>-5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.0007</v>
       </c>
       <c r="H4" t="n">
-        <v>92.25</v>
+        <v>105.5</v>
       </c>
       <c r="I4" t="n">
-        <v>7281</v>
+        <v>7312</v>
       </c>
       <c r="J4" t="n">
-        <v>7280.81</v>
+        <v>7324.94</v>
       </c>
       <c r="K4" t="n">
-        <v>7370.38</v>
+        <v>7382.12</v>
       </c>
       <c r="L4" t="n">
-        <v>7459.94</v>
+        <v>7439.31</v>
       </c>
       <c r="M4" t="n">
-        <v>7504.62</v>
+        <v>7474.38</v>
       </c>
       <c r="N4" t="n">
-        <v>7549.31</v>
+        <v>7509.44</v>
       </c>
       <c r="O4" t="n">
-        <v>7683.75</v>
+        <v>7588.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -861,13 +857,15 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -875,7 +873,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -885,50 +883,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7476.25</v>
+        <v>7431</v>
       </c>
       <c r="C5" t="n">
-        <v>7496</v>
+        <v>7459.5</v>
       </c>
       <c r="D5" t="n">
-        <v>7390.5</v>
+        <v>7357.25</v>
       </c>
       <c r="E5" t="n">
-        <v>7423.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F5" t="n">
-        <v>-5</v>
+        <v>-21.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0029</v>
       </c>
       <c r="H5" t="n">
-        <v>105.5</v>
+        <v>102.25</v>
       </c>
       <c r="I5" t="n">
-        <v>7312</v>
+        <v>7285</v>
       </c>
       <c r="J5" t="n">
-        <v>7324.94</v>
+        <v>7307.75</v>
       </c>
       <c r="K5" t="n">
-        <v>7382.12</v>
+        <v>7370.5</v>
       </c>
       <c r="L5" t="n">
-        <v>7439.31</v>
+        <v>7433.25</v>
       </c>
       <c r="M5" t="n">
-        <v>7474.38</v>
+        <v>7476</v>
       </c>
       <c r="N5" t="n">
-        <v>7509.44</v>
+        <v>7518.75</v>
       </c>
       <c r="O5" t="n">
-        <v>7588.75</v>
+        <v>7601.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -936,18 +934,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -955,7 +953,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -965,50 +963,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7431</v>
+        <v>7398</v>
       </c>
       <c r="C6" t="n">
-        <v>7459.5</v>
+        <v>7505</v>
       </c>
       <c r="D6" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E6" t="n">
-        <v>7401.75</v>
+        <v>7500.25</v>
       </c>
       <c r="F6" t="n">
-        <v>-21.5</v>
+        <v>98.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0133</v>
       </c>
       <c r="H6" t="n">
-        <v>102.25</v>
+        <v>107</v>
       </c>
       <c r="I6" t="n">
-        <v>7285</v>
+        <v>7255</v>
       </c>
       <c r="J6" t="n">
-        <v>7307.75</v>
+        <v>7296.19</v>
       </c>
       <c r="K6" t="n">
-        <v>7370.5</v>
+        <v>7350.62</v>
       </c>
       <c r="L6" t="n">
-        <v>7433.25</v>
+        <v>7405.06</v>
       </c>
       <c r="M6" t="n">
-        <v>7476</v>
+        <v>7452.88</v>
       </c>
       <c r="N6" t="n">
-        <v>7518.75</v>
+        <v>7500.69</v>
       </c>
       <c r="O6" t="n">
-        <v>7601.5</v>
+        <v>7561.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1016,79 +1014,85 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7398</v>
+        <v>7495.5</v>
       </c>
       <c r="C7" t="n">
-        <v>7505</v>
+        <v>7567.75</v>
       </c>
       <c r="D7" t="n">
-        <v>7398</v>
+        <v>7481.75</v>
       </c>
       <c r="E7" t="n">
-        <v>7500.25</v>
+        <v>7548.25</v>
       </c>
       <c r="F7" t="n">
-        <v>98.5</v>
+        <v>48</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0064</v>
       </c>
       <c r="H7" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="I7" t="n">
-        <v>7255</v>
+        <v>7291</v>
       </c>
       <c r="J7" t="n">
-        <v>7296.19</v>
+        <v>7417.62</v>
       </c>
       <c r="K7" t="n">
-        <v>7350.62</v>
+        <v>7446.75</v>
       </c>
       <c r="L7" t="n">
-        <v>7405.06</v>
+        <v>7475.88</v>
       </c>
       <c r="M7" t="n">
-        <v>7452.88</v>
+        <v>7553.75</v>
       </c>
       <c r="N7" t="n">
-        <v>7500.69</v>
+        <v>7631.62</v>
       </c>
       <c r="O7" t="n">
-        <v>7561.75</v>
+        <v>7612</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1099,25 +1103,23 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1131,50 +1133,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7495.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C8" t="n">
-        <v>7567.75</v>
+        <v>7579</v>
       </c>
       <c r="D8" t="n">
-        <v>7481.75</v>
+        <v>7505.75</v>
       </c>
       <c r="E8" t="n">
-        <v>7548.25</v>
+        <v>7543.5</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>-4.75</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0064</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>86</v>
+        <v>73.25</v>
       </c>
       <c r="I8" t="n">
-        <v>7291</v>
+        <v>7395.75</v>
       </c>
       <c r="J8" t="n">
-        <v>7417.62</v>
+        <v>7474</v>
       </c>
       <c r="K8" t="n">
-        <v>7446.75</v>
+        <v>7505.25</v>
       </c>
       <c r="L8" t="n">
-        <v>7475.88</v>
+        <v>7536.5</v>
       </c>
       <c r="M8" t="n">
-        <v>7553.75</v>
+        <v>7591.25</v>
       </c>
       <c r="N8" t="n">
-        <v>7631.62</v>
+        <v>7646</v>
       </c>
       <c r="O8" t="n">
-        <v>7612</v>
+        <v>7653.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,15 +1187,13 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1201,64 +1201,64 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7543.25</v>
+        <v>7536</v>
       </c>
       <c r="C9" t="n">
-        <v>7579</v>
+        <v>7593.75</v>
       </c>
       <c r="D9" t="n">
-        <v>7505.75</v>
+        <v>7479.5</v>
       </c>
       <c r="E9" t="n">
-        <v>7543.5</v>
+        <v>7528.25</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.75</v>
+        <v>-15.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>73.25</v>
+        <v>114.25</v>
       </c>
       <c r="I9" t="n">
-        <v>7395.75</v>
+        <v>7432.5</v>
       </c>
       <c r="J9" t="n">
-        <v>7474</v>
+        <v>7470.81</v>
       </c>
       <c r="K9" t="n">
-        <v>7505.25</v>
+        <v>7506.88</v>
       </c>
       <c r="L9" t="n">
-        <v>7536.5</v>
+        <v>7542.94</v>
       </c>
       <c r="M9" t="n">
-        <v>7591.25</v>
+        <v>7580.12</v>
       </c>
       <c r="N9" t="n">
-        <v>7646</v>
+        <v>7617.31</v>
       </c>
       <c r="O9" t="n">
-        <v>7653.75</v>
+        <v>7652.25</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1266,16 +1266,20 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1283,64 +1287,64 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C10" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D10" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E10" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I10" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J10" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K10" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L10" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M10" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N10" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O10" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1348,19 +1352,17 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U10" s="8" t="n">
@@ -1369,83 +1371,85 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C11" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D11" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E11" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F11" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H11" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I11" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J11" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K11" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L11" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M11" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N11" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O11" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1453,64 +1457,60 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C12" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D12" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E12" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F12" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H12" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I12" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J12" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K12" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L12" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M12" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N12" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O12" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,7 +1525,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1539,7 +1539,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1549,132 +1549,134 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C13" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D13" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E13" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F13" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H13" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I13" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J13" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K13" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L13" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M13" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N13" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O13" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C14" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D14" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E14" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H14" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I14" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J14" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K14" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L14" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M14" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N14" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O14" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1685,7 +1687,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1701,7 +1703,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1715,69 +1717,71 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C15" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D15" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E15" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F15" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I15" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J15" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K15" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L15" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M15" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N15" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O15" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1785,146 +1789,144 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C16" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D16" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E16" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H16" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I16" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J16" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K16" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L16" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M16" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N16" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O16" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C17" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D17" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E17" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F17" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H17" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I17" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J17" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K17" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L17" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M17" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N17" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O17" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1935,7 +1937,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1951,83 +1953,85 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C18" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D18" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E18" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F18" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H18" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I18" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J18" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K18" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L18" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M18" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N18" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O18" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2035,64 +2039,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C19" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D19" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E19" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H19" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I19" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J19" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K19" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L19" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M19" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N19" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O19" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2107,7 +2111,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2121,146 +2125,144 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C20" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D20" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E20" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F20" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H20" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I20" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J20" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K20" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L20" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M20" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N20" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O20" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C21" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D21" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E21" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F21" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I21" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J21" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K21" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L21" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M21" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N21" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O21" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,7 +2275,7 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2281,15 +2283,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2301,50 +2305,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C22" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D22" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E22" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F22" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H22" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I22" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J22" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K22" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L22" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M22" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N22" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O22" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2352,28 +2356,26 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2387,56 +2389,60 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C23" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D23" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E23" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H23" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I23" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J23" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K23" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L23" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M23" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N23" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O23" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
@@ -2445,7 +2451,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2459,81 +2465,71 @@
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C24" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D24" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E24" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F24" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H24" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I24" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J24" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K24" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L24" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M24" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N24" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O24" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>7687.25</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2545,60 +2541,64 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C25" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D25" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E25" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H25" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I25" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J25" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K25" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L25" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M25" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N25" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O25" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2609,21 +2609,25 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2637,50 +2641,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C26" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D26" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E26" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F26" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H26" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I26" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J26" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K26" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L26" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M26" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N26" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O26" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2693,23 +2697,19 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2723,67 +2723,75 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C27" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D27" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E27" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H27" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I27" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J27" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K27" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L27" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M27" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N27" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O27" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2791,154 +2799,150 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C28" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D28" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E28" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F28" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H28" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I28" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J28" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K28" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L28" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M28" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N28" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O28" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C29" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D29" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E29" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F29" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H29" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I29" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J29" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K29" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L29" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M29" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N29" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O29" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2949,82 +2953,80 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C30" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D30" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E30" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F30" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H30" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I30" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J30" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K30" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L30" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M30" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N30" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O30" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3035,23 +3037,25 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3065,50 +3069,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C31" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D31" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E31" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F31" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H31" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I31" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J31" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K31" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L31" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M31" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N31" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O31" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3119,7 +3123,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3134,67 +3138,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V31" s="8" t="n">
-        <v/>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C32" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D32" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E32" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F32" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H32" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I32" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J32" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K32" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L32" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M32" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N32" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O32" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3205,80 +3207,78 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C33" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D33" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E33" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F33" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H33" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I33" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J33" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K33" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L33" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M33" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N33" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O33" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3286,12 +3286,14 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3303,64 +3305,64 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C34" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D34" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E34" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F34" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H34" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I34" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J34" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K34" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L34" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M34" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N34" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O34" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3368,83 +3370,81 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C35" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D35" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E35" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F35" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H35" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I35" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J35" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K35" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L35" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M35" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N35" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O35" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3455,95 +3455,101 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C36" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D36" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E36" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F36" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H36" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I36" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J36" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K36" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L36" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M36" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N36" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O36" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3551,152 +3557,148 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C37" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D37" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E37" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F37" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H37" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I37" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J37" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K37" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L37" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M37" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N37" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O37" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C38" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D38" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E38" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F38" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H38" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I38" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J38" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K38" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L38" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M38" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N38" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O38" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3707,80 +3709,78 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C39" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D39" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E39" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F39" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H39" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I39" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J39" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K39" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L39" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M39" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N39" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O39" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3793,93 +3793,99 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C40" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D40" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E40" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F40" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H40" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I40" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J40" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K40" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L40" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M40" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N40" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O40" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3887,87 +3893,85 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C41" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D41" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E41" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F41" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H41" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I41" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J41" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K41" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L41" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M41" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N41" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O41" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3975,7 +3979,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3989,308 +3993,306 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C42" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D42" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E42" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F42" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H42" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I42" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J42" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K42" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L42" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M42" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N42" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O42" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
       </c>
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C43" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D43" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E43" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F43" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H43" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I43" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J43" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K43" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L43" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M43" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N43" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O43" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C44" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D44" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E44" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F44" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H44" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I44" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J44" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K44" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L44" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M44" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N44" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O44" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C45" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D45" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E45" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F45" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H45" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I45" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J45" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K45" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L45" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M45" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N45" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O45" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4298,18 +4300,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4317,64 +4319,64 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C46" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D46" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E46" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F46" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H46" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I46" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J46" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K46" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L46" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M46" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N46" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O46" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4382,83 +4384,81 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C47" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D47" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E47" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F47" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H47" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I47" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J47" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K47" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L47" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M47" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N47" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O47" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4469,78 +4469,78 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C48" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D48" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E48" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H48" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I48" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J48" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K48" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L48" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M48" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N48" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O48" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4551,78 +4551,80 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D49" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E49" t="n">
         <v>7722</v>
       </c>
-      <c r="C49" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D49" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E49" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F49" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H49" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I49" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J49" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K49" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L49" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M49" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N49" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O49" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4630,12 +4632,14 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4643,70 +4647,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C50" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D50" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E50" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F50" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H50" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I50" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J50" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K50" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L50" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M50" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N50" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O50" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4719,15 +4723,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4735,77 +4737,81 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C51" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D51" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E51" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F51" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H51" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I51" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J51" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K51" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L51" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M51" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N51" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O51" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4821,146 +4827,142 @@
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C52" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D52" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E52" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H52" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I52" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J52" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K52" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L52" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M52" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N52" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O52" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C53" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D53" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E53" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F53" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H53" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I53" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J53" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K53" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L53" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M53" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N53" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O53" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4971,80 +4973,84 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C54" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E54" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F54" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H54" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I54" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J54" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K54" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L54" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M54" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N54" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O54" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5057,82 +5063,76 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C55" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D55" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E55" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H55" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I55" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J55" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K55" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L55" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M55" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N55" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O55" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5140,12 +5140,14 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5157,64 +5159,60 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C56" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D56" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E56" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F56" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H56" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I56" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J56" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K56" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L56" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M56" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N56" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O56" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5227,7 +5225,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5241,7 +5239,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5251,50 +5249,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C57" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D57" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E57" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H57" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I57" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J57" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K57" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L57" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M57" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N57" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O57" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5307,7 +5305,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5321,7 +5319,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5331,50 +5329,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C58" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D58" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H58" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I58" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J58" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K58" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L58" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M58" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N58" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O58" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5382,79 +5380,85 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C59" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D59" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E59" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F59" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H59" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I59" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J59" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K59" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L59" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M59" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N59" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O59" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5462,85 +5466,79 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C60" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D60" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E60" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F60" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H60" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I60" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J60" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K60" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L60" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M60" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N60" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O60" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5553,7 +5551,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5567,7 +5565,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5577,50 +5575,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7631</v>
+        <v>7624</v>
       </c>
       <c r="C61" t="n">
-        <v>7633.25</v>
+        <v>7625</v>
       </c>
       <c r="D61" t="n">
-        <v>7576.75</v>
+        <v>7617.5</v>
       </c>
       <c r="E61" t="n">
-        <v>7589.25</v>
+        <v>7620.25</v>
       </c>
       <c r="F61" t="n">
-        <v>-35.75</v>
+        <v>31</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.0041</v>
       </c>
       <c r="H61" t="n">
-        <v>56.5</v>
+        <v>7.5</v>
       </c>
       <c r="I61" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J61" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K61" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L61" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M61" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N61" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O61" t="n">
-        <v>7710.25</v>
+        <v>7689.75</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5628,142 +5626,62 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>7663.25</v>
-      </c>
-      <c r="C62" t="n">
-        <v>7689.25</v>
-      </c>
-      <c r="D62" t="n">
-        <v>7658.75</v>
-      </c>
-      <c r="E62" t="n">
-        <v>7685.5</v>
-      </c>
-      <c r="F62" t="n">
-        <v>96.25</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0127</v>
-      </c>
-      <c r="H62" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="I62" t="n">
-        <v>7520.25</v>
-      </c>
-      <c r="J62" t="n">
-        <v>7524.88</v>
-      </c>
-      <c r="K62" t="n">
-        <v>7561</v>
-      </c>
-      <c r="L62" t="n">
-        <v>7597.12</v>
-      </c>
-      <c r="M62" t="n">
-        <v>7617.5</v>
-      </c>
-      <c r="N62" t="n">
-        <v>7637.88</v>
-      </c>
-      <c r="O62" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>7628.25</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>7660.75</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>7670.25</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>7679.75</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>7700.75</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>7721.75</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>7719.75</v>
+      <c r="I62" s="13" t="n">
+        <v>7610</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>7612.25</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>7616.5</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>7620.75</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>7624</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>7627.25</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>7632.5</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5582,22 +5582,22 @@
         <v>7624</v>
       </c>
       <c r="C61" t="n">
-        <v>7625</v>
+        <v>7667.75</v>
       </c>
       <c r="D61" t="n">
         <v>7617.5</v>
       </c>
       <c r="E61" t="n">
-        <v>7620.25</v>
+        <v>7661.75</v>
       </c>
       <c r="F61" t="n">
-        <v>31</v>
+        <v>72.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>7.5</v>
+        <v>50.25</v>
       </c>
       <c r="I61" t="n">
         <v>7520.25</v>
@@ -5636,25 +5636,23 @@
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5663,25 +5661,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>7610</v>
+        <v>7567.25</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>7612.25</v>
+        <v>7621.06</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>7616.5</v>
+        <v>7636.62</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>7620.75</v>
+        <v>7652.19</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>7624</v>
+        <v>7686.88</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>7627.25</v>
+        <v>7721.56</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>7632.5</v>
+        <v>7718</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5579,25 +5579,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7624</v>
+        <v>7596.5</v>
       </c>
       <c r="C61" t="n">
-        <v>7667.75</v>
+        <v>7632</v>
       </c>
       <c r="D61" t="n">
-        <v>7617.5</v>
+        <v>7509.25</v>
       </c>
       <c r="E61" t="n">
-        <v>7661.75</v>
+        <v>7556.5</v>
       </c>
       <c r="F61" t="n">
-        <v>72.5</v>
+        <v>-32.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0043</v>
       </c>
       <c r="H61" t="n">
-        <v>50.25</v>
+        <v>122.75</v>
       </c>
       <c r="I61" t="n">
         <v>7520.25</v>
@@ -5620,66 +5620,152 @@
       <c r="O61" t="n">
         <v>7689.75</v>
       </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>7703.5</v>
+      </c>
+      <c r="C62" t="n">
+        <v>7704.25</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7701.25</v>
+      </c>
+      <c r="E62" t="n">
+        <v>7701.25</v>
+      </c>
+      <c r="F62" t="n">
+        <v>144.75</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>7386.5</v>
+      </c>
+      <c r="J62" t="n">
+        <v>7426.69</v>
+      </c>
+      <c r="K62" t="n">
+        <v>7495.12</v>
+      </c>
+      <c r="L62" t="n">
+        <v>7563.56</v>
+      </c>
+      <c r="M62" t="n">
+        <v>7617.88</v>
+      </c>
+      <c r="N62" t="n">
+        <v>7672.19</v>
+      </c>
+      <c r="O62" t="n">
+        <v>7754.75</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>7567.25</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>7621.06</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>7636.62</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>7652.19</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>7686.88</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>7721.56</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>7718</v>
+      <c r="I63" s="13" t="n">
+        <v>7698.25</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>7697.5</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>7699.75</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>7702</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>7702.75</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>7703.5</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>7707.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5671,19 +5671,19 @@
         <v>7704.25</v>
       </c>
       <c r="D62" t="n">
-        <v>7701.25</v>
+        <v>7697</v>
       </c>
       <c r="E62" t="n">
-        <v>7701.25</v>
+        <v>7700</v>
       </c>
       <c r="F62" t="n">
-        <v>144.75</v>
+        <v>143.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0192</v>
+        <v>0.019</v>
       </c>
       <c r="H62" t="n">
-        <v>3</v>
+        <v>7.25</v>
       </c>
       <c r="I62" t="n">
         <v>7386.5</v>
@@ -5747,25 +5747,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>7698.25</v>
+        <v>7689.75</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>7697.5</v>
+        <v>7692.44</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>7699.75</v>
+        <v>7696.38</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>7702</v>
+        <v>7700.31</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>7702.75</v>
+        <v>7703.62</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>7703.5</v>
+        <v>7706.94</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>7707.25</v>
+        <v>7711.5</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5674,13 +5667,13 @@
         <v>7697</v>
       </c>
       <c r="E62" t="n">
-        <v>7700</v>
+        <v>7700.5</v>
       </c>
       <c r="F62" t="n">
-        <v>143.5</v>
+        <v>144</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.019</v>
+        <v>0.0191</v>
       </c>
       <c r="H62" t="n">
         <v>7.25</v>
@@ -5739,34 +5732,6 @@
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>7692.44</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>7696.38</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>7700.31</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>7703.62</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>7706.94</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>7711.5</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,69 +634,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7541.25</v>
+        <v>7449.25</v>
       </c>
       <c r="C2" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7415.25</v>
+        <v>7404.25</v>
       </c>
       <c r="E2" t="n">
-        <v>7437.5</v>
+        <v>7428.25</v>
       </c>
       <c r="F2" t="n">
-        <v>-103.75</v>
+        <v>-9.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.0012</v>
       </c>
       <c r="H2" t="n">
-        <v>134.25</v>
+        <v>92.25</v>
       </c>
       <c r="I2" t="n">
-        <v>7426.75</v>
+        <v>7281</v>
       </c>
       <c r="J2" t="n">
-        <v>7447.56</v>
+        <v>7280.81</v>
       </c>
       <c r="K2" t="n">
-        <v>7498.12</v>
+        <v>7370.38</v>
       </c>
       <c r="L2" t="n">
-        <v>7548.69</v>
+        <v>7459.94</v>
       </c>
       <c r="M2" t="n">
-        <v>7584.38</v>
+        <v>7504.62</v>
       </c>
       <c r="N2" t="n">
-        <v>7620.06</v>
+        <v>7549.31</v>
       </c>
       <c r="O2" t="n">
-        <v>7685.5</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7683.75</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -710,58 +704,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7449.25</v>
+        <v>7476.25</v>
       </c>
       <c r="C3" t="n">
-        <v>7496.5</v>
+        <v>7496</v>
       </c>
       <c r="D3" t="n">
-        <v>7404.25</v>
+        <v>7390.5</v>
       </c>
       <c r="E3" t="n">
-        <v>7428.25</v>
+        <v>7423.25</v>
       </c>
       <c r="F3" t="n">
-        <v>-9.25</v>
+        <v>-5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.0007</v>
       </c>
       <c r="H3" t="n">
-        <v>92.25</v>
+        <v>105.5</v>
       </c>
       <c r="I3" t="n">
-        <v>7281</v>
+        <v>7312</v>
       </c>
       <c r="J3" t="n">
-        <v>7280.81</v>
+        <v>7324.94</v>
       </c>
       <c r="K3" t="n">
-        <v>7370.38</v>
+        <v>7382.12</v>
       </c>
       <c r="L3" t="n">
-        <v>7459.94</v>
+        <v>7439.31</v>
       </c>
       <c r="M3" t="n">
-        <v>7504.62</v>
+        <v>7474.38</v>
       </c>
       <c r="N3" t="n">
-        <v>7549.31</v>
+        <v>7509.44</v>
       </c>
       <c r="O3" t="n">
-        <v>7683.75</v>
+        <v>7588.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -777,8 +775,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -788,58 +788,62 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7476.25</v>
+        <v>7431</v>
       </c>
       <c r="C4" t="n">
-        <v>7496</v>
+        <v>7459.5</v>
       </c>
       <c r="D4" t="n">
-        <v>7390.5</v>
+        <v>7357.25</v>
       </c>
       <c r="E4" t="n">
-        <v>7423.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F4" t="n">
-        <v>-5</v>
+        <v>-21.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0029</v>
       </c>
       <c r="H4" t="n">
-        <v>105.5</v>
+        <v>102.25</v>
       </c>
       <c r="I4" t="n">
-        <v>7312</v>
+        <v>7285</v>
       </c>
       <c r="J4" t="n">
-        <v>7324.94</v>
+        <v>7307.75</v>
       </c>
       <c r="K4" t="n">
-        <v>7382.12</v>
+        <v>7370.5</v>
       </c>
       <c r="L4" t="n">
-        <v>7439.31</v>
+        <v>7433.25</v>
       </c>
       <c r="M4" t="n">
-        <v>7474.38</v>
+        <v>7476</v>
       </c>
       <c r="N4" t="n">
-        <v>7509.44</v>
+        <v>7518.75</v>
       </c>
       <c r="O4" t="n">
-        <v>7588.75</v>
+        <v>7601.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -847,18 +851,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -868,58 +872,62 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7431</v>
+        <v>7398</v>
       </c>
       <c r="C5" t="n">
-        <v>7459.5</v>
+        <v>7505</v>
       </c>
       <c r="D5" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E5" t="n">
-        <v>7401.75</v>
+        <v>7500.25</v>
       </c>
       <c r="F5" t="n">
-        <v>-21.5</v>
+        <v>98.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0133</v>
       </c>
       <c r="H5" t="n">
-        <v>102.25</v>
+        <v>107</v>
       </c>
       <c r="I5" t="n">
-        <v>7285</v>
+        <v>7255</v>
       </c>
       <c r="J5" t="n">
-        <v>7307.75</v>
+        <v>7296.19</v>
       </c>
       <c r="K5" t="n">
-        <v>7370.5</v>
+        <v>7350.62</v>
       </c>
       <c r="L5" t="n">
-        <v>7433.25</v>
+        <v>7405.06</v>
       </c>
       <c r="M5" t="n">
-        <v>7476</v>
+        <v>7452.88</v>
       </c>
       <c r="N5" t="n">
-        <v>7518.75</v>
+        <v>7500.69</v>
       </c>
       <c r="O5" t="n">
-        <v>7601.5</v>
+        <v>7561.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -927,28 +935,30 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -956,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7398</v>
+        <v>7495.5</v>
       </c>
       <c r="C6" t="n">
-        <v>7505</v>
+        <v>7567.75</v>
       </c>
       <c r="D6" t="n">
-        <v>7398</v>
+        <v>7481.75</v>
       </c>
       <c r="E6" t="n">
-        <v>7500.25</v>
+        <v>7548.25</v>
       </c>
       <c r="F6" t="n">
-        <v>98.5</v>
+        <v>48</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0064</v>
       </c>
       <c r="H6" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="I6" t="n">
-        <v>7255</v>
+        <v>7291</v>
       </c>
       <c r="J6" t="n">
-        <v>7296.19</v>
+        <v>7417.62</v>
       </c>
       <c r="K6" t="n">
-        <v>7350.62</v>
+        <v>7446.75</v>
       </c>
       <c r="L6" t="n">
-        <v>7405.06</v>
+        <v>7475.88</v>
       </c>
       <c r="M6" t="n">
-        <v>7452.88</v>
+        <v>7553.75</v>
       </c>
       <c r="N6" t="n">
-        <v>7500.69</v>
+        <v>7631.62</v>
       </c>
       <c r="O6" t="n">
-        <v>7561.75</v>
+        <v>7612</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,75 +1027,69 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7495.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C7" t="n">
-        <v>7567.75</v>
+        <v>7579</v>
       </c>
       <c r="D7" t="n">
-        <v>7481.75</v>
+        <v>7505.75</v>
       </c>
       <c r="E7" t="n">
-        <v>7548.25</v>
+        <v>7543.5</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>-4.75</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0064</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>86</v>
+        <v>73.25</v>
       </c>
       <c r="I7" t="n">
-        <v>7291</v>
+        <v>7395.75</v>
       </c>
       <c r="J7" t="n">
-        <v>7417.62</v>
+        <v>7474</v>
       </c>
       <c r="K7" t="n">
-        <v>7446.75</v>
+        <v>7505.25</v>
       </c>
       <c r="L7" t="n">
-        <v>7475.88</v>
+        <v>7536.5</v>
       </c>
       <c r="M7" t="n">
-        <v>7553.75</v>
+        <v>7591.25</v>
       </c>
       <c r="N7" t="n">
-        <v>7631.62</v>
+        <v>7646</v>
       </c>
       <c r="O7" t="n">
-        <v>7612</v>
+        <v>7653.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1098,13 +1102,11 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1114,62 +1116,62 @@
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7543.25</v>
+        <v>7536</v>
       </c>
       <c r="C8" t="n">
-        <v>7579</v>
+        <v>7593.75</v>
       </c>
       <c r="D8" t="n">
-        <v>7505.75</v>
+        <v>7479.5</v>
       </c>
       <c r="E8" t="n">
-        <v>7543.5</v>
+        <v>7528.25</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.75</v>
+        <v>-15.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="H8" t="n">
-        <v>73.25</v>
+        <v>114.25</v>
       </c>
       <c r="I8" t="n">
-        <v>7395.75</v>
+        <v>7432.5</v>
       </c>
       <c r="J8" t="n">
-        <v>7474</v>
+        <v>7470.81</v>
       </c>
       <c r="K8" t="n">
-        <v>7505.25</v>
+        <v>7506.88</v>
       </c>
       <c r="L8" t="n">
-        <v>7536.5</v>
+        <v>7542.94</v>
       </c>
       <c r="M8" t="n">
-        <v>7591.25</v>
+        <v>7580.12</v>
       </c>
       <c r="N8" t="n">
-        <v>7646</v>
+        <v>7617.31</v>
       </c>
       <c r="O8" t="n">
-        <v>7653.75</v>
+        <v>7652.25</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1177,16 +1179,20 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1196,7 +1202,7 @@
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1208,50 +1214,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C9" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D9" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E9" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I9" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J9" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K9" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L9" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M9" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N9" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O9" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1259,19 +1265,17 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U9" s="8" t="n">
@@ -1282,82 +1286,80 @@
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C10" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D10" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E10" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F10" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H10" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I10" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J10" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K10" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L10" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M10" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N10" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O10" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1366,7 +1368,7 @@
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1378,50 +1380,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C11" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D11" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E11" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F11" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H11" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I11" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J11" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K11" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L11" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M11" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N11" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O11" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1452,80 +1454,82 @@
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C12" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D12" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E12" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F12" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H12" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I12" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J12" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K12" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L12" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M12" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N12" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O12" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1534,7 +1538,7 @@
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1542,50 +1546,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C13" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D13" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E13" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H13" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I13" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J13" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K13" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L13" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M13" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N13" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O13" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1614,82 +1618,80 @@
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C14" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D14" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E14" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F14" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H14" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I14" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J14" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K14" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L14" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M14" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N14" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O14" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1698,7 +1700,7 @@
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -1710,72 +1712,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C15" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D15" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E15" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F15" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H15" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I15" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J15" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K15" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L15" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M15" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N15" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O15" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1784,58 +1784,62 @@
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C16" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D16" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E16" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F16" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H16" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I16" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J16" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K16" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L16" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M16" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N16" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O16" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1864,82 +1868,80 @@
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C17" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D17" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E17" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F17" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H17" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I17" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J17" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K17" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L17" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M17" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N17" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O17" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1948,62 +1950,62 @@
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C18" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D18" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E18" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F18" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H18" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I18" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J18" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K18" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L18" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M18" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N18" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O18" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2034,84 +2036,82 @@
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C19" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D19" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E19" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H19" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I19" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J19" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K19" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L19" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M19" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N19" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O19" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2120,58 +2120,62 @@
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C20" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D20" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E20" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I20" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J20" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K20" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L20" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M20" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N20" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O20" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2182,9 +2186,9 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2192,15 +2196,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2212,50 +2218,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C21" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D21" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E21" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F21" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H21" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I21" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J21" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K21" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L21" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M21" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N21" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O21" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2263,28 +2269,26 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2298,65 +2302,69 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C22" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D22" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E22" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H22" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I22" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J22" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K22" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L22" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M22" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N22" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O22" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2370,81 +2378,71 @@
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C23" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D23" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E23" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F23" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H23" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I23" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J23" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K23" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L23" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M23" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N23" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O23" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7687.25</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2456,60 +2454,64 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C24" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D24" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E24" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H24" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I24" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J24" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K24" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L24" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M24" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N24" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O24" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2525,16 +2527,20 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2548,50 +2554,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C25" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D25" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E25" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F25" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H25" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I25" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J25" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K25" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L25" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M25" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N25" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O25" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2602,25 +2608,21 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2634,67 +2636,75 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C26" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D26" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E26" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H26" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I26" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J26" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K26" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L26" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M26" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N26" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O26" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2702,154 +2712,150 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C27" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D27" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E27" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F27" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H27" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I27" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J27" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K27" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L27" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M27" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N27" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O27" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C28" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D28" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E28" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F28" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H28" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I28" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J28" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K28" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L28" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M28" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N28" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O28" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2867,75 +2873,73 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C29" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D29" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E29" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F29" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H29" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I29" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J29" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K29" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L29" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M29" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N29" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O29" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2953,16 +2957,18 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2976,50 +2982,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C30" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D30" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E30" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F30" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H30" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I30" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J30" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K30" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L30" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M30" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N30" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O30" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3045,67 +3051,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V30" s="8" t="n">
-        <v/>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C31" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D31" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E31" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F31" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H31" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I31" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J31" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K31" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L31" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M31" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N31" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O31" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3118,78 +3122,76 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C32" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D32" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E32" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F32" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H32" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I32" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J32" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K32" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L32" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M32" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N32" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O32" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3197,12 +3199,14 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3214,64 +3218,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C33" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D33" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E33" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F33" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H33" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I33" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J33" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K33" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L33" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M33" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N33" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O33" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3279,83 +3283,81 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C34" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D34" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E34" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F34" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H34" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I34" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J34" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K34" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L34" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M34" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N34" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O34" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3368,93 +3370,99 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C35" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D35" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E35" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F35" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H35" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I35" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J35" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K35" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L35" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M35" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N35" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O35" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3462,152 +3470,148 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C36" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D36" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E36" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F36" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H36" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I36" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J36" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K36" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L36" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M36" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N36" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O36" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C37" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D37" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E37" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F37" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H37" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I37" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J37" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K37" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L37" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M37" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N37" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O37" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3625,73 +3629,71 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C38" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D38" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E38" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F38" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H38" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I38" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J38" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K38" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L38" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M38" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N38" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O38" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3702,95 +3704,101 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C39" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D39" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E39" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F39" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H39" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I39" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J39" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K39" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L39" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M39" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N39" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O39" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3798,73 +3806,73 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C40" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D40" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E40" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F40" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H40" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I40" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J40" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K40" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L40" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M40" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N40" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O40" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3875,10 +3883,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3886,7 +3892,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3900,308 +3906,306 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C41" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D41" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E41" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F41" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H41" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I41" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J41" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K41" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L41" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M41" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N41" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O41" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
       </c>
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C42" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D42" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E42" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F42" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H42" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I42" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J42" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K42" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L42" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M42" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N42" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O42" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C43" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D43" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E43" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F43" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H43" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I43" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J43" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K43" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L43" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M43" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N43" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O43" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C44" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D44" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E44" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F44" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H44" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I44" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J44" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K44" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L44" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M44" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N44" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O44" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4209,18 +4213,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4228,64 +4232,64 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C45" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D45" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E45" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F45" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H45" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I45" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J45" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K45" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L45" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M45" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N45" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O45" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4293,83 +4297,81 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C46" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D46" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E46" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F46" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H46" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I46" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J46" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K46" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L46" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M46" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N46" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O46" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4382,76 +4384,76 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C47" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D47" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E47" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H47" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I47" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J47" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K47" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L47" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M47" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N47" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O47" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4464,76 +4466,78 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C48" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D48" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E48" t="n">
         <v>7722</v>
       </c>
-      <c r="C48" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D48" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E48" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F48" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H48" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I48" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J48" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K48" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L48" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M48" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N48" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O48" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4541,12 +4545,14 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
@@ -4554,70 +4560,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C49" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D49" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E49" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F49" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H49" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I49" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J49" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K49" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L49" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M49" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N49" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O49" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4635,10 +4641,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4646,74 +4650,78 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C50" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D50" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E50" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F50" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H50" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I50" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J50" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K50" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L50" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M50" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N50" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O50" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
@@ -4732,146 +4740,142 @@
       </c>
       <c r="W50" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C51" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D51" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E51" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H51" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I51" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J51" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K51" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L51" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M51" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N51" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O51" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C52" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D52" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E52" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F52" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H52" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I52" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J52" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K52" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L52" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M52" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N52" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O52" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4889,73 +4893,77 @@
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C53" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D53" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E53" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F53" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H53" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I53" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J53" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K53" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L53" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M53" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N53" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O53" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4966,84 +4974,78 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C54" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E54" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H54" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I54" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J54" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K54" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L54" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M54" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N54" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O54" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5051,12 +5053,14 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5068,64 +5072,60 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C55" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D55" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E55" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F55" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H55" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I55" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J55" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K55" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L55" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M55" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N55" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O55" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5152,7 +5152,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5162,50 +5162,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C56" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D56" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E56" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H56" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I56" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J56" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K56" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L56" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M56" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N56" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O56" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5232,7 +5232,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5242,50 +5242,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C57" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D57" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H57" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I57" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J57" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K57" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L57" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M57" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N57" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O57" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5293,79 +5293,85 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C58" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D58" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F58" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H58" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I58" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J58" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K58" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L58" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M58" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N58" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O58" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5373,85 +5379,79 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C59" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D59" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E59" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F59" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H59" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I59" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J59" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K59" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L59" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M59" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N59" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O59" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5478,7 +5478,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5488,56 +5488,60 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7631</v>
+        <v>7596.5</v>
       </c>
       <c r="C60" t="n">
-        <v>7633.25</v>
+        <v>7632</v>
       </c>
       <c r="D60" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E60" t="n">
-        <v>7589.25</v>
+        <v>7556.5</v>
       </c>
       <c r="F60" t="n">
-        <v>-35.75</v>
+        <v>-32.75</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0043</v>
       </c>
       <c r="H60" t="n">
-        <v>56.5</v>
+        <v>122.75</v>
       </c>
       <c r="I60" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J60" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K60" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L60" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M60" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N60" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O60" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+        <v>7689.75</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
@@ -5549,8 +5553,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5558,7 +5564,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5568,136 +5574,134 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7596.5</v>
+        <v>7557.5</v>
       </c>
       <c r="C61" t="n">
-        <v>7632</v>
+        <v>7654.5</v>
       </c>
       <c r="D61" t="n">
-        <v>7509.25</v>
+        <v>7551.5</v>
       </c>
       <c r="E61" t="n">
-        <v>7556.5</v>
+        <v>7640</v>
       </c>
       <c r="F61" t="n">
-        <v>-32.75</v>
+        <v>83.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="H61" t="n">
-        <v>122.75</v>
+        <v>103</v>
       </c>
       <c r="I61" t="n">
-        <v>7520.25</v>
+        <v>7386.5</v>
       </c>
       <c r="J61" t="n">
-        <v>7524.88</v>
+        <v>7426.69</v>
       </c>
       <c r="K61" t="n">
-        <v>7561</v>
+        <v>7495.12</v>
       </c>
       <c r="L61" t="n">
-        <v>7597.12</v>
+        <v>7563.56</v>
       </c>
       <c r="M61" t="n">
-        <v>7617.5</v>
+        <v>7617.88</v>
       </c>
       <c r="N61" t="n">
-        <v>7637.88</v>
+        <v>7672.19</v>
       </c>
       <c r="O61" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
+        <v>7754.75</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7703.5</v>
+        <v>7637</v>
       </c>
       <c r="C62" t="n">
-        <v>7704.25</v>
+        <v>7670.25</v>
       </c>
       <c r="D62" t="n">
-        <v>7697</v>
+        <v>7625.25</v>
       </c>
       <c r="E62" t="n">
-        <v>7700.5</v>
+        <v>7657.35</v>
       </c>
       <c r="F62" t="n">
-        <v>144</v>
+        <v>17.35</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0191</v>
+        <v>0.0023</v>
       </c>
       <c r="H62" t="n">
-        <v>7.25</v>
+        <v>45</v>
       </c>
       <c r="I62" t="n">
-        <v>7386.5</v>
+        <v>7448.5</v>
       </c>
       <c r="J62" t="n">
-        <v>7426.69</v>
+        <v>7555.5</v>
       </c>
       <c r="K62" t="n">
-        <v>7495.12</v>
+        <v>7588.5</v>
       </c>
       <c r="L62" t="n">
-        <v>7563.56</v>
+        <v>7621.5</v>
       </c>
       <c r="M62" t="n">
-        <v>7617.88</v>
+        <v>7691.5</v>
       </c>
       <c r="N62" t="n">
-        <v>7672.19</v>
+        <v>7761.5</v>
       </c>
       <c r="O62" t="n">
-        <v>7754.75</v>
+        <v>7757.5</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5715,23 +5719,109 @@
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7722</v>
+      </c>
+      <c r="C63" t="n">
+        <v>7724.25</v>
+      </c>
+      <c r="D63" t="n">
+        <v>7713.75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>7712.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="H63" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>7580.25</v>
+      </c>
+      <c r="J63" t="n">
+        <v>7617.15</v>
+      </c>
+      <c r="K63" t="n">
+        <v>7634.85</v>
+      </c>
+      <c r="L63" t="n">
+        <v>7652.55</v>
+      </c>
+      <c r="M63" t="n">
+        <v>7679.85</v>
+      </c>
+      <c r="N63" t="n">
+        <v>7707.15</v>
+      </c>
+      <c r="O63" t="n">
+        <v>7715.25</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U62" s="8" t="inlineStr">
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7449.25</v>
+        <v>7476.25</v>
       </c>
       <c r="C2" t="n">
-        <v>7496.5</v>
+        <v>7496</v>
       </c>
       <c r="D2" t="n">
-        <v>7404.25</v>
+        <v>7390.5</v>
       </c>
       <c r="E2" t="n">
-        <v>7428.25</v>
+        <v>7423.25</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.25</v>
+        <v>-5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.0007</v>
       </c>
       <c r="H2" t="n">
-        <v>92.25</v>
+        <v>105.5</v>
       </c>
       <c r="I2" t="n">
-        <v>7281</v>
+        <v>7312</v>
       </c>
       <c r="J2" t="n">
-        <v>7280.81</v>
+        <v>7324.94</v>
       </c>
       <c r="K2" t="n">
-        <v>7370.38</v>
+        <v>7382.12</v>
       </c>
       <c r="L2" t="n">
-        <v>7459.94</v>
+        <v>7439.31</v>
       </c>
       <c r="M2" t="n">
-        <v>7504.62</v>
+        <v>7474.38</v>
       </c>
       <c r="N2" t="n">
-        <v>7549.31</v>
+        <v>7509.44</v>
       </c>
       <c r="O2" t="n">
-        <v>7683.75</v>
+        <v>7588.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -693,8 +693,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -716,50 +718,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7476.25</v>
+        <v>7431</v>
       </c>
       <c r="C3" t="n">
-        <v>7496</v>
+        <v>7459.5</v>
       </c>
       <c r="D3" t="n">
-        <v>7390.5</v>
+        <v>7357.25</v>
       </c>
       <c r="E3" t="n">
-        <v>7423.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F3" t="n">
-        <v>-5</v>
+        <v>-21.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0029</v>
       </c>
       <c r="H3" t="n">
-        <v>105.5</v>
+        <v>102.25</v>
       </c>
       <c r="I3" t="n">
-        <v>7312</v>
+        <v>7285</v>
       </c>
       <c r="J3" t="n">
-        <v>7324.94</v>
+        <v>7307.75</v>
       </c>
       <c r="K3" t="n">
-        <v>7382.12</v>
+        <v>7370.5</v>
       </c>
       <c r="L3" t="n">
-        <v>7439.31</v>
+        <v>7433.25</v>
       </c>
       <c r="M3" t="n">
-        <v>7474.38</v>
+        <v>7476</v>
       </c>
       <c r="N3" t="n">
-        <v>7509.44</v>
+        <v>7518.75</v>
       </c>
       <c r="O3" t="n">
-        <v>7588.75</v>
+        <v>7601.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -767,18 +769,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -800,50 +802,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7431</v>
+        <v>7398</v>
       </c>
       <c r="C4" t="n">
-        <v>7459.5</v>
+        <v>7505</v>
       </c>
       <c r="D4" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E4" t="n">
-        <v>7401.75</v>
+        <v>7500.25</v>
       </c>
       <c r="F4" t="n">
-        <v>-21.5</v>
+        <v>98.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0133</v>
       </c>
       <c r="H4" t="n">
-        <v>102.25</v>
+        <v>107</v>
       </c>
       <c r="I4" t="n">
-        <v>7285</v>
+        <v>7255</v>
       </c>
       <c r="J4" t="n">
-        <v>7307.75</v>
+        <v>7296.19</v>
       </c>
       <c r="K4" t="n">
-        <v>7370.5</v>
+        <v>7350.62</v>
       </c>
       <c r="L4" t="n">
-        <v>7433.25</v>
+        <v>7405.06</v>
       </c>
       <c r="M4" t="n">
-        <v>7476</v>
+        <v>7452.88</v>
       </c>
       <c r="N4" t="n">
-        <v>7518.75</v>
+        <v>7500.69</v>
       </c>
       <c r="O4" t="n">
-        <v>7601.5</v>
+        <v>7561.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,22 +853,24 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
@@ -875,59 +879,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7398</v>
+        <v>7495.5</v>
       </c>
       <c r="C5" t="n">
-        <v>7505</v>
+        <v>7567.75</v>
       </c>
       <c r="D5" t="n">
-        <v>7398</v>
+        <v>7481.75</v>
       </c>
       <c r="E5" t="n">
-        <v>7500.25</v>
+        <v>7548.25</v>
       </c>
       <c r="F5" t="n">
-        <v>98.5</v>
+        <v>48</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0064</v>
       </c>
       <c r="H5" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="I5" t="n">
-        <v>7255</v>
+        <v>7291</v>
       </c>
       <c r="J5" t="n">
-        <v>7296.19</v>
+        <v>7417.62</v>
       </c>
       <c r="K5" t="n">
-        <v>7350.62</v>
+        <v>7446.75</v>
       </c>
       <c r="L5" t="n">
-        <v>7405.06</v>
+        <v>7475.88</v>
       </c>
       <c r="M5" t="n">
-        <v>7452.88</v>
+        <v>7553.75</v>
       </c>
       <c r="N5" t="n">
-        <v>7500.69</v>
+        <v>7631.62</v>
       </c>
       <c r="O5" t="n">
-        <v>7561.75</v>
+        <v>7612</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -945,13 +945,11 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -966,50 +964,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7495.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C6" t="n">
-        <v>7567.75</v>
+        <v>7579</v>
       </c>
       <c r="D6" t="n">
-        <v>7481.75</v>
+        <v>7505.75</v>
       </c>
       <c r="E6" t="n">
-        <v>7548.25</v>
+        <v>7543.5</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>-4.75</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0064</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>86</v>
+        <v>73.25</v>
       </c>
       <c r="I6" t="n">
-        <v>7291</v>
+        <v>7395.75</v>
       </c>
       <c r="J6" t="n">
-        <v>7417.62</v>
+        <v>7474</v>
       </c>
       <c r="K6" t="n">
-        <v>7446.75</v>
+        <v>7505.25</v>
       </c>
       <c r="L6" t="n">
-        <v>7475.88</v>
+        <v>7536.5</v>
       </c>
       <c r="M6" t="n">
-        <v>7553.75</v>
+        <v>7591.25</v>
       </c>
       <c r="N6" t="n">
-        <v>7631.62</v>
+        <v>7646</v>
       </c>
       <c r="O6" t="n">
-        <v>7612</v>
+        <v>7653.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1022,13 +1020,11 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1041,55 +1037,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7543.25</v>
+        <v>7536</v>
       </c>
       <c r="C7" t="n">
-        <v>7579</v>
+        <v>7593.75</v>
       </c>
       <c r="D7" t="n">
-        <v>7505.75</v>
+        <v>7479.5</v>
       </c>
       <c r="E7" t="n">
-        <v>7543.5</v>
+        <v>7528.25</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.75</v>
+        <v>-15.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="H7" t="n">
-        <v>73.25</v>
+        <v>114.25</v>
       </c>
       <c r="I7" t="n">
-        <v>7395.75</v>
+        <v>7432.5</v>
       </c>
       <c r="J7" t="n">
-        <v>7474</v>
+        <v>7470.81</v>
       </c>
       <c r="K7" t="n">
-        <v>7505.25</v>
+        <v>7506.88</v>
       </c>
       <c r="L7" t="n">
-        <v>7536.5</v>
+        <v>7542.94</v>
       </c>
       <c r="M7" t="n">
-        <v>7591.25</v>
+        <v>7580.12</v>
       </c>
       <c r="N7" t="n">
-        <v>7646</v>
+        <v>7617.31</v>
       </c>
       <c r="O7" t="n">
-        <v>7653.75</v>
+        <v>7652.25</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1097,16 +1097,20 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1121,57 +1125,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C8" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D8" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E8" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I8" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J8" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K8" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L8" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M8" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N8" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O8" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1179,19 +1183,17 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1205,79 +1207,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C9" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D9" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E9" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F9" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H9" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I9" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J9" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K9" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L9" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M9" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N9" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O9" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1289,55 +1289,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C10" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D10" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E10" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F10" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H10" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I10" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J10" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K10" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L10" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M10" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N10" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O10" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1380,72 +1384,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C11" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D11" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E11" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F11" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H11" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I11" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J11" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K11" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L11" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M11" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N11" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O11" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1457,59 +1459,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C12" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D12" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E12" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H12" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I12" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J12" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K12" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L12" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M12" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N12" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O12" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1546,70 +1544,72 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C13" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D13" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E13" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F13" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H13" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I13" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J13" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K13" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L13" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M13" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N13" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O13" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="Q13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1621,77 +1621,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C14" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D14" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E14" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F14" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H14" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I14" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J14" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K14" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L14" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M14" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N14" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O14" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1705,57 +1707,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C15" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D15" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E15" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F15" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H15" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I15" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J15" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K15" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L15" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M15" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N15" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O15" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1787,79 +1789,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C16" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D16" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E16" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F16" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H16" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I16" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J16" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K16" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L16" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M16" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N16" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O16" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1871,55 +1871,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C17" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D17" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E17" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F17" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H17" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I17" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J17" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K17" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L17" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M17" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N17" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O17" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1955,79 +1959,77 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C18" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D18" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E18" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H18" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I18" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J18" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K18" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L18" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M18" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N18" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O18" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2041,57 +2043,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C19" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D19" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E19" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I19" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J19" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K19" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L19" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M19" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N19" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O19" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2102,9 +2104,9 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2112,8 +2114,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2125,57 +2129,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C20" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D20" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E20" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F20" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H20" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I20" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J20" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K20" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L20" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M20" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N20" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O20" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2183,23 +2187,21 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2218,65 +2220,69 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C21" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D21" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E21" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H21" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I21" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J21" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K21" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L21" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M21" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N21" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O21" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2288,83 +2294,73 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C22" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D22" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E22" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H22" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I22" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J22" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K22" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L22" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M22" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N22" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O22" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7687.25</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2381,55 +2377,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C23" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D23" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E23" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H23" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I23" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J23" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K23" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L23" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M23" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N23" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O23" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2445,11 +2445,15 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2468,50 +2472,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C24" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D24" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E24" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F24" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H24" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I24" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J24" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K24" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L24" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M24" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N24" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O24" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2522,20 +2526,16 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2554,67 +2554,75 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C25" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D25" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E25" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F25" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H25" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I25" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J25" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K25" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L25" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M25" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N25" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O25" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2629,86 +2637,82 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C26" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D26" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E26" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H26" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I26" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J26" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K26" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L26" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M26" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N26" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O26" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2719,57 +2723,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C27" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D27" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E27" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F27" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H27" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I27" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J27" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K27" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L27" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M27" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N27" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O27" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2787,14 +2791,12 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
@@ -2805,57 +2807,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C28" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D28" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E28" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F28" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H28" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I28" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J28" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K28" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L28" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M28" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N28" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O28" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2873,11 +2875,13 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2896,50 +2900,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C29" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D29" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E29" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F29" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H29" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I29" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J29" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K29" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L29" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M29" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N29" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O29" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2965,67 +2969,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C30" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D30" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E30" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F30" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H30" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I30" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J30" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K30" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L30" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M30" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N30" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O30" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3038,78 +3040,76 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C31" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D31" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E31" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F31" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H31" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I31" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J31" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K31" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L31" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M31" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N31" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O31" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3117,12 +3117,14 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3141,57 +3143,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C32" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D32" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E32" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F32" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H32" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I32" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J32" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K32" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L32" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M32" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N32" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O32" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3199,22 +3201,24 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
@@ -3223,59 +3227,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C33" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D33" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E33" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F33" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H33" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I33" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J33" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K33" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L33" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M33" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N33" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O33" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3288,18 +3288,14 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3309,72 +3305,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C34" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D34" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E34" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F34" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H34" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I34" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J34" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K34" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L34" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M34" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N34" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O34" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3389,81 +3395,77 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C35" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D35" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E35" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F35" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H35" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I35" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J35" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K35" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L35" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M35" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N35" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O35" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3477,57 +3479,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C36" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D36" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E36" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F36" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H36" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I36" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J36" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K36" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L36" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M36" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N36" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O36" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3545,12 +3547,14 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3559,59 +3563,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C37" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D37" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E37" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F37" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H37" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I37" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J37" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K37" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L37" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M37" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N37" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O37" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3622,20 +3622,16 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3645,72 +3641,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C38" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D38" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E38" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F38" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H38" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I38" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J38" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K38" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L38" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M38" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N38" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O38" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3725,66 +3731,66 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C39" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D39" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E39" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F39" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H39" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I39" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J39" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K39" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L39" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M39" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N39" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O39" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3795,10 +3801,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3820,74 +3824,74 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C40" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D40" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E40" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F40" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H40" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I40" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J40" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K40" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L40" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M40" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N40" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O40" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
       </c>
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3899,81 +3903,81 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C41" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D41" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E41" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F41" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H41" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I41" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J41" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K41" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L41" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M41" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N41" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O41" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3985,79 +3989,77 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C42" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D42" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E42" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F42" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H42" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I42" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J42" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K42" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L42" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M42" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N42" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O42" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4071,57 +4073,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C43" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D43" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E43" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F43" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H43" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I43" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J43" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K43" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L43" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M43" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N43" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O43" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4129,18 +4131,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4155,57 +4157,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C44" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D44" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E44" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F44" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H44" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I44" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J44" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K44" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L44" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M44" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N44" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O44" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4213,21 +4215,23 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4237,59 +4241,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C45" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D45" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E45" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F45" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H45" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I45" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J45" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K45" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L45" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M45" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N45" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O45" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4302,18 +4302,14 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4323,55 +4319,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C46" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D46" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E46" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H46" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I46" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J46" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K46" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L46" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M46" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N46" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O46" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4384,76 +4384,78 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C47" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E47" t="n">
         <v>7722</v>
       </c>
-      <c r="C47" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D47" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E47" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F47" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H47" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I47" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J47" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K47" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L47" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M47" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N47" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O47" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4461,12 +4463,14 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
@@ -4474,70 +4478,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C48" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D48" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E48" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F48" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H48" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I48" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J48" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K48" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L48" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M48" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N48" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O48" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4555,10 +4559,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4573,67 +4575,71 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C49" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D49" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E49" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F49" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H49" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I49" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J49" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K49" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L49" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M49" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N49" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O49" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
@@ -4650,88 +4656,80 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C50" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D50" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E50" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H50" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I50" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J50" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K50" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L50" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M50" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N50" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O50" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4743,55 +4741,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C51" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D51" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E51" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F51" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H51" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I51" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J51" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K51" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L51" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M51" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N51" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O51" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4809,14 +4811,18 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
@@ -4825,57 +4831,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C52" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D52" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E52" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F52" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H52" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I52" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J52" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K52" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L52" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M52" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N52" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O52" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4886,25 +4892,19 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
@@ -4913,57 +4913,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C53" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D53" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E53" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H53" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I53" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J53" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K53" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L53" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M53" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N53" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O53" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4971,12 +4971,14 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4993,59 +4995,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C54" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D54" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E54" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F54" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H54" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I54" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J54" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K54" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L54" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M54" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N54" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O54" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5082,50 +5080,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C55" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D55" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E55" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H55" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I55" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J55" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K55" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L55" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M55" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N55" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O55" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5162,50 +5160,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C56" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D56" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E56" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H56" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I56" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J56" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K56" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L56" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M56" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N56" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O56" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5213,22 +5211,24 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
@@ -5237,55 +5237,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C57" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D57" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E57" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F57" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H57" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I57" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J57" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K57" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L57" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M57" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N57" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O57" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5293,24 +5297,22 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
@@ -5319,59 +5321,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C58" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D58" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H58" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I58" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J58" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K58" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L58" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M58" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N58" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O58" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5408,56 +5406,60 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7631</v>
+        <v>7596.5</v>
       </c>
       <c r="C59" t="n">
-        <v>7633.25</v>
+        <v>7632</v>
       </c>
       <c r="D59" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E59" t="n">
-        <v>7589.25</v>
+        <v>7556.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-35.75</v>
+        <v>-32.75</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0043</v>
       </c>
       <c r="H59" t="n">
-        <v>56.5</v>
+        <v>122.75</v>
       </c>
       <c r="I59" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J59" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K59" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L59" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M59" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N59" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O59" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+        <v>7689.75</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
@@ -5469,8 +5471,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5488,76 +5492,70 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7596.5</v>
+        <v>7557.5</v>
       </c>
       <c r="C60" t="n">
-        <v>7632</v>
+        <v>7654.5</v>
       </c>
       <c r="D60" t="n">
-        <v>7509.25</v>
+        <v>7551.5</v>
       </c>
       <c r="E60" t="n">
-        <v>7556.5</v>
+        <v>7640</v>
       </c>
       <c r="F60" t="n">
-        <v>-32.75</v>
+        <v>83.5</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="H60" t="n">
-        <v>122.75</v>
+        <v>103</v>
       </c>
       <c r="I60" t="n">
-        <v>7520.25</v>
+        <v>7386.5</v>
       </c>
       <c r="J60" t="n">
-        <v>7524.88</v>
+        <v>7426.69</v>
       </c>
       <c r="K60" t="n">
-        <v>7561</v>
+        <v>7495.12</v>
       </c>
       <c r="L60" t="n">
-        <v>7597.12</v>
+        <v>7563.56</v>
       </c>
       <c r="M60" t="n">
-        <v>7617.5</v>
+        <v>7617.88</v>
       </c>
       <c r="N60" t="n">
-        <v>7637.88</v>
+        <v>7672.19</v>
       </c>
       <c r="O60" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
+        <v>7754.75</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
@@ -5569,55 +5567,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7557.5</v>
+        <v>7637</v>
       </c>
       <c r="C61" t="n">
-        <v>7654.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D61" t="n">
-        <v>7551.5</v>
+        <v>7625.25</v>
       </c>
       <c r="E61" t="n">
-        <v>7640</v>
+        <v>7657.35</v>
       </c>
       <c r="F61" t="n">
-        <v>83.5</v>
+        <v>17.35</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0023</v>
       </c>
       <c r="H61" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I61" t="n">
-        <v>7386.5</v>
+        <v>7448.5</v>
       </c>
       <c r="J61" t="n">
-        <v>7426.69</v>
+        <v>7555.5</v>
       </c>
       <c r="K61" t="n">
-        <v>7495.12</v>
+        <v>7588.5</v>
       </c>
       <c r="L61" t="n">
-        <v>7563.56</v>
+        <v>7621.5</v>
       </c>
       <c r="M61" t="n">
-        <v>7617.88</v>
+        <v>7691.5</v>
       </c>
       <c r="N61" t="n">
-        <v>7672.19</v>
+        <v>7761.5</v>
       </c>
       <c r="O61" t="n">
-        <v>7754.75</v>
+        <v>7757.5</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5658,50 +5660,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7637</v>
+        <v>7830</v>
       </c>
       <c r="C62" t="n">
-        <v>7670.25</v>
+        <v>7833</v>
       </c>
       <c r="D62" t="n">
-        <v>7625.25</v>
+        <v>7829</v>
       </c>
       <c r="E62" t="n">
-        <v>7657.35</v>
+        <v>7832.5</v>
       </c>
       <c r="F62" t="n">
-        <v>17.35</v>
+        <v>175.15</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.0229</v>
       </c>
       <c r="H62" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="I62" t="n">
-        <v>7448.5</v>
+        <v>7580.25</v>
       </c>
       <c r="J62" t="n">
-        <v>7555.5</v>
+        <v>7617.15</v>
       </c>
       <c r="K62" t="n">
-        <v>7588.5</v>
+        <v>7634.85</v>
       </c>
       <c r="L62" t="n">
-        <v>7621.5</v>
+        <v>7652.55</v>
       </c>
       <c r="M62" t="n">
-        <v>7691.5</v>
+        <v>7679.85</v>
       </c>
       <c r="N62" t="n">
-        <v>7761.5</v>
+        <v>7707.15</v>
       </c>
       <c r="O62" t="n">
-        <v>7757.5</v>
+        <v>7715.25</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5719,109 +5721,25 @@
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>7722</v>
-      </c>
-      <c r="C63" t="n">
-        <v>7724.25</v>
-      </c>
-      <c r="D63" t="n">
-        <v>7713.75</v>
-      </c>
-      <c r="E63" t="n">
-        <v>7712.5</v>
-      </c>
-      <c r="F63" t="n">
-        <v>55.15</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="H63" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I63" t="n">
-        <v>7580.25</v>
-      </c>
-      <c r="J63" t="n">
-        <v>7617.15</v>
-      </c>
-      <c r="K63" t="n">
-        <v>7634.85</v>
-      </c>
-      <c r="L63" t="n">
-        <v>7652.55</v>
-      </c>
-      <c r="M63" t="n">
-        <v>7679.85</v>
-      </c>
-      <c r="N63" t="n">
-        <v>7707.15</v>
-      </c>
-      <c r="O63" t="n">
-        <v>7715.25</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5664,25 +5664,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7830</v>
+        <v>7722</v>
       </c>
       <c r="C62" t="n">
-        <v>7833</v>
+        <v>7847.25</v>
       </c>
       <c r="D62" t="n">
-        <v>7829</v>
+        <v>7713.75</v>
       </c>
       <c r="E62" t="n">
-        <v>7832.5</v>
+        <v>7833.5</v>
       </c>
       <c r="F62" t="n">
-        <v>175.15</v>
+        <v>176.15</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0229</v>
+        <v>0.023</v>
       </c>
       <c r="H62" t="n">
-        <v>4</v>
+        <v>133.5</v>
       </c>
       <c r="I62" t="n">
         <v>7580.25</v>
@@ -5740,6 +5740,84 @@
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7830</v>
+      </c>
+      <c r="C63" t="n">
+        <v>7848.5</v>
+      </c>
+      <c r="D63" t="n">
+        <v>7810.5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>7837.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>4</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H63" t="n">
+        <v>38</v>
+      </c>
+      <c r="I63" t="n">
+        <v>7580.25</v>
+      </c>
+      <c r="J63" t="n">
+        <v>7726.5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>7766.75</v>
+      </c>
+      <c r="L63" t="n">
+        <v>7807</v>
+      </c>
+      <c r="M63" t="n">
+        <v>7900.25</v>
+      </c>
+      <c r="N63" t="n">
+        <v>7993.5</v>
+      </c>
+      <c r="O63" t="n">
+        <v>7980.75</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5757,13 +5757,13 @@
         <v>7810.5</v>
       </c>
       <c r="E63" t="n">
-        <v>7837.5</v>
+        <v>7829.75</v>
       </c>
       <c r="F63" t="n">
-        <v>4</v>
+        <v>-3.75</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0005</v>
+        <v>-0.0005</v>
       </c>
       <c r="H63" t="n">
         <v>38</v>
@@ -5817,7 +5817,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7476.25</v>
+        <v>7431</v>
       </c>
       <c r="C2" t="n">
-        <v>7496</v>
+        <v>7459.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7390.5</v>
+        <v>7357.25</v>
       </c>
       <c r="E2" t="n">
-        <v>7423.25</v>
+        <v>7401.75</v>
       </c>
       <c r="F2" t="n">
-        <v>-5</v>
+        <v>-21.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0029</v>
       </c>
       <c r="H2" t="n">
-        <v>105.5</v>
+        <v>102.25</v>
       </c>
       <c r="I2" t="n">
-        <v>7312</v>
+        <v>7285</v>
       </c>
       <c r="J2" t="n">
-        <v>7324.94</v>
+        <v>7307.75</v>
       </c>
       <c r="K2" t="n">
-        <v>7382.12</v>
+        <v>7370.5</v>
       </c>
       <c r="L2" t="n">
-        <v>7439.31</v>
+        <v>7433.25</v>
       </c>
       <c r="M2" t="n">
-        <v>7474.38</v>
+        <v>7476</v>
       </c>
       <c r="N2" t="n">
-        <v>7509.44</v>
+        <v>7518.75</v>
       </c>
       <c r="O2" t="n">
-        <v>7588.75</v>
+        <v>7601.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,18 +685,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -718,50 +718,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7431</v>
+        <v>7398</v>
       </c>
       <c r="C3" t="n">
-        <v>7459.5</v>
+        <v>7505</v>
       </c>
       <c r="D3" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E3" t="n">
-        <v>7401.75</v>
+        <v>7500.25</v>
       </c>
       <c r="F3" t="n">
-        <v>-21.5</v>
+        <v>98.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0133</v>
       </c>
       <c r="H3" t="n">
-        <v>102.25</v>
+        <v>107</v>
       </c>
       <c r="I3" t="n">
-        <v>7285</v>
+        <v>7255</v>
       </c>
       <c r="J3" t="n">
-        <v>7307.75</v>
+        <v>7296.19</v>
       </c>
       <c r="K3" t="n">
-        <v>7370.5</v>
+        <v>7350.62</v>
       </c>
       <c r="L3" t="n">
-        <v>7433.25</v>
+        <v>7405.06</v>
       </c>
       <c r="M3" t="n">
-        <v>7476</v>
+        <v>7452.88</v>
       </c>
       <c r="N3" t="n">
-        <v>7518.75</v>
+        <v>7500.69</v>
       </c>
       <c r="O3" t="n">
-        <v>7601.5</v>
+        <v>7561.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,22 +769,24 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
@@ -793,59 +795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7398</v>
+        <v>7495.5</v>
       </c>
       <c r="C4" t="n">
-        <v>7505</v>
+        <v>7567.75</v>
       </c>
       <c r="D4" t="n">
-        <v>7398</v>
+        <v>7481.75</v>
       </c>
       <c r="E4" t="n">
-        <v>7500.25</v>
+        <v>7548.25</v>
       </c>
       <c r="F4" t="n">
-        <v>98.5</v>
+        <v>48</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0064</v>
       </c>
       <c r="H4" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="I4" t="n">
-        <v>7255</v>
+        <v>7291</v>
       </c>
       <c r="J4" t="n">
-        <v>7296.19</v>
+        <v>7417.62</v>
       </c>
       <c r="K4" t="n">
-        <v>7350.62</v>
+        <v>7446.75</v>
       </c>
       <c r="L4" t="n">
-        <v>7405.06</v>
+        <v>7475.88</v>
       </c>
       <c r="M4" t="n">
-        <v>7452.88</v>
+        <v>7553.75</v>
       </c>
       <c r="N4" t="n">
-        <v>7500.69</v>
+        <v>7631.62</v>
       </c>
       <c r="O4" t="n">
-        <v>7561.75</v>
+        <v>7612</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -863,13 +861,11 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -884,50 +880,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7495.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C5" t="n">
-        <v>7567.75</v>
+        <v>7579</v>
       </c>
       <c r="D5" t="n">
-        <v>7481.75</v>
+        <v>7505.75</v>
       </c>
       <c r="E5" t="n">
-        <v>7548.25</v>
+        <v>7543.5</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>-4.75</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0064</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>86</v>
+        <v>73.25</v>
       </c>
       <c r="I5" t="n">
-        <v>7291</v>
+        <v>7395.75</v>
       </c>
       <c r="J5" t="n">
-        <v>7417.62</v>
+        <v>7474</v>
       </c>
       <c r="K5" t="n">
-        <v>7446.75</v>
+        <v>7505.25</v>
       </c>
       <c r="L5" t="n">
-        <v>7475.88</v>
+        <v>7536.5</v>
       </c>
       <c r="M5" t="n">
-        <v>7553.75</v>
+        <v>7591.25</v>
       </c>
       <c r="N5" t="n">
-        <v>7631.62</v>
+        <v>7646</v>
       </c>
       <c r="O5" t="n">
-        <v>7612</v>
+        <v>7653.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,13 +936,11 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -959,55 +953,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7543.25</v>
+        <v>7536</v>
       </c>
       <c r="C6" t="n">
-        <v>7579</v>
+        <v>7593.75</v>
       </c>
       <c r="D6" t="n">
-        <v>7505.75</v>
+        <v>7479.5</v>
       </c>
       <c r="E6" t="n">
-        <v>7543.5</v>
+        <v>7528.25</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.75</v>
+        <v>-15.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="H6" t="n">
-        <v>73.25</v>
+        <v>114.25</v>
       </c>
       <c r="I6" t="n">
-        <v>7395.75</v>
+        <v>7432.5</v>
       </c>
       <c r="J6" t="n">
-        <v>7474</v>
+        <v>7470.81</v>
       </c>
       <c r="K6" t="n">
-        <v>7505.25</v>
+        <v>7506.88</v>
       </c>
       <c r="L6" t="n">
-        <v>7536.5</v>
+        <v>7542.94</v>
       </c>
       <c r="M6" t="n">
-        <v>7591.25</v>
+        <v>7580.12</v>
       </c>
       <c r="N6" t="n">
-        <v>7646</v>
+        <v>7617.31</v>
       </c>
       <c r="O6" t="n">
-        <v>7653.75</v>
+        <v>7652.25</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1015,16 +1013,20 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1039,57 +1041,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C7" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D7" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E7" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I7" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J7" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K7" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L7" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M7" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N7" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O7" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1097,19 +1099,17 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1123,79 +1123,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C8" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D8" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E8" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F8" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H8" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I8" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J8" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K8" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L8" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M8" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N8" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O8" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1207,55 +1205,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C9" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D9" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E9" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F9" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H9" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I9" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J9" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K9" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L9" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M9" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N9" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O9" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1298,72 +1300,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C10" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D10" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E10" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F10" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H10" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I10" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J10" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K10" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L10" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M10" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N10" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O10" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1375,59 +1375,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C11" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D11" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E11" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H11" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I11" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J11" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K11" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L11" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M11" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N11" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O11" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1464,70 +1460,72 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C12" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D12" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E12" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F12" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H12" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I12" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J12" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K12" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L12" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M12" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N12" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O12" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1539,77 +1537,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C13" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D13" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E13" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F13" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H13" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I13" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J13" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K13" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L13" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M13" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N13" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O13" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1623,57 +1623,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C14" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D14" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E14" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F14" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H14" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I14" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J14" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K14" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L14" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M14" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N14" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O14" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1705,79 +1705,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C15" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D15" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E15" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F15" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H15" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I15" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J15" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K15" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L15" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M15" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N15" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O15" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1789,55 +1787,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C16" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D16" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E16" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F16" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H16" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I16" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J16" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K16" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L16" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M16" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N16" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O16" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1873,79 +1875,77 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C17" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D17" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E17" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F17" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H17" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I17" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J17" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K17" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L17" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M17" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N17" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O17" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1959,57 +1959,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C18" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D18" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E18" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I18" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J18" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K18" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L18" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M18" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N18" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O18" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2020,9 +2020,9 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2030,8 +2030,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2043,57 +2045,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C19" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D19" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E19" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F19" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H19" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I19" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J19" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K19" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L19" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M19" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N19" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O19" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2101,23 +2103,21 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2136,65 +2136,69 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C20" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D20" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E20" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H20" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I20" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J20" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K20" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L20" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M20" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N20" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O20" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2206,83 +2210,73 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C21" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D21" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E21" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H21" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I21" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J21" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K21" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L21" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M21" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N21" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O21" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7687.25</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2299,55 +2293,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C22" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D22" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E22" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H22" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I22" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J22" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K22" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L22" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M22" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N22" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O22" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2363,11 +2361,15 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2386,50 +2388,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C23" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D23" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E23" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F23" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H23" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I23" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J23" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K23" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L23" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M23" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N23" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O23" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2440,20 +2442,16 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2472,67 +2470,75 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C24" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D24" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E24" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F24" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H24" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I24" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J24" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K24" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L24" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M24" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N24" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O24" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2547,86 +2553,82 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C25" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D25" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E25" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F25" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H25" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I25" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J25" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K25" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L25" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M25" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N25" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O25" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2637,57 +2639,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C26" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D26" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E26" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F26" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H26" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I26" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J26" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K26" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L26" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M26" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N26" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O26" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2705,14 +2707,12 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2723,57 +2723,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C27" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D27" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E27" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F27" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H27" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I27" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J27" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K27" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L27" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M27" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N27" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O27" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2791,11 +2791,13 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2814,50 +2816,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C28" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D28" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E28" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F28" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H28" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I28" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J28" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K28" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L28" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M28" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N28" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O28" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2883,67 +2885,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C29" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D29" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E29" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F29" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H29" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I29" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J29" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K29" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L29" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M29" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N29" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O29" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2956,78 +2956,76 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C30" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D30" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E30" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F30" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H30" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I30" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J30" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K30" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L30" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M30" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N30" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O30" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3035,12 +3033,14 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3059,57 +3059,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C31" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D31" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E31" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F31" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H31" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I31" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J31" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K31" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L31" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M31" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N31" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O31" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3117,22 +3117,24 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
@@ -3141,59 +3143,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C32" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D32" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E32" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F32" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H32" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I32" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J32" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K32" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L32" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M32" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N32" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O32" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3206,18 +3204,14 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3227,72 +3221,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C33" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D33" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E33" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H33" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I33" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J33" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K33" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L33" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M33" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N33" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O33" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3307,81 +3311,77 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C34" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D34" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E34" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F34" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H34" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I34" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J34" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K34" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L34" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M34" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N34" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O34" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3395,57 +3395,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C35" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D35" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E35" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F35" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H35" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I35" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J35" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K35" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L35" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M35" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N35" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O35" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3463,12 +3463,14 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3477,59 +3479,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C36" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D36" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E36" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F36" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H36" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I36" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J36" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K36" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L36" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M36" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N36" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O36" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3540,20 +3538,16 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3563,72 +3557,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C37" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D37" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E37" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F37" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H37" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I37" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J37" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K37" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L37" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M37" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N37" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O37" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3643,66 +3647,66 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C38" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D38" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E38" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F38" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H38" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I38" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J38" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K38" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L38" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M38" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N38" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O38" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3713,10 +3717,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3738,74 +3740,74 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C39" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D39" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E39" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F39" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H39" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I39" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J39" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K39" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L39" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M39" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N39" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O39" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
       </c>
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3817,81 +3819,81 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C40" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D40" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E40" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F40" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H40" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I40" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J40" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K40" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L40" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M40" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N40" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O40" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3903,79 +3905,77 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C41" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D41" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E41" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F41" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H41" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I41" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J41" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K41" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L41" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M41" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N41" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O41" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3989,57 +3989,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C42" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D42" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E42" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F42" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H42" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I42" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J42" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K42" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L42" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M42" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N42" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O42" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4047,18 +4047,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4073,57 +4073,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C43" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D43" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E43" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F43" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H43" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I43" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J43" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K43" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L43" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M43" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N43" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O43" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4131,21 +4131,23 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4155,59 +4157,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C44" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D44" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E44" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F44" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H44" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I44" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J44" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K44" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L44" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M44" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N44" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O44" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4220,18 +4218,14 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4241,55 +4235,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C45" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D45" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E45" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F45" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H45" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I45" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J45" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K45" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L45" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M45" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N45" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O45" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4302,76 +4300,78 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C46" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E46" t="n">
         <v>7722</v>
       </c>
-      <c r="C46" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D46" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E46" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F46" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H46" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I46" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J46" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K46" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L46" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M46" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N46" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O46" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4379,12 +4379,14 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -4392,70 +4394,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C47" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D47" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E47" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F47" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H47" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I47" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J47" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K47" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L47" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M47" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N47" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O47" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4473,10 +4475,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4491,67 +4491,71 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C48" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D48" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E48" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F48" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H48" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I48" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J48" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K48" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L48" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M48" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N48" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O48" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
@@ -4568,88 +4572,80 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C49" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D49" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E49" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H49" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I49" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J49" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K49" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L49" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M49" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N49" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O49" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4661,55 +4657,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C50" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D50" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E50" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F50" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H50" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I50" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J50" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K50" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L50" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M50" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N50" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O50" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4727,14 +4727,18 @@
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W50" s="11" t="inlineStr">
         <is>
@@ -4743,57 +4747,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C51" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D51" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E51" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F51" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H51" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I51" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J51" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K51" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L51" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M51" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N51" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O51" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4804,25 +4808,19 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
@@ -4831,57 +4829,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C52" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D52" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E52" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H52" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I52" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J52" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K52" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L52" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M52" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N52" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O52" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4889,12 +4887,14 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4911,59 +4911,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C53" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D53" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E53" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F53" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H53" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I53" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J53" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K53" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L53" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M53" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N53" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O53" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -5000,50 +4996,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C54" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D54" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E54" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H54" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I54" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J54" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K54" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L54" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M54" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N54" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O54" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5080,50 +5076,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C55" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D55" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E55" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H55" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I55" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J55" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K55" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L55" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M55" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N55" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O55" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5131,22 +5127,24 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5155,55 +5153,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C56" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D56" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E56" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F56" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H56" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I56" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J56" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K56" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L56" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M56" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N56" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O56" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5211,24 +5213,22 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
@@ -5237,59 +5237,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C57" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D57" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E57" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F57" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H57" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I57" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J57" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K57" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L57" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M57" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N57" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O57" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5326,56 +5322,60 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7631</v>
+        <v>7596.5</v>
       </c>
       <c r="C58" t="n">
-        <v>7633.25</v>
+        <v>7632</v>
       </c>
       <c r="D58" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7589.25</v>
+        <v>7556.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-35.75</v>
+        <v>-32.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0043</v>
       </c>
       <c r="H58" t="n">
-        <v>56.5</v>
+        <v>122.75</v>
       </c>
       <c r="I58" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J58" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K58" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L58" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M58" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N58" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O58" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+        <v>7689.75</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
@@ -5387,8 +5387,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5406,76 +5408,70 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7596.5</v>
+        <v>7557.5</v>
       </c>
       <c r="C59" t="n">
-        <v>7632</v>
+        <v>7654.5</v>
       </c>
       <c r="D59" t="n">
-        <v>7509.25</v>
+        <v>7551.5</v>
       </c>
       <c r="E59" t="n">
-        <v>7556.5</v>
+        <v>7640</v>
       </c>
       <c r="F59" t="n">
-        <v>-32.75</v>
+        <v>83.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="H59" t="n">
-        <v>122.75</v>
+        <v>103</v>
       </c>
       <c r="I59" t="n">
-        <v>7520.25</v>
+        <v>7386.5</v>
       </c>
       <c r="J59" t="n">
-        <v>7524.88</v>
+        <v>7426.69</v>
       </c>
       <c r="K59" t="n">
-        <v>7561</v>
+        <v>7495.12</v>
       </c>
       <c r="L59" t="n">
-        <v>7597.12</v>
+        <v>7563.56</v>
       </c>
       <c r="M59" t="n">
-        <v>7617.5</v>
+        <v>7617.88</v>
       </c>
       <c r="N59" t="n">
-        <v>7637.88</v>
+        <v>7672.19</v>
       </c>
       <c r="O59" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
+        <v>7754.75</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5487,55 +5483,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7557.5</v>
+        <v>7637</v>
       </c>
       <c r="C60" t="n">
-        <v>7654.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D60" t="n">
-        <v>7551.5</v>
+        <v>7625.25</v>
       </c>
       <c r="E60" t="n">
-        <v>7640</v>
+        <v>7657.35</v>
       </c>
       <c r="F60" t="n">
-        <v>83.5</v>
+        <v>17.35</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0023</v>
       </c>
       <c r="H60" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I60" t="n">
-        <v>7386.5</v>
+        <v>7448.5</v>
       </c>
       <c r="J60" t="n">
-        <v>7426.69</v>
+        <v>7555.5</v>
       </c>
       <c r="K60" t="n">
-        <v>7495.12</v>
+        <v>7588.5</v>
       </c>
       <c r="L60" t="n">
-        <v>7563.56</v>
+        <v>7621.5</v>
       </c>
       <c r="M60" t="n">
-        <v>7617.88</v>
+        <v>7691.5</v>
       </c>
       <c r="N60" t="n">
-        <v>7672.19</v>
+        <v>7761.5</v>
       </c>
       <c r="O60" t="n">
-        <v>7754.75</v>
+        <v>7757.5</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5576,50 +5576,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7637</v>
+        <v>7722</v>
       </c>
       <c r="C61" t="n">
-        <v>7670.25</v>
+        <v>7847.25</v>
       </c>
       <c r="D61" t="n">
-        <v>7625.25</v>
+        <v>7713.75</v>
       </c>
       <c r="E61" t="n">
-        <v>7657.35</v>
+        <v>7833.5</v>
       </c>
       <c r="F61" t="n">
-        <v>17.35</v>
+        <v>176.15</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.023</v>
       </c>
       <c r="H61" t="n">
-        <v>45</v>
+        <v>133.5</v>
       </c>
       <c r="I61" t="n">
-        <v>7448.5</v>
+        <v>7580.25</v>
       </c>
       <c r="J61" t="n">
-        <v>7555.5</v>
+        <v>7617.15</v>
       </c>
       <c r="K61" t="n">
-        <v>7588.5</v>
+        <v>7634.85</v>
       </c>
       <c r="L61" t="n">
-        <v>7621.5</v>
+        <v>7652.55</v>
       </c>
       <c r="M61" t="n">
-        <v>7691.5</v>
+        <v>7679.85</v>
       </c>
       <c r="N61" t="n">
-        <v>7761.5</v>
+        <v>7707.15</v>
       </c>
       <c r="O61" t="n">
-        <v>7757.5</v>
+        <v>7715.25</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5637,73 +5637,73 @@
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7722</v>
+        <v>7830</v>
       </c>
       <c r="C62" t="n">
-        <v>7847.25</v>
+        <v>7833.75</v>
       </c>
       <c r="D62" t="n">
-        <v>7713.75</v>
+        <v>7829</v>
       </c>
       <c r="E62" t="n">
-        <v>7833.5</v>
+        <v>7830.75</v>
       </c>
       <c r="F62" t="n">
-        <v>176.15</v>
+        <v>-2.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.023</v>
+        <v>-0.0004</v>
       </c>
       <c r="H62" t="n">
-        <v>133.5</v>
+        <v>4.75</v>
       </c>
       <c r="I62" t="n">
         <v>7580.25</v>
       </c>
       <c r="J62" t="n">
-        <v>7617.15</v>
+        <v>7726.5</v>
       </c>
       <c r="K62" t="n">
-        <v>7634.85</v>
+        <v>7766.75</v>
       </c>
       <c r="L62" t="n">
-        <v>7652.55</v>
+        <v>7807</v>
       </c>
       <c r="M62" t="n">
-        <v>7679.85</v>
+        <v>7900.25</v>
       </c>
       <c r="N62" t="n">
-        <v>7707.15</v>
+        <v>7993.5</v>
       </c>
       <c r="O62" t="n">
-        <v>7715.25</v>
+        <v>7980.75</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5716,110 +5716,26 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>7830</v>
-      </c>
-      <c r="C63" t="n">
-        <v>7848.5</v>
-      </c>
-      <c r="D63" t="n">
-        <v>7810.5</v>
-      </c>
-      <c r="E63" t="n">
-        <v>7829.75</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="H63" t="n">
-        <v>38</v>
-      </c>
-      <c r="I63" t="n">
-        <v>7580.25</v>
-      </c>
-      <c r="J63" t="n">
-        <v>7726.5</v>
-      </c>
-      <c r="K63" t="n">
-        <v>7766.75</v>
-      </c>
-      <c r="L63" t="n">
-        <v>7807</v>
-      </c>
-      <c r="M63" t="n">
-        <v>7900.25</v>
-      </c>
-      <c r="N63" t="n">
-        <v>7993.5</v>
-      </c>
-      <c r="O63" t="n">
-        <v>7980.75</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5667,22 +5667,22 @@
         <v>7830</v>
       </c>
       <c r="C62" t="n">
-        <v>7833.75</v>
+        <v>7834</v>
       </c>
       <c r="D62" t="n">
-        <v>7829</v>
+        <v>7827.75</v>
       </c>
       <c r="E62" t="n">
-        <v>7830.75</v>
+        <v>7832.75</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.75</v>
+        <v>-0.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="H62" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="I62" t="n">
         <v>7580.25</v>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5667,22 +5667,22 @@
         <v>7830</v>
       </c>
       <c r="C62" t="n">
-        <v>7834</v>
+        <v>7835.25</v>
       </c>
       <c r="D62" t="n">
         <v>7827.75</v>
       </c>
       <c r="E62" t="n">
-        <v>7832.75</v>
+        <v>7831.25</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.75</v>
+        <v>-2.25</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0003</v>
       </c>
       <c r="H62" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="I62" t="n">
         <v>7580.25</v>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5670,19 +5670,19 @@
         <v>7835.25</v>
       </c>
       <c r="D62" t="n">
-        <v>7827.75</v>
+        <v>7827.25</v>
       </c>
       <c r="E62" t="n">
-        <v>7831.25</v>
+        <v>7831.5</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.25</v>
+        <v>-2</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>-0.0003</v>
       </c>
       <c r="H62" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I62" t="n">
         <v>7580.25</v>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -5673,13 +5673,13 @@
         <v>7827.25</v>
       </c>
       <c r="E62" t="n">
-        <v>7831.5</v>
+        <v>7834.25</v>
       </c>
       <c r="F62" t="n">
-        <v>-2</v>
+        <v>0.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H62" t="n">
         <v>8</v>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5667,22 +5667,22 @@
         <v>7830</v>
       </c>
       <c r="C62" t="n">
-        <v>7835.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D62" t="n">
-        <v>7827.25</v>
+        <v>7810.5</v>
       </c>
       <c r="E62" t="n">
-        <v>7834.25</v>
+        <v>7831.75</v>
       </c>
       <c r="F62" t="n">
-        <v>0.75</v>
+        <v>-1.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="H62" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="I62" t="n">
         <v>7580.25</v>
@@ -5736,6 +5736,90 @@
       <c r="X62" t="inlineStr">
         <is>
           <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7830</v>
+      </c>
+      <c r="C63" t="n">
+        <v>7843.25</v>
+      </c>
+      <c r="D63" t="n">
+        <v>7818.75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>7820.75</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="H63" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>7772.5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>7794.88</v>
+      </c>
+      <c r="K63" t="n">
+        <v>7812.75</v>
+      </c>
+      <c r="L63" t="n">
+        <v>7830.62</v>
+      </c>
+      <c r="M63" t="n">
+        <v>7850.75</v>
+      </c>
+      <c r="N63" t="n">
+        <v>7870.88</v>
+      </c>
+      <c r="O63" t="n">
+        <v>7886.5</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7431</v>
+        <v>7398</v>
       </c>
       <c r="C2" t="n">
-        <v>7459.5</v>
+        <v>7505</v>
       </c>
       <c r="D2" t="n">
-        <v>7357.25</v>
+        <v>7398</v>
       </c>
       <c r="E2" t="n">
-        <v>7401.75</v>
+        <v>7500.25</v>
       </c>
       <c r="F2" t="n">
-        <v>-21.5</v>
+        <v>98.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0133</v>
       </c>
       <c r="H2" t="n">
-        <v>102.25</v>
+        <v>107</v>
       </c>
       <c r="I2" t="n">
-        <v>7285</v>
+        <v>7255</v>
       </c>
       <c r="J2" t="n">
-        <v>7307.75</v>
+        <v>7296.19</v>
       </c>
       <c r="K2" t="n">
-        <v>7370.5</v>
+        <v>7350.62</v>
       </c>
       <c r="L2" t="n">
-        <v>7433.25</v>
+        <v>7405.06</v>
       </c>
       <c r="M2" t="n">
-        <v>7476</v>
+        <v>7452.88</v>
       </c>
       <c r="N2" t="n">
-        <v>7518.75</v>
+        <v>7500.69</v>
       </c>
       <c r="O2" t="n">
-        <v>7601.5</v>
+        <v>7561.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,22 +685,24 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
@@ -709,59 +711,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7398</v>
+        <v>7495.5</v>
       </c>
       <c r="C3" t="n">
-        <v>7505</v>
+        <v>7567.75</v>
       </c>
       <c r="D3" t="n">
-        <v>7398</v>
+        <v>7481.75</v>
       </c>
       <c r="E3" t="n">
-        <v>7500.25</v>
+        <v>7548.25</v>
       </c>
       <c r="F3" t="n">
-        <v>98.5</v>
+        <v>48</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0064</v>
       </c>
       <c r="H3" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="I3" t="n">
-        <v>7255</v>
+        <v>7291</v>
       </c>
       <c r="J3" t="n">
-        <v>7296.19</v>
+        <v>7417.62</v>
       </c>
       <c r="K3" t="n">
-        <v>7350.62</v>
+        <v>7446.75</v>
       </c>
       <c r="L3" t="n">
-        <v>7405.06</v>
+        <v>7475.88</v>
       </c>
       <c r="M3" t="n">
-        <v>7452.88</v>
+        <v>7553.75</v>
       </c>
       <c r="N3" t="n">
-        <v>7500.69</v>
+        <v>7631.62</v>
       </c>
       <c r="O3" t="n">
-        <v>7561.75</v>
+        <v>7612</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,20 +770,18 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -800,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7495.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C4" t="n">
-        <v>7567.75</v>
+        <v>7579</v>
       </c>
       <c r="D4" t="n">
-        <v>7481.75</v>
+        <v>7505.75</v>
       </c>
       <c r="E4" t="n">
-        <v>7548.25</v>
+        <v>7543.5</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>-4.75</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0064</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>86</v>
+        <v>73.25</v>
       </c>
       <c r="I4" t="n">
-        <v>7291</v>
+        <v>7395.75</v>
       </c>
       <c r="J4" t="n">
-        <v>7417.62</v>
+        <v>7474</v>
       </c>
       <c r="K4" t="n">
-        <v>7446.75</v>
+        <v>7505.25</v>
       </c>
       <c r="L4" t="n">
-        <v>7475.88</v>
+        <v>7536.5</v>
       </c>
       <c r="M4" t="n">
-        <v>7553.75</v>
+        <v>7591.25</v>
       </c>
       <c r="N4" t="n">
-        <v>7631.62</v>
+        <v>7646</v>
       </c>
       <c r="O4" t="n">
-        <v>7612</v>
+        <v>7653.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,15 +850,13 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -875,55 +869,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7543.25</v>
+        <v>7536</v>
       </c>
       <c r="C5" t="n">
-        <v>7579</v>
+        <v>7593.75</v>
       </c>
       <c r="D5" t="n">
-        <v>7505.75</v>
+        <v>7479.5</v>
       </c>
       <c r="E5" t="n">
-        <v>7543.5</v>
+        <v>7528.25</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.75</v>
+        <v>-15.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="H5" t="n">
-        <v>73.25</v>
+        <v>114.25</v>
       </c>
       <c r="I5" t="n">
-        <v>7395.75</v>
+        <v>7432.5</v>
       </c>
       <c r="J5" t="n">
-        <v>7474</v>
+        <v>7470.81</v>
       </c>
       <c r="K5" t="n">
-        <v>7505.25</v>
+        <v>7506.88</v>
       </c>
       <c r="L5" t="n">
-        <v>7536.5</v>
+        <v>7542.94</v>
       </c>
       <c r="M5" t="n">
-        <v>7591.25</v>
+        <v>7580.12</v>
       </c>
       <c r="N5" t="n">
-        <v>7646</v>
+        <v>7617.31</v>
       </c>
       <c r="O5" t="n">
-        <v>7653.75</v>
+        <v>7652.25</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -931,16 +929,20 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -955,57 +957,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C6" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D6" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E6" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I6" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J6" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K6" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L6" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M6" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N6" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O6" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1013,19 +1015,17 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1039,78 +1039,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C7" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D7" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E7" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F7" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H7" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I7" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J7" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K7" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L7" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M7" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N7" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O7" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1123,55 +1121,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C8" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D8" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E8" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F8" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H8" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I8" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J8" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K8" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L8" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M8" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N8" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O8" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1186,7 +1188,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1214,72 +1216,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C9" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D9" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E9" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F9" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H9" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I9" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J9" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K9" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L9" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M9" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N9" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O9" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1291,59 +1291,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C10" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D10" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E10" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F10" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H10" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I10" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J10" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K10" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L10" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M10" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N10" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O10" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,7 +1350,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1380,69 +1376,71 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C11" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D11" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E11" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F11" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H11" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I11" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J11" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K11" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L11" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M11" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N11" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O11" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1455,77 +1453,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C12" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D12" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E12" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F12" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H12" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I12" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J12" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K12" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L12" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M12" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N12" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O12" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1539,57 +1539,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C13" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D13" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E13" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F13" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H13" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I13" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J13" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K13" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L13" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M13" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N13" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O13" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,7 +1600,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1621,78 +1621,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C14" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D14" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E14" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F14" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H14" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I14" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J14" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K14" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L14" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M14" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N14" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O14" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1705,55 +1703,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C15" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D15" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E15" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F15" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H15" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I15" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J15" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K15" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L15" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M15" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N15" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O15" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1768,7 +1770,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1789,79 +1791,77 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C16" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D16" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E16" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H16" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I16" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J16" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K16" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L16" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M16" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N16" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O16" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1875,57 +1875,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C17" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D17" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E17" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F17" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I17" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J17" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K17" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L17" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M17" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N17" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O17" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1946,8 +1946,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1959,57 +1961,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C18" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D18" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E18" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F18" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H18" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I18" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J18" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K18" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L18" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M18" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N18" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O18" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2017,23 +2019,21 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2052,56 +2052,60 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C19" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D19" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E19" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H19" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I19" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J19" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K19" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L19" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M19" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N19" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O19" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
@@ -2110,7 +2114,7 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2122,83 +2126,73 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C20" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D20" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E20" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F20" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H20" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I20" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J20" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K20" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L20" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M20" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N20" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O20" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>7687.25</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2215,55 +2209,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C21" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D21" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E21" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H21" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I21" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J21" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K21" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L21" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M21" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N21" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O21" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,16 +2272,20 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2302,50 +2304,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C22" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D22" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E22" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F22" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H22" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I22" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J22" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K22" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L22" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M22" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N22" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O22" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,18 +2360,14 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2388,67 +2386,75 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C23" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D23" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E23" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H23" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I23" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J23" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K23" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L23" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M23" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N23" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O23" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2463,86 +2469,82 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C24" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D24" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E24" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F24" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H24" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I24" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J24" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K24" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L24" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M24" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N24" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O24" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
@@ -2553,57 +2555,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C25" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D25" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E25" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F25" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H25" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I25" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J25" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K25" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L25" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M25" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N25" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O25" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2614,21 +2616,19 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2639,57 +2639,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C26" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D26" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E26" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F26" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H26" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I26" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J26" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K26" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L26" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M26" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N26" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O26" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2700,18 +2700,20 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2730,50 +2732,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C27" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D27" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E27" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F27" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H27" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I27" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J27" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K27" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L27" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M27" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N27" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O27" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2784,7 +2786,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2799,67 +2801,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C28" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D28" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E28" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F28" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H28" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I28" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J28" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K28" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L28" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M28" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N28" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O28" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2870,80 +2870,78 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C29" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D29" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E29" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F29" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H29" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I29" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J29" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K29" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L29" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M29" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N29" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O29" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2951,12 +2949,14 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2975,57 +2975,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C30" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D30" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E30" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F30" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H30" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I30" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J30" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K30" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L30" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M30" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N30" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O30" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3033,22 +3033,24 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3057,59 +3059,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C31" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D31" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E31" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F31" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H31" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I31" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J31" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K31" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L31" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M31" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N31" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O31" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3120,20 +3118,16 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3143,72 +3137,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C32" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D32" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E32" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F32" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H32" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I32" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J32" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K32" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L32" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M32" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N32" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O32" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3223,81 +3227,77 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C33" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D33" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E33" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H33" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I33" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J33" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K33" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L33" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M33" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N33" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O33" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3311,57 +3311,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C34" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D34" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E34" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F34" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H34" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I34" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J34" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K34" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L34" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M34" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N34" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O34" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3372,19 +3372,21 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3393,59 +3395,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C35" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D35" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E35" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F35" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H35" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I35" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J35" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K35" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L35" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M35" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N35" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O35" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3458,18 +3456,14 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3479,72 +3473,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C36" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D36" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E36" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F36" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H36" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I36" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J36" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K36" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L36" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M36" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N36" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O36" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3559,80 +3563,78 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C37" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D37" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E37" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F37" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H37" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I37" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J37" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K37" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L37" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M37" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N37" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O37" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3654,74 +3656,74 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C38" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D38" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E38" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F38" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H38" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I38" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J38" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K38" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L38" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M38" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N38" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O38" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
       </c>
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3733,81 +3735,81 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C39" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D39" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E39" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F39" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H39" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I39" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J39" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K39" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L39" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M39" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N39" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O39" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3819,79 +3821,77 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C40" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D40" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E40" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F40" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H40" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I40" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J40" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K40" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L40" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M40" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N40" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O40" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3905,57 +3905,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C41" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D41" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E41" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F41" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H41" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I41" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J41" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K41" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L41" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M41" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N41" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O41" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3963,18 +3963,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3989,57 +3989,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C42" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D42" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E42" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F42" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H42" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I42" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J42" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K42" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L42" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M42" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N42" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O42" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4047,21 +4047,23 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4071,59 +4073,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C43" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D43" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E43" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F43" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H43" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I43" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J43" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K43" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L43" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M43" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N43" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O43" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4134,20 +4132,16 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4157,55 +4151,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C44" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D44" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E44" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F44" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H44" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I44" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J44" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K44" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L44" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M44" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N44" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O44" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4216,78 +4214,80 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C45" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E45" t="n">
         <v>7722</v>
       </c>
-      <c r="C45" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D45" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E45" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F45" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H45" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I45" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J45" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K45" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L45" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M45" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N45" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O45" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4295,12 +4295,14 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
@@ -4308,70 +4310,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C46" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D46" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E46" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F46" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H46" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I46" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J46" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K46" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L46" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M46" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N46" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O46" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4384,15 +4386,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4407,70 +4407,74 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C47" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D47" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E47" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F47" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H47" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I47" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J47" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K47" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L47" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M47" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N47" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O47" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4484,88 +4488,80 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C48" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D48" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E48" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H48" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I48" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J48" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K48" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L48" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M48" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N48" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O48" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4577,55 +4573,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C49" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D49" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E49" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F49" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H49" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I49" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J49" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K49" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L49" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M49" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N49" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O49" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4636,21 +4636,25 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W49" s="11" t="inlineStr">
         <is>
@@ -4659,57 +4663,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C50" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D50" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E50" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F50" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H50" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I50" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J50" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K50" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L50" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M50" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N50" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O50" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4722,23 +4726,17 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="11" t="inlineStr">
         <is>
@@ -4747,57 +4745,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C51" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D51" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E51" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H51" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I51" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J51" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K51" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L51" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M51" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N51" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O51" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4805,12 +4803,14 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4827,59 +4827,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C52" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D52" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E52" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F52" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H52" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I52" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J52" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K52" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L52" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M52" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N52" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O52" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4892,7 +4888,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4916,50 +4912,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C53" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D53" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E53" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H53" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I53" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J53" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K53" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L53" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M53" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N53" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O53" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4972,7 +4968,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4996,50 +4992,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C54" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E54" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H54" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I54" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J54" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K54" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L54" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M54" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N54" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O54" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5047,22 +5043,24 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5071,55 +5069,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C55" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D55" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E55" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F55" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H55" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I55" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J55" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K55" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L55" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M55" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N55" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O55" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5127,23 +5129,21 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5153,59 +5153,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C56" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D56" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E56" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F56" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H56" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I56" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J56" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K56" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L56" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M56" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N56" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O56" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5218,7 +5214,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5242,69 +5238,75 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7631</v>
+        <v>7596.5</v>
       </c>
       <c r="C57" t="n">
-        <v>7633.25</v>
+        <v>7632</v>
       </c>
       <c r="D57" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7589.25</v>
+        <v>7556.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-35.75</v>
+        <v>-32.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0043</v>
       </c>
       <c r="H57" t="n">
-        <v>56.5</v>
+        <v>122.75</v>
       </c>
       <c r="I57" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J57" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K57" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L57" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M57" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N57" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O57" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+        <v>7689.75</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5322,76 +5324,70 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7596.5</v>
+        <v>7557.5</v>
       </c>
       <c r="C58" t="n">
-        <v>7632</v>
+        <v>7654.5</v>
       </c>
       <c r="D58" t="n">
-        <v>7509.25</v>
+        <v>7551.5</v>
       </c>
       <c r="E58" t="n">
-        <v>7556.5</v>
+        <v>7640</v>
       </c>
       <c r="F58" t="n">
-        <v>-32.75</v>
+        <v>83.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="H58" t="n">
-        <v>122.75</v>
+        <v>103</v>
       </c>
       <c r="I58" t="n">
-        <v>7520.25</v>
+        <v>7386.5</v>
       </c>
       <c r="J58" t="n">
-        <v>7524.88</v>
+        <v>7426.69</v>
       </c>
       <c r="K58" t="n">
-        <v>7561</v>
+        <v>7495.12</v>
       </c>
       <c r="L58" t="n">
-        <v>7597.12</v>
+        <v>7563.56</v>
       </c>
       <c r="M58" t="n">
-        <v>7617.5</v>
+        <v>7617.88</v>
       </c>
       <c r="N58" t="n">
-        <v>7637.88</v>
+        <v>7672.19</v>
       </c>
       <c r="O58" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
+        <v>7754.75</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5403,55 +5399,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7557.5</v>
+        <v>7637</v>
       </c>
       <c r="C59" t="n">
-        <v>7654.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D59" t="n">
-        <v>7551.5</v>
+        <v>7625.25</v>
       </c>
       <c r="E59" t="n">
-        <v>7640</v>
+        <v>7657.35</v>
       </c>
       <c r="F59" t="n">
-        <v>83.5</v>
+        <v>17.35</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0023</v>
       </c>
       <c r="H59" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I59" t="n">
-        <v>7386.5</v>
+        <v>7448.5</v>
       </c>
       <c r="J59" t="n">
-        <v>7426.69</v>
+        <v>7555.5</v>
       </c>
       <c r="K59" t="n">
-        <v>7495.12</v>
+        <v>7588.5</v>
       </c>
       <c r="L59" t="n">
-        <v>7563.56</v>
+        <v>7621.5</v>
       </c>
       <c r="M59" t="n">
-        <v>7617.88</v>
+        <v>7691.5</v>
       </c>
       <c r="N59" t="n">
-        <v>7672.19</v>
+        <v>7761.5</v>
       </c>
       <c r="O59" t="n">
-        <v>7754.75</v>
+        <v>7757.5</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5462,7 +5462,7 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5492,50 +5492,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7637</v>
+        <v>7722</v>
       </c>
       <c r="C60" t="n">
-        <v>7670.25</v>
+        <v>7847.25</v>
       </c>
       <c r="D60" t="n">
-        <v>7625.25</v>
+        <v>7713.75</v>
       </c>
       <c r="E60" t="n">
-        <v>7657.35</v>
+        <v>7833.5</v>
       </c>
       <c r="F60" t="n">
-        <v>17.35</v>
+        <v>176.15</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.023</v>
       </c>
       <c r="H60" t="n">
-        <v>45</v>
+        <v>133.5</v>
       </c>
       <c r="I60" t="n">
-        <v>7448.5</v>
+        <v>7580.25</v>
       </c>
       <c r="J60" t="n">
-        <v>7555.5</v>
+        <v>7617.15</v>
       </c>
       <c r="K60" t="n">
-        <v>7588.5</v>
+        <v>7634.85</v>
       </c>
       <c r="L60" t="n">
-        <v>7621.5</v>
+        <v>7652.55</v>
       </c>
       <c r="M60" t="n">
-        <v>7691.5</v>
+        <v>7679.85</v>
       </c>
       <c r="N60" t="n">
-        <v>7761.5</v>
+        <v>7707.15</v>
       </c>
       <c r="O60" t="n">
-        <v>7757.5</v>
+        <v>7715.25</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5546,80 +5546,80 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W60" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W60" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7722</v>
+        <v>7830</v>
       </c>
       <c r="C61" t="n">
-        <v>7847.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D61" t="n">
-        <v>7713.75</v>
+        <v>7810.5</v>
       </c>
       <c r="E61" t="n">
-        <v>7833.5</v>
+        <v>7831.75</v>
       </c>
       <c r="F61" t="n">
-        <v>176.15</v>
+        <v>-1.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.023</v>
+        <v>-0.0002</v>
       </c>
       <c r="H61" t="n">
-        <v>133.5</v>
+        <v>38</v>
       </c>
       <c r="I61" t="n">
         <v>7580.25</v>
       </c>
       <c r="J61" t="n">
-        <v>7617.15</v>
+        <v>7726.5</v>
       </c>
       <c r="K61" t="n">
-        <v>7634.85</v>
+        <v>7766.75</v>
       </c>
       <c r="L61" t="n">
-        <v>7652.55</v>
+        <v>7807</v>
       </c>
       <c r="M61" t="n">
-        <v>7679.85</v>
+        <v>7900.25</v>
       </c>
       <c r="N61" t="n">
-        <v>7707.15</v>
+        <v>7993.5</v>
       </c>
       <c r="O61" t="n">
-        <v>7715.25</v>
+        <v>7980.75</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5630,93 +5630,97 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7830</v>
+        <v>7774.75</v>
       </c>
       <c r="C62" t="n">
-        <v>7848.5</v>
+        <v>7778</v>
       </c>
       <c r="D62" t="n">
-        <v>7810.5</v>
+        <v>7773.5</v>
       </c>
       <c r="E62" t="n">
-        <v>7831.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.75</v>
+        <v>-55</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.007</v>
       </c>
       <c r="H62" t="n">
-        <v>38</v>
+        <v>4.5</v>
       </c>
       <c r="I62" t="n">
-        <v>7580.25</v>
+        <v>7772.5</v>
       </c>
       <c r="J62" t="n">
-        <v>7726.5</v>
+        <v>7794.88</v>
       </c>
       <c r="K62" t="n">
-        <v>7766.75</v>
+        <v>7812.75</v>
       </c>
       <c r="L62" t="n">
-        <v>7807</v>
+        <v>7830.62</v>
       </c>
       <c r="M62" t="n">
-        <v>7900.25</v>
+        <v>7850.75</v>
       </c>
       <c r="N62" t="n">
-        <v>7993.5</v>
+        <v>7870.88</v>
       </c>
       <c r="O62" t="n">
-        <v>7980.75</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+        <v>7886.5</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5728,100 +5732,12 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>7830</v>
-      </c>
-      <c r="C63" t="n">
-        <v>7843.25</v>
-      </c>
-      <c r="D63" t="n">
-        <v>7818.75</v>
-      </c>
-      <c r="E63" t="n">
-        <v>7820.75</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-11</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0014</v>
-      </c>
-      <c r="H63" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="I63" t="n">
-        <v>7772.5</v>
-      </c>
-      <c r="J63" t="n">
-        <v>7794.88</v>
-      </c>
-      <c r="K63" t="n">
-        <v>7812.75</v>
-      </c>
-      <c r="L63" t="n">
-        <v>7830.62</v>
-      </c>
-      <c r="M63" t="n">
-        <v>7850.75</v>
-      </c>
-      <c r="N63" t="n">
-        <v>7870.88</v>
-      </c>
-      <c r="O63" t="n">
-        <v>7886.5</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7398</v>
+        <v>7495.5</v>
       </c>
       <c r="C2" t="n">
-        <v>7505</v>
+        <v>7567.75</v>
       </c>
       <c r="D2" t="n">
-        <v>7398</v>
+        <v>7481.75</v>
       </c>
       <c r="E2" t="n">
-        <v>7500.25</v>
+        <v>7548.25</v>
       </c>
       <c r="F2" t="n">
-        <v>98.5</v>
+        <v>48</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0064</v>
       </c>
       <c r="H2" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="I2" t="n">
-        <v>7255</v>
+        <v>7291</v>
       </c>
       <c r="J2" t="n">
-        <v>7296.19</v>
+        <v>7417.62</v>
       </c>
       <c r="K2" t="n">
-        <v>7350.62</v>
+        <v>7446.75</v>
       </c>
       <c r="L2" t="n">
-        <v>7405.06</v>
+        <v>7475.88</v>
       </c>
       <c r="M2" t="n">
-        <v>7452.88</v>
+        <v>7553.75</v>
       </c>
       <c r="N2" t="n">
-        <v>7500.69</v>
+        <v>7631.62</v>
       </c>
       <c r="O2" t="n">
-        <v>7561.75</v>
+        <v>7612</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,13 +695,11 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -716,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7495.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C3" t="n">
-        <v>7567.75</v>
+        <v>7579</v>
       </c>
       <c r="D3" t="n">
-        <v>7481.75</v>
+        <v>7505.75</v>
       </c>
       <c r="E3" t="n">
-        <v>7548.25</v>
+        <v>7543.5</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>-4.75</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0064</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>86</v>
+        <v>73.25</v>
       </c>
       <c r="I3" t="n">
-        <v>7291</v>
+        <v>7395.75</v>
       </c>
       <c r="J3" t="n">
-        <v>7417.62</v>
+        <v>7474</v>
       </c>
       <c r="K3" t="n">
-        <v>7446.75</v>
+        <v>7505.25</v>
       </c>
       <c r="L3" t="n">
-        <v>7475.88</v>
+        <v>7536.5</v>
       </c>
       <c r="M3" t="n">
-        <v>7553.75</v>
+        <v>7591.25</v>
       </c>
       <c r="N3" t="n">
-        <v>7631.62</v>
+        <v>7646</v>
       </c>
       <c r="O3" t="n">
-        <v>7612</v>
+        <v>7653.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,13 +770,11 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -791,55 +787,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7543.25</v>
+        <v>7536</v>
       </c>
       <c r="C4" t="n">
-        <v>7579</v>
+        <v>7593.75</v>
       </c>
       <c r="D4" t="n">
-        <v>7505.75</v>
+        <v>7479.5</v>
       </c>
       <c r="E4" t="n">
-        <v>7543.5</v>
+        <v>7528.25</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.75</v>
+        <v>-15.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="H4" t="n">
-        <v>73.25</v>
+        <v>114.25</v>
       </c>
       <c r="I4" t="n">
-        <v>7395.75</v>
+        <v>7432.5</v>
       </c>
       <c r="J4" t="n">
-        <v>7474</v>
+        <v>7470.81</v>
       </c>
       <c r="K4" t="n">
-        <v>7505.25</v>
+        <v>7506.88</v>
       </c>
       <c r="L4" t="n">
-        <v>7536.5</v>
+        <v>7542.94</v>
       </c>
       <c r="M4" t="n">
-        <v>7591.25</v>
+        <v>7580.12</v>
       </c>
       <c r="N4" t="n">
-        <v>7646</v>
+        <v>7617.31</v>
       </c>
       <c r="O4" t="n">
-        <v>7653.75</v>
+        <v>7652.25</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -847,16 +847,20 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -871,57 +875,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C5" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D5" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E5" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I5" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J5" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K5" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L5" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M5" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N5" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O5" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -929,19 +933,17 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
@@ -955,79 +957,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C6" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D6" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E6" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F6" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H6" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I6" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J6" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K6" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L6" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M6" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N6" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O6" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1039,55 +1039,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C7" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D7" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E7" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F7" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H7" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I7" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J7" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K7" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L7" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M7" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N7" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O7" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1130,72 +1134,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C8" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D8" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E8" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F8" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H8" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I8" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J8" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K8" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L8" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M8" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N8" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O8" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1207,59 +1209,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C9" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D9" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E9" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H9" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I9" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J9" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K9" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L9" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M9" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N9" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O9" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1296,70 +1294,72 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C10" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D10" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E10" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F10" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H10" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I10" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J10" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K10" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L10" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M10" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N10" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O10" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1371,77 +1371,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C11" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D11" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E11" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F11" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H11" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I11" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J11" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K11" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L11" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M11" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N11" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O11" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1455,57 +1457,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C12" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D12" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E12" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F12" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H12" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I12" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J12" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K12" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L12" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M12" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N12" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O12" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1537,79 +1539,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C13" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D13" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E13" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F13" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H13" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I13" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J13" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K13" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L13" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M13" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N13" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O13" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="Q13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1621,55 +1621,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C14" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D14" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E14" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F14" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H14" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I14" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J14" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K14" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L14" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M14" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N14" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O14" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1705,79 +1709,77 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C15" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D15" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E15" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F15" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H15" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I15" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J15" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K15" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L15" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M15" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N15" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O15" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1791,57 +1793,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C16" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D16" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E16" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I16" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J16" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K16" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L16" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M16" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N16" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O16" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1852,9 +1854,9 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1862,8 +1864,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1875,57 +1879,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C17" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D17" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E17" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F17" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H17" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I17" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J17" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K17" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L17" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M17" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N17" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O17" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1933,23 +1937,21 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1968,65 +1970,69 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C18" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D18" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E18" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H18" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I18" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J18" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K18" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L18" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M18" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N18" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O18" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2038,83 +2044,73 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C19" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D19" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E19" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F19" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H19" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I19" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J19" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K19" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L19" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M19" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N19" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O19" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7687.25</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2131,55 +2127,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C20" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D20" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E20" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H20" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I20" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J20" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K20" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L20" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M20" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N20" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O20" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2195,11 +2195,15 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2218,50 +2222,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C21" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D21" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E21" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F21" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H21" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I21" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J21" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K21" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L21" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M21" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N21" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O21" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2272,20 +2276,16 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2304,67 +2304,75 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C22" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D22" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E22" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H22" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I22" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J22" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K22" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L22" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M22" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N22" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O22" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2379,86 +2387,82 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C23" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D23" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E23" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F23" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H23" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I23" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J23" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K23" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L23" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M23" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N23" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O23" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2469,57 +2473,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C24" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D24" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E24" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F24" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H24" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I24" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J24" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K24" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L24" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M24" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N24" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O24" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2537,14 +2541,12 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
@@ -2555,57 +2557,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C25" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D25" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E25" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F25" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H25" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I25" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J25" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K25" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L25" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M25" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N25" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O25" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2623,11 +2625,13 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2646,50 +2650,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C26" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D26" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E26" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F26" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H26" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I26" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J26" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K26" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L26" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M26" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N26" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O26" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2715,67 +2719,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C27" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D27" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E27" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F27" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H27" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I27" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J27" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K27" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L27" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M27" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N27" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O27" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2788,78 +2790,76 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C28" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D28" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E28" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F28" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H28" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I28" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J28" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K28" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L28" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M28" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N28" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O28" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2867,12 +2867,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2891,57 +2893,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C29" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D29" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E29" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F29" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H29" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I29" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J29" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K29" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L29" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M29" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N29" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O29" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2949,22 +2951,24 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
@@ -2973,59 +2977,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C30" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D30" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E30" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F30" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H30" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I30" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J30" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K30" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L30" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M30" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N30" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O30" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3038,18 +3038,14 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3059,72 +3055,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C31" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D31" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E31" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H31" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I31" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J31" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K31" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L31" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M31" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N31" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O31" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3139,81 +3145,77 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C32" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D32" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E32" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F32" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H32" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I32" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J32" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K32" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L32" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M32" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N32" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O32" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3227,57 +3229,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C33" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D33" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E33" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F33" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H33" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I33" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J33" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K33" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L33" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M33" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N33" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O33" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3295,12 +3297,14 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
@@ -3309,59 +3313,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C34" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D34" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E34" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F34" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H34" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I34" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J34" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K34" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L34" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M34" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N34" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O34" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3372,20 +3372,16 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3395,72 +3391,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C35" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D35" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E35" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F35" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H35" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I35" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J35" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K35" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L35" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M35" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N35" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O35" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3475,66 +3481,66 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C36" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D36" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E36" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F36" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H36" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I36" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J36" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K36" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L36" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M36" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N36" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O36" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3545,10 +3551,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3570,74 +3574,74 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C37" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D37" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E37" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F37" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H37" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I37" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J37" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K37" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L37" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M37" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N37" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O37" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
       </c>
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3649,81 +3653,81 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C38" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D38" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E38" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H38" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I38" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J38" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K38" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L38" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M38" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N38" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O38" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3735,79 +3739,77 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C39" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D39" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E39" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F39" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H39" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I39" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J39" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K39" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L39" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M39" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N39" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O39" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3821,57 +3823,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C40" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D40" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E40" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F40" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H40" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I40" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J40" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K40" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L40" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M40" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N40" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O40" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3879,18 +3881,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3905,57 +3907,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C41" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D41" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E41" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F41" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H41" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I41" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J41" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K41" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L41" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M41" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N41" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O41" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3963,21 +3965,23 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3987,59 +3991,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C42" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D42" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E42" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F42" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H42" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I42" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J42" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K42" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L42" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M42" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N42" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O42" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4052,18 +4052,14 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4073,55 +4069,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C43" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D43" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E43" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F43" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H43" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I43" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J43" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K43" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L43" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M43" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N43" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O43" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4134,76 +4134,78 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C44" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E44" t="n">
         <v>7722</v>
       </c>
-      <c r="C44" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D44" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E44" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F44" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H44" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I44" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J44" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K44" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L44" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M44" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N44" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O44" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4211,12 +4213,14 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
@@ -4224,70 +4228,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C45" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D45" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E45" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F45" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H45" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I45" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J45" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K45" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L45" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M45" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N45" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O45" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4305,10 +4309,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4323,67 +4325,71 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C46" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D46" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E46" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F46" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H46" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I46" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J46" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K46" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L46" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M46" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N46" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O46" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
@@ -4400,88 +4406,80 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C47" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D47" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E47" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H47" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I47" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J47" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K47" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L47" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M47" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N47" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O47" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4493,55 +4491,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C48" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D48" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E48" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F48" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H48" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I48" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J48" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K48" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L48" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M48" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N48" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O48" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4559,14 +4561,18 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W48" s="11" t="inlineStr">
         <is>
@@ -4575,57 +4581,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C49" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D49" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E49" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F49" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H49" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I49" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J49" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K49" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L49" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M49" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N49" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O49" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4636,25 +4642,19 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="11" t="inlineStr">
         <is>
@@ -4663,57 +4663,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C50" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D50" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E50" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H50" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I50" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J50" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K50" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L50" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M50" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N50" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O50" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4721,12 +4721,14 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4743,59 +4745,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C51" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D51" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E51" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F51" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H51" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I51" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J51" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K51" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L51" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M51" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N51" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O51" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4832,50 +4830,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C52" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D52" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E52" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H52" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I52" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J52" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K52" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L52" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M52" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N52" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O52" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4912,50 +4910,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C53" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D53" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E53" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H53" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I53" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J53" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K53" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L53" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M53" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N53" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O53" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4963,22 +4961,24 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
@@ -4987,55 +4987,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C54" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D54" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E54" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F54" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H54" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I54" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J54" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K54" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L54" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M54" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N54" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O54" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5043,24 +5047,22 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5069,59 +5071,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C55" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D55" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E55" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F55" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H55" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I55" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J55" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K55" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L55" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M55" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N55" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O55" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5158,56 +5156,60 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7631</v>
+        <v>7596.5</v>
       </c>
       <c r="C56" t="n">
-        <v>7633.25</v>
+        <v>7632</v>
       </c>
       <c r="D56" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E56" t="n">
-        <v>7589.25</v>
+        <v>7556.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-35.75</v>
+        <v>-32.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0043</v>
       </c>
       <c r="H56" t="n">
-        <v>56.5</v>
+        <v>122.75</v>
       </c>
       <c r="I56" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J56" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K56" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L56" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M56" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N56" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O56" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+        <v>7689.75</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
@@ -5219,8 +5221,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5238,76 +5242,70 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7596.5</v>
+        <v>7557.5</v>
       </c>
       <c r="C57" t="n">
-        <v>7632</v>
+        <v>7654.5</v>
       </c>
       <c r="D57" t="n">
-        <v>7509.25</v>
+        <v>7551.5</v>
       </c>
       <c r="E57" t="n">
-        <v>7556.5</v>
+        <v>7640</v>
       </c>
       <c r="F57" t="n">
-        <v>-32.75</v>
+        <v>83.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="H57" t="n">
-        <v>122.75</v>
+        <v>103</v>
       </c>
       <c r="I57" t="n">
-        <v>7520.25</v>
+        <v>7386.5</v>
       </c>
       <c r="J57" t="n">
-        <v>7524.88</v>
+        <v>7426.69</v>
       </c>
       <c r="K57" t="n">
-        <v>7561</v>
+        <v>7495.12</v>
       </c>
       <c r="L57" t="n">
-        <v>7597.12</v>
+        <v>7563.56</v>
       </c>
       <c r="M57" t="n">
-        <v>7617.5</v>
+        <v>7617.88</v>
       </c>
       <c r="N57" t="n">
-        <v>7637.88</v>
+        <v>7672.19</v>
       </c>
       <c r="O57" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
+        <v>7754.75</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5319,55 +5317,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7557.5</v>
+        <v>7637</v>
       </c>
       <c r="C58" t="n">
-        <v>7654.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D58" t="n">
-        <v>7551.5</v>
+        <v>7625.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7640</v>
+        <v>7657.35</v>
       </c>
       <c r="F58" t="n">
-        <v>83.5</v>
+        <v>17.35</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0023</v>
       </c>
       <c r="H58" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I58" t="n">
-        <v>7386.5</v>
+        <v>7448.5</v>
       </c>
       <c r="J58" t="n">
-        <v>7426.69</v>
+        <v>7555.5</v>
       </c>
       <c r="K58" t="n">
-        <v>7495.12</v>
+        <v>7588.5</v>
       </c>
       <c r="L58" t="n">
-        <v>7563.56</v>
+        <v>7621.5</v>
       </c>
       <c r="M58" t="n">
-        <v>7617.88</v>
+        <v>7691.5</v>
       </c>
       <c r="N58" t="n">
-        <v>7672.19</v>
+        <v>7761.5</v>
       </c>
       <c r="O58" t="n">
-        <v>7754.75</v>
+        <v>7757.5</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5408,50 +5410,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7637</v>
+        <v>7722</v>
       </c>
       <c r="C59" t="n">
-        <v>7670.25</v>
+        <v>7847.25</v>
       </c>
       <c r="D59" t="n">
-        <v>7625.25</v>
+        <v>7713.75</v>
       </c>
       <c r="E59" t="n">
-        <v>7657.35</v>
+        <v>7833.5</v>
       </c>
       <c r="F59" t="n">
-        <v>17.35</v>
+        <v>176.15</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.023</v>
       </c>
       <c r="H59" t="n">
-        <v>45</v>
+        <v>133.5</v>
       </c>
       <c r="I59" t="n">
-        <v>7448.5</v>
+        <v>7580.25</v>
       </c>
       <c r="J59" t="n">
-        <v>7555.5</v>
+        <v>7617.15</v>
       </c>
       <c r="K59" t="n">
-        <v>7588.5</v>
+        <v>7634.85</v>
       </c>
       <c r="L59" t="n">
-        <v>7621.5</v>
+        <v>7652.55</v>
       </c>
       <c r="M59" t="n">
-        <v>7691.5</v>
+        <v>7679.85</v>
       </c>
       <c r="N59" t="n">
-        <v>7761.5</v>
+        <v>7707.15</v>
       </c>
       <c r="O59" t="n">
-        <v>7757.5</v>
+        <v>7715.25</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5469,73 +5471,73 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W59" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W59" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7722</v>
+        <v>7830</v>
       </c>
       <c r="C60" t="n">
-        <v>7847.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D60" t="n">
-        <v>7713.75</v>
+        <v>7810.5</v>
       </c>
       <c r="E60" t="n">
-        <v>7833.5</v>
+        <v>7831.75</v>
       </c>
       <c r="F60" t="n">
-        <v>176.15</v>
+        <v>-1.75</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.023</v>
+        <v>-0.0002</v>
       </c>
       <c r="H60" t="n">
-        <v>133.5</v>
+        <v>38</v>
       </c>
       <c r="I60" t="n">
         <v>7580.25</v>
       </c>
       <c r="J60" t="n">
-        <v>7617.15</v>
+        <v>7726.5</v>
       </c>
       <c r="K60" t="n">
-        <v>7634.85</v>
+        <v>7766.75</v>
       </c>
       <c r="L60" t="n">
-        <v>7652.55</v>
+        <v>7807</v>
       </c>
       <c r="M60" t="n">
-        <v>7679.85</v>
+        <v>7900.25</v>
       </c>
       <c r="N60" t="n">
-        <v>7707.15</v>
+        <v>7993.5</v>
       </c>
       <c r="O60" t="n">
-        <v>7715.25</v>
+        <v>7980.75</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5548,91 +5550,95 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>7830</v>
       </c>
       <c r="C61" t="n">
-        <v>7848.5</v>
+        <v>7843.25</v>
       </c>
       <c r="D61" t="n">
-        <v>7810.5</v>
+        <v>7758.75</v>
       </c>
       <c r="E61" t="n">
-        <v>7831.75</v>
+        <v>7772.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.75</v>
+        <v>-59.25</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0076</v>
       </c>
       <c r="H61" t="n">
-        <v>38</v>
+        <v>84.5</v>
       </c>
       <c r="I61" t="n">
-        <v>7580.25</v>
+        <v>7772.5</v>
       </c>
       <c r="J61" t="n">
-        <v>7726.5</v>
+        <v>7794.88</v>
       </c>
       <c r="K61" t="n">
-        <v>7766.75</v>
+        <v>7812.75</v>
       </c>
       <c r="L61" t="n">
-        <v>7807</v>
+        <v>7830.62</v>
       </c>
       <c r="M61" t="n">
-        <v>7900.25</v>
+        <v>7850.75</v>
       </c>
       <c r="N61" t="n">
-        <v>7993.5</v>
+        <v>7870.88</v>
       </c>
       <c r="O61" t="n">
-        <v>7980.75</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>7886.5</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5644,83 +5650,73 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7774.75</v>
+        <v>7759</v>
       </c>
       <c r="C62" t="n">
-        <v>7778</v>
+        <v>7763.75</v>
       </c>
       <c r="D62" t="n">
-        <v>7773.5</v>
+        <v>7756.75</v>
       </c>
       <c r="E62" t="n">
-        <v>7776.75</v>
+        <v>7759</v>
       </c>
       <c r="F62" t="n">
-        <v>-55</v>
+        <v>-13.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0017</v>
       </c>
       <c r="H62" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="I62" t="n">
-        <v>7772.5</v>
+        <v>7674.25</v>
       </c>
       <c r="J62" t="n">
-        <v>7794.88</v>
+        <v>7673.75</v>
       </c>
       <c r="K62" t="n">
-        <v>7812.75</v>
+        <v>7730.25</v>
       </c>
       <c r="L62" t="n">
-        <v>7830.62</v>
+        <v>7786.75</v>
       </c>
       <c r="M62" t="n">
-        <v>7850.75</v>
+        <v>7814.75</v>
       </c>
       <c r="N62" t="n">
-        <v>7870.88</v>
+        <v>7842.75</v>
       </c>
       <c r="O62" t="n">
-        <v>7886.5</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7927.75</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7495.5</v>
+        <v>7543.25</v>
       </c>
       <c r="C2" t="n">
-        <v>7567.75</v>
+        <v>7579</v>
       </c>
       <c r="D2" t="n">
-        <v>7481.75</v>
+        <v>7505.75</v>
       </c>
       <c r="E2" t="n">
-        <v>7548.25</v>
+        <v>7543.5</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>-4.75</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0064</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>86</v>
+        <v>73.25</v>
       </c>
       <c r="I2" t="n">
-        <v>7291</v>
+        <v>7395.75</v>
       </c>
       <c r="J2" t="n">
-        <v>7417.62</v>
+        <v>7474</v>
       </c>
       <c r="K2" t="n">
-        <v>7446.75</v>
+        <v>7505.25</v>
       </c>
       <c r="L2" t="n">
-        <v>7475.88</v>
+        <v>7536.5</v>
       </c>
       <c r="M2" t="n">
-        <v>7553.75</v>
+        <v>7591.25</v>
       </c>
       <c r="N2" t="n">
-        <v>7631.62</v>
+        <v>7646</v>
       </c>
       <c r="O2" t="n">
-        <v>7612</v>
+        <v>7653.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,13 +690,11 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,55 +707,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7543.25</v>
+        <v>7536</v>
       </c>
       <c r="C3" t="n">
-        <v>7579</v>
+        <v>7593.75</v>
       </c>
       <c r="D3" t="n">
-        <v>7505.75</v>
+        <v>7479.5</v>
       </c>
       <c r="E3" t="n">
-        <v>7543.5</v>
+        <v>7528.25</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.75</v>
+        <v>-15.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="H3" t="n">
-        <v>73.25</v>
+        <v>114.25</v>
       </c>
       <c r="I3" t="n">
-        <v>7395.75</v>
+        <v>7432.5</v>
       </c>
       <c r="J3" t="n">
-        <v>7474</v>
+        <v>7470.81</v>
       </c>
       <c r="K3" t="n">
-        <v>7505.25</v>
+        <v>7506.88</v>
       </c>
       <c r="L3" t="n">
-        <v>7536.5</v>
+        <v>7542.94</v>
       </c>
       <c r="M3" t="n">
-        <v>7591.25</v>
+        <v>7580.12</v>
       </c>
       <c r="N3" t="n">
-        <v>7646</v>
+        <v>7617.31</v>
       </c>
       <c r="O3" t="n">
-        <v>7653.75</v>
+        <v>7652.25</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -765,16 +767,20 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -789,57 +795,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C4" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D4" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E4" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F4" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I4" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J4" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K4" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L4" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M4" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N4" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O4" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -847,19 +853,17 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -873,79 +877,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C5" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D5" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E5" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F5" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H5" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I5" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J5" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K5" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L5" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M5" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N5" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O5" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -957,55 +959,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C6" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D6" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E6" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F6" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H6" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I6" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J6" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K6" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L6" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M6" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N6" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O6" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1048,72 +1054,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C7" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D7" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E7" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F7" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H7" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I7" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J7" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K7" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L7" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M7" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N7" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O7" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1125,59 +1129,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C8" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D8" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E8" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H8" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I8" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J8" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K8" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L8" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M8" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N8" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O8" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1214,70 +1214,72 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C9" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D9" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E9" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F9" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I9" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J9" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K9" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L9" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M9" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N9" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O9" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1289,77 +1291,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C10" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D10" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E10" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F10" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H10" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I10" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J10" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K10" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L10" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M10" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N10" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O10" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1373,57 +1377,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C11" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D11" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E11" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F11" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H11" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I11" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J11" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K11" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L11" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M11" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N11" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O11" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1455,79 +1459,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C12" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D12" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E12" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F12" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H12" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I12" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J12" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K12" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L12" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M12" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N12" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O12" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1539,55 +1541,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C13" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D13" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E13" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F13" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H13" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I13" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J13" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K13" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L13" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M13" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N13" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O13" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1623,79 +1629,77 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C14" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D14" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E14" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F14" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H14" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I14" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J14" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K14" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L14" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M14" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N14" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O14" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1709,57 +1713,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C15" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D15" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E15" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I15" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J15" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K15" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L15" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M15" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N15" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O15" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1770,9 +1774,9 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -1780,8 +1784,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1793,57 +1799,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C16" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D16" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E16" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F16" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H16" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I16" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J16" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K16" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L16" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M16" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N16" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O16" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1851,23 +1857,21 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1886,65 +1890,69 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C17" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D17" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E17" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H17" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I17" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J17" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K17" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L17" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M17" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N17" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O17" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1956,83 +1964,73 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C18" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D18" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E18" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F18" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H18" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I18" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J18" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K18" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L18" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M18" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N18" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O18" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7687.25</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2049,55 +2047,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C19" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D19" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E19" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I19" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J19" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K19" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L19" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M19" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N19" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O19" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2113,11 +2115,15 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2136,50 +2142,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C20" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D20" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E20" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F20" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H20" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I20" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J20" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K20" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L20" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M20" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N20" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O20" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,20 +2196,16 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2222,67 +2224,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C21" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D21" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E21" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H21" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I21" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J21" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K21" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L21" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M21" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N21" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O21" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2297,86 +2307,82 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C22" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D22" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E22" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H22" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I22" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J22" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K22" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L22" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M22" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N22" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O22" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2387,57 +2393,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C23" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D23" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E23" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F23" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H23" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I23" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J23" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K23" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L23" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M23" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N23" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O23" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2455,14 +2461,12 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2473,57 +2477,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C24" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D24" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E24" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F24" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H24" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I24" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J24" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K24" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L24" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M24" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N24" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O24" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2541,11 +2545,13 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2564,50 +2570,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C25" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D25" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E25" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F25" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H25" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I25" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J25" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K25" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L25" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M25" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N25" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O25" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2633,67 +2639,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C26" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D26" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E26" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F26" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H26" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I26" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J26" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K26" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L26" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M26" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N26" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O26" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2706,78 +2710,76 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C27" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D27" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E27" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F27" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H27" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I27" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J27" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K27" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L27" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M27" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N27" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O27" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2785,12 +2787,14 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2809,57 +2813,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C28" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D28" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E28" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F28" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H28" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I28" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J28" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K28" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L28" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M28" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N28" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O28" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2867,22 +2871,24 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
@@ -2891,59 +2897,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C29" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D29" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E29" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F29" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H29" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I29" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J29" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K29" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L29" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M29" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N29" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O29" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2956,18 +2958,14 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2977,72 +2975,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C30" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D30" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E30" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F30" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H30" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I30" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J30" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K30" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L30" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M30" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N30" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O30" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3057,81 +3065,77 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C31" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D31" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E31" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H31" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I31" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J31" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K31" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L31" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M31" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N31" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O31" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3145,57 +3149,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C32" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D32" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E32" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F32" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H32" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I32" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J32" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K32" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L32" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M32" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N32" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O32" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3213,12 +3217,14 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
@@ -3227,59 +3233,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C33" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D33" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E33" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F33" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H33" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I33" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J33" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K33" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L33" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M33" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N33" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O33" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3290,20 +3292,16 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3313,72 +3311,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C34" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D34" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E34" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F34" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H34" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I34" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J34" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K34" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L34" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M34" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N34" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O34" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3393,66 +3401,66 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C35" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D35" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E35" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F35" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H35" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I35" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J35" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K35" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L35" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M35" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N35" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O35" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3463,10 +3471,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3488,74 +3494,74 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C36" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D36" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E36" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F36" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H36" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I36" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J36" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K36" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L36" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M36" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N36" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O36" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
       </c>
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3567,81 +3573,81 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C37" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D37" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E37" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F37" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H37" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I37" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J37" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K37" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L37" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M37" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N37" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O37" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3653,79 +3659,77 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C38" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D38" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E38" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F38" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H38" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I38" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J38" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K38" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L38" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M38" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N38" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O38" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3739,57 +3743,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C39" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D39" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E39" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F39" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H39" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I39" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J39" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K39" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L39" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M39" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N39" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O39" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3797,18 +3801,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3823,57 +3827,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C40" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D40" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E40" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F40" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H40" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I40" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J40" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K40" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L40" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M40" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N40" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O40" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3881,21 +3885,23 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3905,59 +3911,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C41" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D41" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E41" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F41" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H41" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I41" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J41" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K41" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L41" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M41" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N41" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O41" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3970,18 +3972,14 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3991,55 +3989,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C42" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D42" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E42" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F42" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H42" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I42" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J42" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K42" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L42" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M42" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N42" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O42" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4052,76 +4054,78 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E43" t="n">
         <v>7722</v>
       </c>
-      <c r="C43" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D43" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E43" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F43" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H43" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I43" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J43" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K43" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L43" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M43" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N43" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O43" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4129,12 +4133,14 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
@@ -4142,70 +4148,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C44" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D44" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E44" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F44" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H44" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I44" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J44" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K44" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L44" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M44" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N44" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O44" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4223,10 +4229,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4241,67 +4245,71 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C45" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D45" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E45" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F45" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H45" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I45" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J45" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K45" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L45" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M45" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N45" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O45" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
@@ -4318,88 +4326,80 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C46" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D46" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E46" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H46" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I46" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J46" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K46" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L46" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M46" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N46" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O46" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4411,55 +4411,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C47" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D47" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E47" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F47" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H47" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I47" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J47" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K47" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L47" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M47" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N47" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O47" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4477,14 +4481,18 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
@@ -4493,57 +4501,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C48" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D48" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E48" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F48" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H48" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I48" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J48" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K48" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L48" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M48" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N48" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O48" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4554,25 +4562,19 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="11" t="inlineStr">
         <is>
@@ -4581,57 +4583,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C49" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D49" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E49" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H49" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I49" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J49" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K49" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L49" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M49" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N49" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O49" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4639,12 +4641,14 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4661,59 +4665,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C50" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D50" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E50" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F50" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H50" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I50" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J50" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K50" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L50" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M50" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N50" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O50" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4750,50 +4750,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C51" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D51" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E51" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H51" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I51" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J51" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K51" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L51" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M51" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N51" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O51" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4830,50 +4830,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C52" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D52" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E52" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H52" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I52" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J52" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K52" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L52" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M52" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N52" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O52" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4881,22 +4881,24 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4905,55 +4907,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C53" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D53" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E53" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F53" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H53" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I53" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J53" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K53" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L53" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M53" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N53" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O53" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4961,24 +4967,22 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
@@ -4987,59 +4991,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C54" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D54" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E54" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F54" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H54" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I54" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J54" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K54" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L54" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M54" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N54" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O54" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5076,56 +5076,60 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7631</v>
+        <v>7596.5</v>
       </c>
       <c r="C55" t="n">
-        <v>7633.25</v>
+        <v>7632</v>
       </c>
       <c r="D55" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E55" t="n">
-        <v>7589.25</v>
+        <v>7556.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-35.75</v>
+        <v>-32.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0043</v>
       </c>
       <c r="H55" t="n">
-        <v>56.5</v>
+        <v>122.75</v>
       </c>
       <c r="I55" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J55" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K55" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L55" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M55" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N55" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O55" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+        <v>7689.75</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5137,8 +5141,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5156,76 +5162,70 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7596.5</v>
+        <v>7557.5</v>
       </c>
       <c r="C56" t="n">
-        <v>7632</v>
+        <v>7654.5</v>
       </c>
       <c r="D56" t="n">
-        <v>7509.25</v>
+        <v>7551.5</v>
       </c>
       <c r="E56" t="n">
-        <v>7556.5</v>
+        <v>7640</v>
       </c>
       <c r="F56" t="n">
-        <v>-32.75</v>
+        <v>83.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="H56" t="n">
-        <v>122.75</v>
+        <v>103</v>
       </c>
       <c r="I56" t="n">
-        <v>7520.25</v>
+        <v>7386.5</v>
       </c>
       <c r="J56" t="n">
-        <v>7524.88</v>
+        <v>7426.69</v>
       </c>
       <c r="K56" t="n">
-        <v>7561</v>
+        <v>7495.12</v>
       </c>
       <c r="L56" t="n">
-        <v>7597.12</v>
+        <v>7563.56</v>
       </c>
       <c r="M56" t="n">
-        <v>7617.5</v>
+        <v>7617.88</v>
       </c>
       <c r="N56" t="n">
-        <v>7637.88</v>
+        <v>7672.19</v>
       </c>
       <c r="O56" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
+        <v>7754.75</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5237,55 +5237,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7557.5</v>
+        <v>7637</v>
       </c>
       <c r="C57" t="n">
-        <v>7654.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D57" t="n">
-        <v>7551.5</v>
+        <v>7625.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7640</v>
+        <v>7657.35</v>
       </c>
       <c r="F57" t="n">
-        <v>83.5</v>
+        <v>17.35</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0023</v>
       </c>
       <c r="H57" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I57" t="n">
-        <v>7386.5</v>
+        <v>7448.5</v>
       </c>
       <c r="J57" t="n">
-        <v>7426.69</v>
+        <v>7555.5</v>
       </c>
       <c r="K57" t="n">
-        <v>7495.12</v>
+        <v>7588.5</v>
       </c>
       <c r="L57" t="n">
-        <v>7563.56</v>
+        <v>7621.5</v>
       </c>
       <c r="M57" t="n">
-        <v>7617.88</v>
+        <v>7691.5</v>
       </c>
       <c r="N57" t="n">
-        <v>7672.19</v>
+        <v>7761.5</v>
       </c>
       <c r="O57" t="n">
-        <v>7754.75</v>
+        <v>7757.5</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5326,50 +5330,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7637</v>
+        <v>7722</v>
       </c>
       <c r="C58" t="n">
-        <v>7670.25</v>
+        <v>7847.25</v>
       </c>
       <c r="D58" t="n">
-        <v>7625.25</v>
+        <v>7713.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7657.35</v>
+        <v>7833.5</v>
       </c>
       <c r="F58" t="n">
-        <v>17.35</v>
+        <v>176.15</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.023</v>
       </c>
       <c r="H58" t="n">
-        <v>45</v>
+        <v>133.5</v>
       </c>
       <c r="I58" t="n">
-        <v>7448.5</v>
+        <v>7580.25</v>
       </c>
       <c r="J58" t="n">
-        <v>7555.5</v>
+        <v>7617.15</v>
       </c>
       <c r="K58" t="n">
-        <v>7588.5</v>
+        <v>7634.85</v>
       </c>
       <c r="L58" t="n">
-        <v>7621.5</v>
+        <v>7652.55</v>
       </c>
       <c r="M58" t="n">
-        <v>7691.5</v>
+        <v>7679.85</v>
       </c>
       <c r="N58" t="n">
-        <v>7761.5</v>
+        <v>7707.15</v>
       </c>
       <c r="O58" t="n">
-        <v>7757.5</v>
+        <v>7715.25</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5387,73 +5391,73 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7722</v>
+        <v>7830</v>
       </c>
       <c r="C59" t="n">
-        <v>7847.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D59" t="n">
-        <v>7713.75</v>
+        <v>7810.5</v>
       </c>
       <c r="E59" t="n">
-        <v>7833.5</v>
+        <v>7831.75</v>
       </c>
       <c r="F59" t="n">
-        <v>176.15</v>
+        <v>-1.75</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.023</v>
+        <v>-0.0002</v>
       </c>
       <c r="H59" t="n">
-        <v>133.5</v>
+        <v>38</v>
       </c>
       <c r="I59" t="n">
         <v>7580.25</v>
       </c>
       <c r="J59" t="n">
-        <v>7617.15</v>
+        <v>7726.5</v>
       </c>
       <c r="K59" t="n">
-        <v>7634.85</v>
+        <v>7766.75</v>
       </c>
       <c r="L59" t="n">
-        <v>7652.55</v>
+        <v>7807</v>
       </c>
       <c r="M59" t="n">
-        <v>7679.85</v>
+        <v>7900.25</v>
       </c>
       <c r="N59" t="n">
-        <v>7707.15</v>
+        <v>7993.5</v>
       </c>
       <c r="O59" t="n">
-        <v>7715.25</v>
+        <v>7980.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5466,91 +5470,95 @@
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>7830</v>
       </c>
       <c r="C60" t="n">
-        <v>7848.5</v>
+        <v>7843.25</v>
       </c>
       <c r="D60" t="n">
-        <v>7810.5</v>
+        <v>7758.75</v>
       </c>
       <c r="E60" t="n">
-        <v>7831.75</v>
+        <v>7772.5</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.75</v>
+        <v>-59.25</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0076</v>
       </c>
       <c r="H60" t="n">
-        <v>38</v>
+        <v>84.5</v>
       </c>
       <c r="I60" t="n">
-        <v>7580.25</v>
+        <v>7772.5</v>
       </c>
       <c r="J60" t="n">
-        <v>7726.5</v>
+        <v>7794.88</v>
       </c>
       <c r="K60" t="n">
-        <v>7766.75</v>
+        <v>7812.75</v>
       </c>
       <c r="L60" t="n">
-        <v>7807</v>
+        <v>7830.62</v>
       </c>
       <c r="M60" t="n">
-        <v>7900.25</v>
+        <v>7850.75</v>
       </c>
       <c r="N60" t="n">
-        <v>7993.5</v>
+        <v>7870.88</v>
       </c>
       <c r="O60" t="n">
-        <v>7980.75</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>7886.5</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5562,83 +5570,75 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W60" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7830</v>
+        <v>7774.75</v>
       </c>
       <c r="C61" t="n">
-        <v>7843.25</v>
+        <v>7783.5</v>
       </c>
       <c r="D61" t="n">
-        <v>7758.75</v>
+        <v>7707.25</v>
       </c>
       <c r="E61" t="n">
-        <v>7772.5</v>
+        <v>7767</v>
       </c>
       <c r="F61" t="n">
-        <v>-59.25</v>
+        <v>-5.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0076</v>
+        <v>-0.0007</v>
       </c>
       <c r="H61" t="n">
-        <v>84.5</v>
+        <v>76.25</v>
       </c>
       <c r="I61" t="n">
-        <v>7772.5</v>
+        <v>7674.25</v>
       </c>
       <c r="J61" t="n">
-        <v>7794.88</v>
+        <v>7673.75</v>
       </c>
       <c r="K61" t="n">
-        <v>7812.75</v>
+        <v>7730.25</v>
       </c>
       <c r="L61" t="n">
-        <v>7830.62</v>
+        <v>7786.75</v>
       </c>
       <c r="M61" t="n">
-        <v>7850.75</v>
+        <v>7814.75</v>
       </c>
       <c r="N61" t="n">
-        <v>7870.88</v>
+        <v>7842.75</v>
       </c>
       <c r="O61" t="n">
-        <v>7886.5</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="inlineStr">
+        <v>7927.75</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5660,80 +5660,168 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>7759</v>
       </c>
       <c r="C62" t="n">
-        <v>7763.75</v>
+        <v>7814.75</v>
       </c>
       <c r="D62" t="n">
-        <v>7756.75</v>
+        <v>7748.5</v>
       </c>
       <c r="E62" t="n">
-        <v>7759</v>
+        <v>7803.75</v>
       </c>
       <c r="F62" t="n">
-        <v>-13.5</v>
+        <v>36.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0047</v>
       </c>
       <c r="H62" t="n">
-        <v>7</v>
+        <v>66.25</v>
       </c>
       <c r="I62" t="n">
-        <v>7674.25</v>
+        <v>7631</v>
       </c>
       <c r="J62" t="n">
-        <v>7673.75</v>
+        <v>7701.56</v>
       </c>
       <c r="K62" t="n">
-        <v>7730.25</v>
+        <v>7728.88</v>
       </c>
       <c r="L62" t="n">
+        <v>7756.19</v>
+      </c>
+      <c r="M62" t="n">
+        <v>7805.12</v>
+      </c>
+      <c r="N62" t="n">
+        <v>7854.06</v>
+      </c>
+      <c r="O62" t="n">
+        <v>7859.75</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7796</v>
+      </c>
+      <c r="C63" t="n">
+        <v>7803</v>
+      </c>
+      <c r="D63" t="n">
         <v>7786.75</v>
       </c>
-      <c r="M62" t="n">
-        <v>7814.75</v>
-      </c>
-      <c r="N62" t="n">
-        <v>7842.75</v>
-      </c>
-      <c r="O62" t="n">
-        <v>7927.75</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="E63" t="n">
+        <v>7803.75</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="I63" t="n">
+        <v>7682.25</v>
+      </c>
+      <c r="J63" t="n">
+        <v>7748.56</v>
+      </c>
+      <c r="K63" t="n">
+        <v>7770.62</v>
+      </c>
+      <c r="L63" t="n">
+        <v>7792.69</v>
+      </c>
+      <c r="M63" t="n">
+        <v>7836.88</v>
+      </c>
+      <c r="N63" t="n">
+        <v>7881.06</v>
+      </c>
+      <c r="O63" t="n">
+        <v>7881</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7543.25</v>
+        <v>7536</v>
       </c>
       <c r="C2" t="n">
-        <v>7579</v>
+        <v>7593.75</v>
       </c>
       <c r="D2" t="n">
-        <v>7505.75</v>
+        <v>7479.5</v>
       </c>
       <c r="E2" t="n">
-        <v>7543.5</v>
+        <v>7528.25</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.75</v>
+        <v>-15.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="H2" t="n">
-        <v>73.25</v>
+        <v>114.25</v>
       </c>
       <c r="I2" t="n">
-        <v>7395.75</v>
+        <v>7432.5</v>
       </c>
       <c r="J2" t="n">
-        <v>7474</v>
+        <v>7470.81</v>
       </c>
       <c r="K2" t="n">
-        <v>7505.25</v>
+        <v>7506.88</v>
       </c>
       <c r="L2" t="n">
-        <v>7536.5</v>
+        <v>7542.94</v>
       </c>
       <c r="M2" t="n">
-        <v>7591.25</v>
+        <v>7580.12</v>
       </c>
       <c r="N2" t="n">
-        <v>7646</v>
+        <v>7617.31</v>
       </c>
       <c r="O2" t="n">
-        <v>7653.75</v>
+        <v>7652.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,16 +685,20 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,57 +713,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C3" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D3" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E3" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I3" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J3" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K3" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L3" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M3" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N3" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O3" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -767,19 +771,17 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -793,78 +795,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C4" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D4" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E4" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F4" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H4" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I4" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J4" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K4" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L4" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M4" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N4" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O4" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -877,55 +877,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C5" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D5" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E5" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F5" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H5" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I5" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J5" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K5" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L5" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M5" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N5" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O5" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,7 +944,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -968,72 +972,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C6" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D6" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E6" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F6" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H6" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I6" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J6" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K6" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L6" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M6" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N6" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O6" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1045,59 +1047,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C7" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D7" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E7" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H7" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I7" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J7" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K7" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L7" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M7" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N7" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O7" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,7 +1106,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1134,69 +1132,71 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C8" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D8" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E8" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F8" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H8" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I8" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J8" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K8" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L8" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M8" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N8" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O8" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1209,77 +1209,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C9" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D9" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E9" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F9" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H9" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I9" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J9" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K9" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L9" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M9" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N9" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O9" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1293,57 +1295,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C10" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D10" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E10" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F10" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H10" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I10" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J10" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K10" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L10" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M10" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N10" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O10" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,7 +1356,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1375,78 +1377,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C11" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D11" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E11" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F11" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H11" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I11" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J11" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K11" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L11" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M11" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N11" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O11" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1459,55 +1459,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C12" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D12" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E12" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F12" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H12" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I12" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J12" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K12" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L12" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M12" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N12" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O12" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1522,7 +1526,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1543,79 +1547,77 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C13" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D13" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E13" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F13" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H13" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I13" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J13" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K13" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L13" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M13" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N13" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O13" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1629,57 +1631,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C14" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D14" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E14" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I14" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J14" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K14" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L14" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M14" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N14" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O14" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1692,7 +1694,7 @@
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
@@ -1700,8 +1702,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1713,57 +1717,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C15" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D15" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E15" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F15" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H15" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I15" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J15" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K15" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L15" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M15" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N15" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O15" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,23 +1775,21 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1806,56 +1808,60 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C16" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D16" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E16" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H16" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I16" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J16" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K16" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L16" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M16" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N16" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O16" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
@@ -1864,7 +1870,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1876,83 +1882,73 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C17" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D17" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E17" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H17" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I17" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J17" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K17" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L17" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M17" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N17" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O17" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>7687.25</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1969,55 +1965,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C18" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D18" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E18" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H18" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I18" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J18" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K18" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L18" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M18" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N18" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O18" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2028,16 +2028,20 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2056,50 +2060,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C19" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D19" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E19" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F19" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H19" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I19" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J19" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K19" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L19" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M19" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N19" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O19" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2112,18 +2116,14 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2142,67 +2142,75 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C20" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D20" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E20" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H20" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I20" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J20" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K20" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L20" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M20" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N20" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O20" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2217,86 +2225,82 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C21" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D21" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E21" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H21" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I21" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J21" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K21" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L21" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M21" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N21" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O21" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2307,57 +2311,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C22" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D22" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E22" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F22" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H22" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I22" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J22" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K22" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L22" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M22" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N22" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O22" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2368,21 +2372,19 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2393,57 +2395,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C23" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D23" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E23" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F23" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H23" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I23" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J23" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K23" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L23" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M23" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N23" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O23" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2454,18 +2456,20 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2484,50 +2488,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C24" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D24" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E24" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F24" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H24" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I24" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J24" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K24" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L24" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M24" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N24" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O24" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2538,7 +2542,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2553,67 +2557,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C25" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D25" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E25" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F25" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H25" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I25" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J25" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K25" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L25" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M25" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N25" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O25" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2624,80 +2626,78 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C26" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D26" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E26" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F26" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H26" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I26" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J26" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K26" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L26" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M26" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N26" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O26" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2705,12 +2705,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2729,57 +2731,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C27" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D27" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E27" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F27" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H27" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I27" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J27" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K27" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L27" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M27" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N27" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O27" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2787,22 +2789,24 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
@@ -2811,59 +2815,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C28" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D28" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E28" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F28" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H28" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I28" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J28" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K28" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L28" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M28" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N28" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O28" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2874,20 +2874,16 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2897,72 +2893,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C29" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D29" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E29" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F29" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H29" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I29" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J29" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K29" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L29" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M29" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N29" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O29" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2977,81 +2983,77 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C30" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D30" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E30" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F30" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H30" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I30" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J30" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K30" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L30" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M30" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N30" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O30" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3065,57 +3067,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C31" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D31" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E31" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F31" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H31" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I31" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J31" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K31" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L31" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M31" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N31" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O31" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3126,19 +3128,21 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
@@ -3147,59 +3151,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C32" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D32" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E32" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F32" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H32" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I32" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J32" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K32" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L32" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M32" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N32" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O32" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3212,18 +3212,14 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3233,72 +3229,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C33" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D33" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E33" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F33" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H33" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I33" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J33" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K33" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L33" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M33" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N33" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O33" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3313,80 +3319,78 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C34" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D34" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E34" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F34" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H34" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I34" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J34" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K34" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L34" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M34" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N34" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O34" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3408,74 +3412,74 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C35" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D35" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E35" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F35" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H35" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I35" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J35" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K35" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L35" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M35" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N35" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O35" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
       </c>
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3487,81 +3491,81 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C36" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D36" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E36" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F36" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H36" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I36" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J36" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K36" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L36" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M36" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N36" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O36" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3573,79 +3577,77 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C37" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D37" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E37" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F37" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H37" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I37" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J37" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K37" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L37" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M37" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N37" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O37" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3659,57 +3661,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C38" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D38" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E38" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F38" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H38" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I38" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J38" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K38" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L38" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M38" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N38" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O38" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3717,18 +3719,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3743,57 +3745,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C39" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D39" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E39" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F39" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H39" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I39" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J39" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K39" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L39" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M39" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N39" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O39" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3801,21 +3803,23 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3825,59 +3829,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C40" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D40" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E40" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F40" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H40" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I40" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J40" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K40" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L40" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M40" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N40" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O40" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3888,20 +3888,16 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3911,55 +3907,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C41" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D41" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E41" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F41" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H41" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I41" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J41" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K41" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L41" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M41" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N41" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O41" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3970,78 +3970,80 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C42" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E42" t="n">
         <v>7722</v>
       </c>
-      <c r="C42" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D42" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E42" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F42" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H42" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I42" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J42" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K42" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L42" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M42" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N42" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O42" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4049,12 +4051,14 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
@@ -4062,70 +4066,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C43" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D43" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E43" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F43" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H43" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I43" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J43" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K43" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L43" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M43" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N43" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O43" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4138,15 +4142,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4161,70 +4163,74 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C44" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D44" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E44" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F44" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H44" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I44" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J44" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K44" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L44" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M44" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N44" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O44" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4238,88 +4244,80 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C45" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D45" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E45" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F45" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H45" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I45" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J45" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K45" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L45" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M45" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N45" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O45" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4331,55 +4329,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C46" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D46" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E46" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F46" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H46" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I46" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J46" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K46" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L46" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M46" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N46" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O46" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4390,21 +4392,25 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W46" s="11" t="inlineStr">
         <is>
@@ -4413,57 +4419,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C47" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D47" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E47" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F47" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H47" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I47" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J47" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K47" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L47" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M47" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N47" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O47" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4476,23 +4482,17 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
@@ -4501,57 +4501,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C48" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D48" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E48" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H48" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I48" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J48" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K48" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L48" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M48" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N48" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O48" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4559,12 +4559,14 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4581,59 +4583,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C49" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D49" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E49" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F49" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H49" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I49" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J49" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K49" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L49" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M49" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N49" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O49" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4646,7 +4644,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4670,50 +4668,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C50" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D50" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E50" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H50" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I50" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J50" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K50" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L50" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M50" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N50" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O50" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4726,7 +4724,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4750,50 +4748,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C51" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D51" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E51" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H51" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I51" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J51" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K51" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L51" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M51" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N51" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O51" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4801,22 +4799,24 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4825,55 +4825,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C52" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D52" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E52" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F52" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H52" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I52" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J52" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K52" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L52" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M52" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N52" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O52" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4881,23 +4885,21 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4907,59 +4909,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C53" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D53" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E53" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F53" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H53" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I53" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J53" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K53" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L53" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M53" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N53" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O53" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4972,7 +4970,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4996,69 +4994,75 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7631</v>
+        <v>7596.5</v>
       </c>
       <c r="C54" t="n">
-        <v>7633.25</v>
+        <v>7632</v>
       </c>
       <c r="D54" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E54" t="n">
-        <v>7589.25</v>
+        <v>7556.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-35.75</v>
+        <v>-32.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0043</v>
       </c>
       <c r="H54" t="n">
-        <v>56.5</v>
+        <v>122.75</v>
       </c>
       <c r="I54" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J54" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K54" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L54" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M54" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N54" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O54" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+        <v>7689.75</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5076,76 +5080,70 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7596.5</v>
+        <v>7557.5</v>
       </c>
       <c r="C55" t="n">
-        <v>7632</v>
+        <v>7654.5</v>
       </c>
       <c r="D55" t="n">
-        <v>7509.25</v>
+        <v>7551.5</v>
       </c>
       <c r="E55" t="n">
-        <v>7556.5</v>
+        <v>7640</v>
       </c>
       <c r="F55" t="n">
-        <v>-32.75</v>
+        <v>83.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="H55" t="n">
-        <v>122.75</v>
+        <v>103</v>
       </c>
       <c r="I55" t="n">
-        <v>7520.25</v>
+        <v>7386.5</v>
       </c>
       <c r="J55" t="n">
-        <v>7524.88</v>
+        <v>7426.69</v>
       </c>
       <c r="K55" t="n">
-        <v>7561</v>
+        <v>7495.12</v>
       </c>
       <c r="L55" t="n">
-        <v>7597.12</v>
+        <v>7563.56</v>
       </c>
       <c r="M55" t="n">
-        <v>7617.5</v>
+        <v>7617.88</v>
       </c>
       <c r="N55" t="n">
-        <v>7637.88</v>
+        <v>7672.19</v>
       </c>
       <c r="O55" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
+        <v>7754.75</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5157,55 +5155,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7557.5</v>
+        <v>7637</v>
       </c>
       <c r="C56" t="n">
-        <v>7654.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D56" t="n">
-        <v>7551.5</v>
+        <v>7625.25</v>
       </c>
       <c r="E56" t="n">
-        <v>7640</v>
+        <v>7657.35</v>
       </c>
       <c r="F56" t="n">
-        <v>83.5</v>
+        <v>17.35</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0023</v>
       </c>
       <c r="H56" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I56" t="n">
-        <v>7386.5</v>
+        <v>7448.5</v>
       </c>
       <c r="J56" t="n">
-        <v>7426.69</v>
+        <v>7555.5</v>
       </c>
       <c r="K56" t="n">
-        <v>7495.12</v>
+        <v>7588.5</v>
       </c>
       <c r="L56" t="n">
-        <v>7563.56</v>
+        <v>7621.5</v>
       </c>
       <c r="M56" t="n">
-        <v>7617.88</v>
+        <v>7691.5</v>
       </c>
       <c r="N56" t="n">
-        <v>7672.19</v>
+        <v>7761.5</v>
       </c>
       <c r="O56" t="n">
-        <v>7754.75</v>
+        <v>7757.5</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5216,7 +5218,7 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5246,50 +5248,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7637</v>
+        <v>7722</v>
       </c>
       <c r="C57" t="n">
-        <v>7670.25</v>
+        <v>7847.25</v>
       </c>
       <c r="D57" t="n">
-        <v>7625.25</v>
+        <v>7713.75</v>
       </c>
       <c r="E57" t="n">
-        <v>7657.35</v>
+        <v>7833.5</v>
       </c>
       <c r="F57" t="n">
-        <v>17.35</v>
+        <v>176.15</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.023</v>
       </c>
       <c r="H57" t="n">
-        <v>45</v>
+        <v>133.5</v>
       </c>
       <c r="I57" t="n">
-        <v>7448.5</v>
+        <v>7580.25</v>
       </c>
       <c r="J57" t="n">
-        <v>7555.5</v>
+        <v>7617.15</v>
       </c>
       <c r="K57" t="n">
-        <v>7588.5</v>
+        <v>7634.85</v>
       </c>
       <c r="L57" t="n">
-        <v>7621.5</v>
+        <v>7652.55</v>
       </c>
       <c r="M57" t="n">
-        <v>7691.5</v>
+        <v>7679.85</v>
       </c>
       <c r="N57" t="n">
-        <v>7761.5</v>
+        <v>7707.15</v>
       </c>
       <c r="O57" t="n">
-        <v>7757.5</v>
+        <v>7715.25</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5300,80 +5302,80 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7722</v>
+        <v>7830</v>
       </c>
       <c r="C58" t="n">
-        <v>7847.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D58" t="n">
-        <v>7713.75</v>
+        <v>7810.5</v>
       </c>
       <c r="E58" t="n">
-        <v>7833.5</v>
+        <v>7831.75</v>
       </c>
       <c r="F58" t="n">
-        <v>176.15</v>
+        <v>-1.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.023</v>
+        <v>-0.0002</v>
       </c>
       <c r="H58" t="n">
-        <v>133.5</v>
+        <v>38</v>
       </c>
       <c r="I58" t="n">
         <v>7580.25</v>
       </c>
       <c r="J58" t="n">
-        <v>7617.15</v>
+        <v>7726.5</v>
       </c>
       <c r="K58" t="n">
-        <v>7634.85</v>
+        <v>7766.75</v>
       </c>
       <c r="L58" t="n">
-        <v>7652.55</v>
+        <v>7807</v>
       </c>
       <c r="M58" t="n">
-        <v>7679.85</v>
+        <v>7900.25</v>
       </c>
       <c r="N58" t="n">
-        <v>7707.15</v>
+        <v>7993.5</v>
       </c>
       <c r="O58" t="n">
-        <v>7715.25</v>
+        <v>7980.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5384,93 +5386,97 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>7830</v>
       </c>
       <c r="C59" t="n">
-        <v>7848.5</v>
+        <v>7843.25</v>
       </c>
       <c r="D59" t="n">
-        <v>7810.5</v>
+        <v>7758.75</v>
       </c>
       <c r="E59" t="n">
-        <v>7831.75</v>
+        <v>7772.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.75</v>
+        <v>-59.25</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0076</v>
       </c>
       <c r="H59" t="n">
-        <v>38</v>
+        <v>84.5</v>
       </c>
       <c r="I59" t="n">
-        <v>7580.25</v>
+        <v>7772.5</v>
       </c>
       <c r="J59" t="n">
-        <v>7726.5</v>
+        <v>7794.88</v>
       </c>
       <c r="K59" t="n">
-        <v>7766.75</v>
+        <v>7812.75</v>
       </c>
       <c r="L59" t="n">
-        <v>7807</v>
+        <v>7830.62</v>
       </c>
       <c r="M59" t="n">
-        <v>7900.25</v>
+        <v>7850.75</v>
       </c>
       <c r="N59" t="n">
-        <v>7993.5</v>
+        <v>7870.88</v>
       </c>
       <c r="O59" t="n">
-        <v>7980.75</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+        <v>7886.5</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5482,83 +5488,75 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W59" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7830</v>
+        <v>7774.75</v>
       </c>
       <c r="C60" t="n">
-        <v>7843.25</v>
+        <v>7783.5</v>
       </c>
       <c r="D60" t="n">
-        <v>7758.75</v>
+        <v>7707.25</v>
       </c>
       <c r="E60" t="n">
-        <v>7772.5</v>
+        <v>7767</v>
       </c>
       <c r="F60" t="n">
-        <v>-59.25</v>
+        <v>-5.5</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0076</v>
+        <v>-0.0007</v>
       </c>
       <c r="H60" t="n">
-        <v>84.5</v>
+        <v>76.25</v>
       </c>
       <c r="I60" t="n">
-        <v>7772.5</v>
+        <v>7674.25</v>
       </c>
       <c r="J60" t="n">
-        <v>7794.88</v>
+        <v>7673.75</v>
       </c>
       <c r="K60" t="n">
-        <v>7812.75</v>
+        <v>7730.25</v>
       </c>
       <c r="L60" t="n">
-        <v>7830.62</v>
+        <v>7786.75</v>
       </c>
       <c r="M60" t="n">
-        <v>7850.75</v>
+        <v>7814.75</v>
       </c>
       <c r="N60" t="n">
-        <v>7870.88</v>
+        <v>7842.75</v>
       </c>
       <c r="O60" t="n">
-        <v>7886.5</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
+        <v>7927.75</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5580,50 +5578,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7774.75</v>
+        <v>7759</v>
       </c>
       <c r="C61" t="n">
-        <v>7783.5</v>
+        <v>7814.75</v>
       </c>
       <c r="D61" t="n">
-        <v>7707.25</v>
+        <v>7748.5</v>
       </c>
       <c r="E61" t="n">
-        <v>7767</v>
+        <v>7803.75</v>
       </c>
       <c r="F61" t="n">
-        <v>-5.5</v>
+        <v>36.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0047</v>
       </c>
       <c r="H61" t="n">
-        <v>76.25</v>
+        <v>66.25</v>
       </c>
       <c r="I61" t="n">
-        <v>7674.25</v>
+        <v>7631</v>
       </c>
       <c r="J61" t="n">
-        <v>7673.75</v>
+        <v>7701.56</v>
       </c>
       <c r="K61" t="n">
-        <v>7730.25</v>
+        <v>7728.88</v>
       </c>
       <c r="L61" t="n">
-        <v>7786.75</v>
+        <v>7756.19</v>
       </c>
       <c r="M61" t="n">
-        <v>7814.75</v>
+        <v>7805.12</v>
       </c>
       <c r="N61" t="n">
-        <v>7842.75</v>
+        <v>7854.06</v>
       </c>
       <c r="O61" t="n">
-        <v>7927.75</v>
+        <v>7859.75</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5631,18 +5629,18 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5655,74 +5653,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7759</v>
+        <v>7746.5</v>
       </c>
       <c r="C62" t="n">
-        <v>7814.75</v>
+        <v>7748.25</v>
       </c>
       <c r="D62" t="n">
-        <v>7748.5</v>
+        <v>7741</v>
       </c>
       <c r="E62" t="n">
-        <v>7803.75</v>
+        <v>7742.75</v>
       </c>
       <c r="F62" t="n">
-        <v>36.75</v>
+        <v>-61</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0047</v>
+        <v>-0.0078</v>
       </c>
       <c r="H62" t="n">
-        <v>66.25</v>
+        <v>7.25</v>
       </c>
       <c r="I62" t="n">
-        <v>7631</v>
+        <v>7682.25</v>
       </c>
       <c r="J62" t="n">
-        <v>7701.56</v>
+        <v>7748.56</v>
       </c>
       <c r="K62" t="n">
-        <v>7728.88</v>
+        <v>7770.62</v>
       </c>
       <c r="L62" t="n">
-        <v>7756.19</v>
+        <v>7792.69</v>
       </c>
       <c r="M62" t="n">
-        <v>7805.12</v>
+        <v>7836.88</v>
       </c>
       <c r="N62" t="n">
-        <v>7854.06</v>
+        <v>7881.06</v>
       </c>
       <c r="O62" t="n">
-        <v>7859.75</v>
+        <v>7881</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5735,93 +5739,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>7796</v>
-      </c>
-      <c r="C63" t="n">
-        <v>7803</v>
-      </c>
-      <c r="D63" t="n">
-        <v>7786.75</v>
-      </c>
-      <c r="E63" t="n">
-        <v>7803.75</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="I63" t="n">
-        <v>7682.25</v>
-      </c>
-      <c r="J63" t="n">
-        <v>7748.56</v>
-      </c>
-      <c r="K63" t="n">
-        <v>7770.62</v>
-      </c>
-      <c r="L63" t="n">
-        <v>7792.69</v>
-      </c>
-      <c r="M63" t="n">
-        <v>7836.88</v>
-      </c>
-      <c r="N63" t="n">
-        <v>7881.06</v>
-      </c>
-      <c r="O63" t="n">
-        <v>7881</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7536</v>
+        <v>7562.25</v>
       </c>
       <c r="C2" t="n">
-        <v>7593.75</v>
+        <v>7602.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7479.5</v>
+        <v>7538.25</v>
       </c>
       <c r="E2" t="n">
-        <v>7528.25</v>
+        <v>7591.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-15.25</v>
+        <v>63.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>114.25</v>
+        <v>64.25</v>
       </c>
       <c r="I2" t="n">
-        <v>7432.5</v>
+        <v>7365.25</v>
       </c>
       <c r="J2" t="n">
-        <v>7470.81</v>
+        <v>7409.81</v>
       </c>
       <c r="K2" t="n">
-        <v>7506.88</v>
+        <v>7471.12</v>
       </c>
       <c r="L2" t="n">
-        <v>7542.94</v>
+        <v>7532.44</v>
       </c>
       <c r="M2" t="n">
-        <v>7580.12</v>
+        <v>7585.38</v>
       </c>
       <c r="N2" t="n">
-        <v>7617.31</v>
+        <v>7638.31</v>
       </c>
       <c r="O2" t="n">
-        <v>7652.25</v>
+        <v>7708</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,19 +685,17 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -711,78 +709,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C3" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D3" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E3" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F3" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H3" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I3" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J3" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K3" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L3" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M3" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N3" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O3" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -795,55 +791,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C4" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D4" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E4" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F4" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H4" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I4" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J4" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K4" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L4" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M4" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N4" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O4" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,7 +858,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -886,72 +886,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C5" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D5" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E5" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F5" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H5" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I5" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J5" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K5" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L5" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M5" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N5" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O5" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -963,59 +961,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C6" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D6" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E6" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H6" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I6" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J6" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K6" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L6" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M6" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N6" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O6" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1026,7 +1020,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1052,69 +1046,71 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C7" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D7" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E7" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F7" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H7" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I7" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J7" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K7" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L7" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M7" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N7" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O7" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1127,77 +1123,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C8" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D8" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E8" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F8" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H8" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I8" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J8" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K8" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L8" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M8" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N8" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O8" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1211,57 +1209,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C9" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D9" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E9" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F9" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H9" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I9" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J9" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K9" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L9" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M9" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N9" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O9" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,7 +1270,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1293,78 +1291,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C10" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D10" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E10" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F10" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H10" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I10" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J10" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K10" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L10" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M10" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N10" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O10" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1377,55 +1373,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C11" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D11" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E11" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F11" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H11" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I11" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J11" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K11" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L11" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M11" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N11" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O11" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1440,7 +1440,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1461,79 +1461,77 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C12" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D12" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E12" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F12" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H12" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I12" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J12" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K12" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L12" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M12" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N12" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O12" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1547,57 +1545,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C13" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D13" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E13" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I13" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J13" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K13" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L13" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M13" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N13" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O13" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1610,7 +1608,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
@@ -1618,8 +1616,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1631,57 +1631,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C14" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D14" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E14" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F14" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H14" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I14" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J14" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K14" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L14" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M14" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N14" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O14" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,23 +1689,21 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1724,56 +1722,60 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C15" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D15" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E15" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H15" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I15" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J15" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K15" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L15" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M15" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N15" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O15" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
@@ -1782,7 +1784,7 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1794,83 +1796,73 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C16" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D16" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E16" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H16" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I16" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J16" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K16" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L16" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M16" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N16" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O16" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>7687.25</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1887,55 +1879,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C17" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D17" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E17" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H17" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I17" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J17" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K17" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L17" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M17" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N17" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O17" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1946,16 +1942,20 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1974,50 +1974,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C18" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D18" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E18" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F18" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H18" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I18" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J18" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K18" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L18" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M18" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N18" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O18" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2030,18 +2030,14 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2060,67 +2056,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C19" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D19" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E19" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H19" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I19" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J19" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K19" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L19" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M19" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N19" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O19" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2135,86 +2139,82 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C20" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D20" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E20" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F20" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H20" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I20" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J20" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K20" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L20" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M20" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N20" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O20" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2225,57 +2225,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C21" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D21" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E21" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F21" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H21" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I21" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J21" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K21" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L21" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M21" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N21" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O21" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2286,21 +2286,19 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2311,57 +2309,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C22" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D22" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E22" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F22" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H22" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I22" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J22" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K22" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L22" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M22" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N22" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O22" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2372,18 +2370,20 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2402,50 +2402,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C23" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D23" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E23" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F23" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H23" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I23" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J23" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K23" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L23" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M23" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N23" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O23" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2456,7 +2456,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2471,67 +2471,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C24" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D24" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E24" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F24" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H24" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I24" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J24" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K24" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L24" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M24" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N24" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O24" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2542,80 +2540,78 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C25" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D25" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E25" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F25" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H25" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I25" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J25" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K25" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L25" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M25" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N25" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O25" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2623,12 +2619,14 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2647,57 +2645,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C26" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D26" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E26" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F26" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H26" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I26" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J26" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K26" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L26" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M26" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N26" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O26" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2705,22 +2703,24 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2729,59 +2729,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C27" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D27" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E27" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H27" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I27" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J27" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K27" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L27" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M27" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N27" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O27" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2792,20 +2788,16 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2815,72 +2807,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C28" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D28" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E28" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F28" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H28" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I28" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J28" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K28" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L28" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M28" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N28" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O28" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2895,81 +2897,77 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C29" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D29" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E29" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F29" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H29" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I29" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J29" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K29" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L29" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M29" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N29" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O29" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2983,57 +2981,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C30" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D30" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E30" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H30" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I30" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J30" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K30" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L30" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M30" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N30" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O30" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3044,19 +3042,21 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3065,59 +3065,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C31" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D31" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E31" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F31" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H31" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I31" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J31" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K31" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L31" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M31" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N31" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O31" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3130,18 +3126,14 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3151,72 +3143,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C32" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D32" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E32" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F32" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H32" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I32" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J32" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K32" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L32" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M32" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N32" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O32" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3231,80 +3233,78 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C33" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D33" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E33" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F33" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H33" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I33" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J33" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K33" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L33" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M33" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N33" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O33" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3326,74 +3326,74 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C34" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D34" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E34" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F34" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H34" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I34" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J34" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K34" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L34" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M34" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N34" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O34" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
       </c>
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3405,81 +3405,81 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C35" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D35" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E35" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F35" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H35" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I35" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J35" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K35" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L35" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M35" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N35" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O35" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3491,79 +3491,77 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C36" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D36" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E36" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F36" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H36" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I36" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J36" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K36" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L36" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M36" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N36" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O36" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3577,57 +3575,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C37" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D37" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E37" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F37" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H37" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I37" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J37" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K37" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L37" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M37" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N37" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O37" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3635,18 +3633,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3661,57 +3659,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C38" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D38" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E38" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F38" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H38" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I38" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J38" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K38" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L38" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M38" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N38" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O38" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3719,21 +3717,23 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3743,59 +3743,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C39" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D39" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E39" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F39" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H39" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I39" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J39" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K39" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L39" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M39" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N39" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O39" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3806,20 +3802,16 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3829,55 +3821,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C40" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D40" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E40" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F40" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H40" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I40" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J40" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K40" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L40" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M40" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N40" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O40" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3888,78 +3884,80 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C41" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E41" t="n">
         <v>7722</v>
       </c>
-      <c r="C41" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D41" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E41" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F41" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H41" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I41" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J41" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K41" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L41" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M41" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N41" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O41" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3967,12 +3965,14 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -3980,70 +3980,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C42" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D42" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E42" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F42" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H42" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I42" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J42" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K42" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L42" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M42" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N42" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O42" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4056,15 +4056,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4079,70 +4077,74 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C43" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D43" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E43" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F43" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H43" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I43" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J43" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K43" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L43" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M43" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N43" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O43" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4156,88 +4158,80 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C44" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D44" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E44" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F44" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H44" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I44" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J44" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K44" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L44" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M44" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N44" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O44" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4249,55 +4243,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C45" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D45" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E45" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F45" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H45" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I45" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J45" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K45" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L45" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M45" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N45" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O45" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4308,21 +4306,25 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
@@ -4331,57 +4333,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C46" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D46" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E46" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F46" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H46" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I46" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J46" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K46" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L46" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M46" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N46" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O46" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4394,23 +4396,17 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
       </c>
       <c r="W46" s="11" t="inlineStr">
         <is>
@@ -4419,57 +4415,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C47" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D47" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E47" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H47" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I47" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J47" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K47" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L47" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M47" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N47" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O47" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4477,12 +4473,14 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4499,59 +4497,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C48" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D48" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E48" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F48" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H48" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I48" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J48" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K48" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L48" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M48" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N48" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O48" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4564,7 +4558,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4588,50 +4582,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C49" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D49" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E49" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H49" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I49" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J49" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K49" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L49" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M49" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N49" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O49" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4644,7 +4638,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4668,50 +4662,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C50" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D50" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E50" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H50" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I50" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J50" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K50" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L50" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M50" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N50" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O50" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4719,22 +4713,24 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
@@ -4743,55 +4739,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C51" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D51" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E51" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F51" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H51" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I51" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J51" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K51" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L51" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M51" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N51" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O51" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4799,23 +4799,21 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4825,59 +4823,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C52" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D52" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E52" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F52" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H52" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I52" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J52" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K52" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L52" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M52" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N52" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O52" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4890,7 +4884,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4914,69 +4908,75 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7631</v>
+        <v>7596.5</v>
       </c>
       <c r="C53" t="n">
-        <v>7633.25</v>
+        <v>7632</v>
       </c>
       <c r="D53" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E53" t="n">
-        <v>7589.25</v>
+        <v>7556.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-35.75</v>
+        <v>-32.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0043</v>
       </c>
       <c r="H53" t="n">
-        <v>56.5</v>
+        <v>122.75</v>
       </c>
       <c r="I53" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J53" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K53" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L53" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M53" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N53" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O53" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+        <v>7689.75</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4994,76 +4994,70 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7596.5</v>
+        <v>7557.5</v>
       </c>
       <c r="C54" t="n">
-        <v>7632</v>
+        <v>7654.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7509.25</v>
+        <v>7551.5</v>
       </c>
       <c r="E54" t="n">
-        <v>7556.5</v>
+        <v>7640</v>
       </c>
       <c r="F54" t="n">
-        <v>-32.75</v>
+        <v>83.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="H54" t="n">
-        <v>122.75</v>
+        <v>103</v>
       </c>
       <c r="I54" t="n">
-        <v>7520.25</v>
+        <v>7386.5</v>
       </c>
       <c r="J54" t="n">
-        <v>7524.88</v>
+        <v>7426.69</v>
       </c>
       <c r="K54" t="n">
-        <v>7561</v>
+        <v>7495.12</v>
       </c>
       <c r="L54" t="n">
-        <v>7597.12</v>
+        <v>7563.56</v>
       </c>
       <c r="M54" t="n">
-        <v>7617.5</v>
+        <v>7617.88</v>
       </c>
       <c r="N54" t="n">
-        <v>7637.88</v>
+        <v>7672.19</v>
       </c>
       <c r="O54" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
+        <v>7754.75</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5075,55 +5069,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7557.5</v>
+        <v>7637</v>
       </c>
       <c r="C55" t="n">
-        <v>7654.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D55" t="n">
-        <v>7551.5</v>
+        <v>7625.25</v>
       </c>
       <c r="E55" t="n">
-        <v>7640</v>
+        <v>7657.35</v>
       </c>
       <c r="F55" t="n">
-        <v>83.5</v>
+        <v>17.35</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0023</v>
       </c>
       <c r="H55" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I55" t="n">
-        <v>7386.5</v>
+        <v>7448.5</v>
       </c>
       <c r="J55" t="n">
-        <v>7426.69</v>
+        <v>7555.5</v>
       </c>
       <c r="K55" t="n">
-        <v>7495.12</v>
+        <v>7588.5</v>
       </c>
       <c r="L55" t="n">
-        <v>7563.56</v>
+        <v>7621.5</v>
       </c>
       <c r="M55" t="n">
-        <v>7617.88</v>
+        <v>7691.5</v>
       </c>
       <c r="N55" t="n">
-        <v>7672.19</v>
+        <v>7761.5</v>
       </c>
       <c r="O55" t="n">
-        <v>7754.75</v>
+        <v>7757.5</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5134,7 +5132,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5164,50 +5162,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7637</v>
+        <v>7722</v>
       </c>
       <c r="C56" t="n">
-        <v>7670.25</v>
+        <v>7847.25</v>
       </c>
       <c r="D56" t="n">
-        <v>7625.25</v>
+        <v>7713.75</v>
       </c>
       <c r="E56" t="n">
-        <v>7657.35</v>
+        <v>7833.5</v>
       </c>
       <c r="F56" t="n">
-        <v>17.35</v>
+        <v>176.15</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.023</v>
       </c>
       <c r="H56" t="n">
-        <v>45</v>
+        <v>133.5</v>
       </c>
       <c r="I56" t="n">
-        <v>7448.5</v>
+        <v>7580.25</v>
       </c>
       <c r="J56" t="n">
-        <v>7555.5</v>
+        <v>7617.15</v>
       </c>
       <c r="K56" t="n">
-        <v>7588.5</v>
+        <v>7634.85</v>
       </c>
       <c r="L56" t="n">
-        <v>7621.5</v>
+        <v>7652.55</v>
       </c>
       <c r="M56" t="n">
-        <v>7691.5</v>
+        <v>7679.85</v>
       </c>
       <c r="N56" t="n">
-        <v>7761.5</v>
+        <v>7707.15</v>
       </c>
       <c r="O56" t="n">
-        <v>7757.5</v>
+        <v>7715.25</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5218,80 +5216,80 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7722</v>
+        <v>7830</v>
       </c>
       <c r="C57" t="n">
-        <v>7847.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D57" t="n">
-        <v>7713.75</v>
+        <v>7810.5</v>
       </c>
       <c r="E57" t="n">
-        <v>7833.5</v>
+        <v>7831.75</v>
       </c>
       <c r="F57" t="n">
-        <v>176.15</v>
+        <v>-1.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.023</v>
+        <v>-0.0002</v>
       </c>
       <c r="H57" t="n">
-        <v>133.5</v>
+        <v>38</v>
       </c>
       <c r="I57" t="n">
         <v>7580.25</v>
       </c>
       <c r="J57" t="n">
-        <v>7617.15</v>
+        <v>7726.5</v>
       </c>
       <c r="K57" t="n">
-        <v>7634.85</v>
+        <v>7766.75</v>
       </c>
       <c r="L57" t="n">
-        <v>7652.55</v>
+        <v>7807</v>
       </c>
       <c r="M57" t="n">
-        <v>7679.85</v>
+        <v>7900.25</v>
       </c>
       <c r="N57" t="n">
-        <v>7707.15</v>
+        <v>7993.5</v>
       </c>
       <c r="O57" t="n">
-        <v>7715.25</v>
+        <v>7980.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5302,93 +5300,97 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>7830</v>
       </c>
       <c r="C58" t="n">
-        <v>7848.5</v>
+        <v>7843.25</v>
       </c>
       <c r="D58" t="n">
-        <v>7810.5</v>
+        <v>7758.75</v>
       </c>
       <c r="E58" t="n">
-        <v>7831.75</v>
+        <v>7772.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.75</v>
+        <v>-59.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0076</v>
       </c>
       <c r="H58" t="n">
-        <v>38</v>
+        <v>84.5</v>
       </c>
       <c r="I58" t="n">
-        <v>7580.25</v>
+        <v>7772.5</v>
       </c>
       <c r="J58" t="n">
-        <v>7726.5</v>
+        <v>7794.88</v>
       </c>
       <c r="K58" t="n">
-        <v>7766.75</v>
+        <v>7812.75</v>
       </c>
       <c r="L58" t="n">
-        <v>7807</v>
+        <v>7830.62</v>
       </c>
       <c r="M58" t="n">
-        <v>7900.25</v>
+        <v>7850.75</v>
       </c>
       <c r="N58" t="n">
-        <v>7993.5</v>
+        <v>7870.88</v>
       </c>
       <c r="O58" t="n">
-        <v>7980.75</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+        <v>7886.5</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5400,83 +5402,75 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7830</v>
+        <v>7774.75</v>
       </c>
       <c r="C59" t="n">
-        <v>7843.25</v>
+        <v>7783.5</v>
       </c>
       <c r="D59" t="n">
-        <v>7758.75</v>
+        <v>7707.25</v>
       </c>
       <c r="E59" t="n">
-        <v>7772.5</v>
+        <v>7767</v>
       </c>
       <c r="F59" t="n">
-        <v>-59.25</v>
+        <v>-5.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0076</v>
+        <v>-0.0007</v>
       </c>
       <c r="H59" t="n">
-        <v>84.5</v>
+        <v>76.25</v>
       </c>
       <c r="I59" t="n">
-        <v>7772.5</v>
+        <v>7674.25</v>
       </c>
       <c r="J59" t="n">
-        <v>7794.88</v>
+        <v>7673.75</v>
       </c>
       <c r="K59" t="n">
-        <v>7812.75</v>
+        <v>7730.25</v>
       </c>
       <c r="L59" t="n">
-        <v>7830.62</v>
+        <v>7786.75</v>
       </c>
       <c r="M59" t="n">
-        <v>7850.75</v>
+        <v>7814.75</v>
       </c>
       <c r="N59" t="n">
-        <v>7870.88</v>
+        <v>7842.75</v>
       </c>
       <c r="O59" t="n">
-        <v>7886.5</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q59" s="6" t="inlineStr">
+        <v>7927.75</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5498,50 +5492,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7774.75</v>
+        <v>7759</v>
       </c>
       <c r="C60" t="n">
-        <v>7783.5</v>
+        <v>7814.75</v>
       </c>
       <c r="D60" t="n">
-        <v>7707.25</v>
+        <v>7748.5</v>
       </c>
       <c r="E60" t="n">
-        <v>7767</v>
+        <v>7803.75</v>
       </c>
       <c r="F60" t="n">
-        <v>-5.5</v>
+        <v>36.75</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0047</v>
       </c>
       <c r="H60" t="n">
-        <v>76.25</v>
+        <v>66.25</v>
       </c>
       <c r="I60" t="n">
-        <v>7674.25</v>
+        <v>7631</v>
       </c>
       <c r="J60" t="n">
-        <v>7673.75</v>
+        <v>7701.56</v>
       </c>
       <c r="K60" t="n">
-        <v>7730.25</v>
+        <v>7728.88</v>
       </c>
       <c r="L60" t="n">
-        <v>7786.75</v>
+        <v>7756.19</v>
       </c>
       <c r="M60" t="n">
-        <v>7814.75</v>
+        <v>7805.12</v>
       </c>
       <c r="N60" t="n">
-        <v>7842.75</v>
+        <v>7854.06</v>
       </c>
       <c r="O60" t="n">
-        <v>7927.75</v>
+        <v>7859.75</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5549,18 +5543,18 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5573,74 +5567,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7759</v>
+        <v>7796</v>
       </c>
       <c r="C61" t="n">
-        <v>7814.75</v>
+        <v>7803</v>
       </c>
       <c r="D61" t="n">
-        <v>7748.5</v>
+        <v>7726</v>
       </c>
       <c r="E61" t="n">
-        <v>7803.75</v>
+        <v>7746.75</v>
       </c>
       <c r="F61" t="n">
-        <v>36.75</v>
+        <v>-57</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0047</v>
+        <v>-0.0073</v>
       </c>
       <c r="H61" t="n">
-        <v>66.25</v>
+        <v>77</v>
       </c>
       <c r="I61" t="n">
-        <v>7631</v>
+        <v>7682.25</v>
       </c>
       <c r="J61" t="n">
-        <v>7701.56</v>
+        <v>7748.56</v>
       </c>
       <c r="K61" t="n">
-        <v>7728.88</v>
+        <v>7770.62</v>
       </c>
       <c r="L61" t="n">
-        <v>7756.19</v>
+        <v>7792.69</v>
       </c>
       <c r="M61" t="n">
-        <v>7805.12</v>
+        <v>7836.88</v>
       </c>
       <c r="N61" t="n">
-        <v>7854.06</v>
+        <v>7881.06</v>
       </c>
       <c r="O61" t="n">
-        <v>7859.75</v>
+        <v>7881</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5653,76 +5653,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7746.5</v>
+        <v>7739</v>
       </c>
       <c r="C62" t="n">
-        <v>7748.25</v>
+        <v>7745.75</v>
       </c>
       <c r="D62" t="n">
-        <v>7741</v>
+        <v>7738</v>
       </c>
       <c r="E62" t="n">
-        <v>7742.75</v>
+        <v>7745</v>
       </c>
       <c r="F62" t="n">
-        <v>-61</v>
+        <v>-1.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0002</v>
       </c>
       <c r="H62" t="n">
-        <v>7.25</v>
+        <v>7.75</v>
       </c>
       <c r="I62" t="n">
-        <v>7682.25</v>
+        <v>7649</v>
       </c>
       <c r="J62" t="n">
-        <v>7748.56</v>
+        <v>7660.88</v>
       </c>
       <c r="K62" t="n">
-        <v>7770.62</v>
+        <v>7708.25</v>
       </c>
       <c r="L62" t="n">
-        <v>7792.69</v>
+        <v>7755.62</v>
       </c>
       <c r="M62" t="n">
-        <v>7836.88</v>
+        <v>7785.25</v>
       </c>
       <c r="N62" t="n">
-        <v>7881.06</v>
+        <v>7814.88</v>
       </c>
       <c r="O62" t="n">
-        <v>7881</v>
+        <v>7880</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5739,7 +5731,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,69 +634,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7562.25</v>
+        <v>7597</v>
       </c>
       <c r="C2" t="n">
-        <v>7602.5</v>
+        <v>7601.25</v>
       </c>
       <c r="D2" t="n">
-        <v>7538.25</v>
+        <v>7529.5</v>
       </c>
       <c r="E2" t="n">
-        <v>7591.5</v>
+        <v>7551.25</v>
       </c>
       <c r="F2" t="n">
-        <v>63.25</v>
+        <v>-40.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="H2" t="n">
-        <v>64.25</v>
+        <v>71.75</v>
       </c>
       <c r="I2" t="n">
-        <v>7365.25</v>
+        <v>7474</v>
       </c>
       <c r="J2" t="n">
-        <v>7409.81</v>
+        <v>7537.81</v>
       </c>
       <c r="K2" t="n">
-        <v>7471.12</v>
+        <v>7559.38</v>
       </c>
       <c r="L2" t="n">
-        <v>7532.44</v>
+        <v>7580.94</v>
       </c>
       <c r="M2" t="n">
-        <v>7585.38</v>
+        <v>7623.62</v>
       </c>
       <c r="N2" t="n">
-        <v>7638.31</v>
+        <v>7666.31</v>
       </c>
       <c r="O2" t="n">
-        <v>7708</v>
+        <v>7666.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,55 +711,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C3" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D3" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E3" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F3" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H3" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I3" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J3" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K3" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L3" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M3" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N3" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O3" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,7 +778,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -800,72 +806,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C4" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D4" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E4" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F4" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H4" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I4" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J4" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K4" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L4" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M4" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N4" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O4" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -877,59 +881,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C5" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D5" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E5" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H5" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I5" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J5" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K5" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L5" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M5" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N5" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O5" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,7 +940,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -966,69 +966,71 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C6" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D6" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E6" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F6" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H6" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I6" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J6" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K6" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L6" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M6" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N6" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O6" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1041,77 +1043,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C7" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D7" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E7" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F7" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H7" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I7" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J7" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K7" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L7" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M7" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N7" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O7" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1125,57 +1129,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C8" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D8" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E8" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F8" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H8" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I8" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J8" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K8" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L8" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M8" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N8" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O8" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1186,7 +1190,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1207,78 +1211,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C9" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D9" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E9" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F9" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H9" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I9" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J9" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K9" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L9" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M9" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N9" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O9" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1291,55 +1293,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C10" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D10" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E10" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F10" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H10" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I10" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J10" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K10" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L10" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M10" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N10" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O10" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,7 +1360,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1375,79 +1381,77 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C11" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D11" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E11" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F11" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H11" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I11" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J11" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K11" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L11" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M11" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N11" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O11" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1461,57 +1465,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C12" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D12" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E12" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I12" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J12" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K12" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L12" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M12" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N12" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O12" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1524,7 +1528,7 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
@@ -1532,8 +1536,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1545,57 +1551,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C13" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D13" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E13" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F13" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H13" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I13" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J13" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K13" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L13" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M13" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N13" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O13" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,23 +1609,21 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1638,56 +1642,60 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C14" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D14" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E14" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H14" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I14" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J14" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K14" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L14" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M14" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N14" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O14" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
@@ -1696,7 +1704,7 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1708,83 +1716,73 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C15" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D15" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E15" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H15" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I15" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J15" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K15" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L15" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M15" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N15" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O15" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>7687.25</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1801,55 +1799,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C16" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D16" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E16" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H16" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I16" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J16" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K16" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L16" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M16" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N16" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O16" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,16 +1862,20 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1888,50 +1894,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C17" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D17" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E17" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H17" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I17" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J17" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K17" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L17" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M17" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N17" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O17" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1944,18 +1950,14 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1974,67 +1976,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C18" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D18" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E18" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H18" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I18" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J18" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K18" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L18" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M18" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N18" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O18" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2049,86 +2059,82 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C19" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D19" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E19" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F19" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H19" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I19" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J19" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K19" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L19" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M19" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N19" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O19" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2139,57 +2145,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C20" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D20" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E20" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F20" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H20" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I20" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J20" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K20" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L20" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M20" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N20" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O20" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2200,21 +2206,19 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2225,57 +2229,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C21" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D21" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E21" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F21" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H21" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I21" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J21" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K21" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L21" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M21" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N21" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O21" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2286,18 +2290,20 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2316,50 +2322,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C22" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D22" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E22" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F22" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H22" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I22" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J22" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K22" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L22" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M22" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N22" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O22" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2370,7 +2376,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2385,67 +2391,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C23" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D23" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E23" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F23" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H23" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I23" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J23" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K23" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L23" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M23" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N23" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O23" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2456,80 +2460,78 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C24" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D24" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E24" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F24" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H24" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I24" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J24" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K24" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L24" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M24" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N24" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O24" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2537,12 +2539,14 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2561,57 +2565,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C25" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D25" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E25" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H25" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I25" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J25" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K25" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L25" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M25" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N25" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O25" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2619,22 +2623,24 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2643,59 +2649,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C26" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D26" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E26" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H26" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I26" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J26" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K26" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L26" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M26" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N26" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O26" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2706,20 +2708,16 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2729,72 +2727,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C27" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D27" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E27" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F27" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H27" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I27" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J27" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K27" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L27" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M27" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N27" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O27" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2809,81 +2817,77 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C28" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D28" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E28" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F28" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H28" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I28" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J28" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K28" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L28" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M28" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N28" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O28" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2897,57 +2901,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C29" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D29" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E29" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H29" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I29" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J29" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K29" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L29" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M29" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N29" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O29" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2958,19 +2962,21 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
@@ -2979,59 +2985,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C30" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D30" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E30" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F30" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H30" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I30" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J30" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K30" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L30" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M30" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N30" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O30" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3044,18 +3046,14 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3065,72 +3063,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C31" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D31" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E31" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F31" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H31" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I31" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J31" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K31" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L31" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M31" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N31" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O31" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3145,80 +3153,78 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C32" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D32" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E32" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F32" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H32" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I32" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J32" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K32" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L32" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M32" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N32" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O32" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3240,74 +3246,74 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C33" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D33" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E33" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F33" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H33" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I33" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J33" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K33" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L33" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M33" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N33" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O33" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
       </c>
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3319,81 +3325,81 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C34" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D34" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E34" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H34" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I34" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J34" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K34" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L34" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M34" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N34" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O34" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3405,79 +3411,77 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C35" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D35" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E35" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F35" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H35" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I35" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J35" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K35" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L35" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M35" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N35" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O35" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3491,57 +3495,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C36" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D36" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E36" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F36" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H36" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I36" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J36" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K36" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L36" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M36" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N36" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O36" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3549,18 +3553,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3575,57 +3579,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C37" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D37" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E37" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F37" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H37" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I37" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J37" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K37" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L37" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M37" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N37" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O37" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3633,21 +3637,23 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3657,59 +3663,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C38" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D38" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E38" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F38" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H38" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I38" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J38" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K38" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L38" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M38" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N38" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O38" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3720,20 +3722,16 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3743,55 +3741,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C39" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D39" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E39" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H39" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I39" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J39" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K39" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L39" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M39" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N39" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O39" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3802,78 +3804,80 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C40" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E40" t="n">
         <v>7722</v>
       </c>
-      <c r="C40" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D40" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E40" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F40" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H40" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I40" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J40" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K40" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L40" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M40" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N40" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O40" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3881,12 +3885,14 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3894,70 +3900,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C41" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D41" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E41" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F41" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H41" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I41" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J41" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K41" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L41" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M41" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N41" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O41" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3970,15 +3976,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3993,70 +3997,74 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C42" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D42" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E42" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F42" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H42" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I42" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J42" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K42" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L42" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M42" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N42" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O42" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4070,88 +4078,80 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C43" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D43" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E43" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F43" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H43" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I43" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J43" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K43" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L43" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M43" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N43" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O43" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4163,55 +4163,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C44" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D44" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E44" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F44" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H44" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I44" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J44" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K44" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L44" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M44" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N44" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O44" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4222,21 +4226,25 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
@@ -4245,57 +4253,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C45" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D45" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E45" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F45" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H45" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I45" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J45" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K45" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L45" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M45" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N45" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O45" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4308,23 +4316,17 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
@@ -4333,57 +4335,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C46" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D46" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E46" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H46" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I46" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J46" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K46" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L46" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M46" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N46" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O46" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4391,12 +4393,14 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4413,59 +4417,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C47" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D47" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E47" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F47" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H47" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I47" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J47" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K47" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L47" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M47" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N47" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O47" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4478,7 +4478,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4502,50 +4502,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C48" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D48" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E48" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H48" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I48" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J48" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K48" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L48" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M48" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N48" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O48" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4558,7 +4558,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4582,50 +4582,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C49" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D49" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E49" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H49" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I49" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J49" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K49" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L49" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M49" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N49" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O49" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4633,22 +4633,24 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4657,55 +4659,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C50" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D50" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E50" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F50" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H50" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I50" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J50" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K50" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L50" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M50" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N50" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O50" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4713,23 +4719,21 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4739,59 +4743,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C51" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D51" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E51" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F51" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H51" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I51" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J51" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K51" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L51" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M51" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N51" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O51" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4804,7 +4804,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4828,69 +4828,75 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7631</v>
+        <v>7596.5</v>
       </c>
       <c r="C52" t="n">
-        <v>7633.25</v>
+        <v>7632</v>
       </c>
       <c r="D52" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E52" t="n">
-        <v>7589.25</v>
+        <v>7556.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-35.75</v>
+        <v>-32.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0043</v>
       </c>
       <c r="H52" t="n">
-        <v>56.5</v>
+        <v>122.75</v>
       </c>
       <c r="I52" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J52" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K52" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L52" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M52" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N52" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O52" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+        <v>7689.75</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4908,76 +4914,70 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7596.5</v>
+        <v>7557.5</v>
       </c>
       <c r="C53" t="n">
-        <v>7632</v>
+        <v>7654.5</v>
       </c>
       <c r="D53" t="n">
-        <v>7509.25</v>
+        <v>7551.5</v>
       </c>
       <c r="E53" t="n">
-        <v>7556.5</v>
+        <v>7640</v>
       </c>
       <c r="F53" t="n">
-        <v>-32.75</v>
+        <v>83.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="H53" t="n">
-        <v>122.75</v>
+        <v>103</v>
       </c>
       <c r="I53" t="n">
-        <v>7520.25</v>
+        <v>7386.5</v>
       </c>
       <c r="J53" t="n">
-        <v>7524.88</v>
+        <v>7426.69</v>
       </c>
       <c r="K53" t="n">
-        <v>7561</v>
+        <v>7495.12</v>
       </c>
       <c r="L53" t="n">
-        <v>7597.12</v>
+        <v>7563.56</v>
       </c>
       <c r="M53" t="n">
-        <v>7617.5</v>
+        <v>7617.88</v>
       </c>
       <c r="N53" t="n">
-        <v>7637.88</v>
+        <v>7672.19</v>
       </c>
       <c r="O53" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
+        <v>7754.75</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4989,55 +4989,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7557.5</v>
+        <v>7637</v>
       </c>
       <c r="C54" t="n">
-        <v>7654.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D54" t="n">
-        <v>7551.5</v>
+        <v>7625.25</v>
       </c>
       <c r="E54" t="n">
-        <v>7640</v>
+        <v>7657.35</v>
       </c>
       <c r="F54" t="n">
-        <v>83.5</v>
+        <v>17.35</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0023</v>
       </c>
       <c r="H54" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I54" t="n">
-        <v>7386.5</v>
+        <v>7448.5</v>
       </c>
       <c r="J54" t="n">
-        <v>7426.69</v>
+        <v>7555.5</v>
       </c>
       <c r="K54" t="n">
-        <v>7495.12</v>
+        <v>7588.5</v>
       </c>
       <c r="L54" t="n">
-        <v>7563.56</v>
+        <v>7621.5</v>
       </c>
       <c r="M54" t="n">
-        <v>7617.88</v>
+        <v>7691.5</v>
       </c>
       <c r="N54" t="n">
-        <v>7672.19</v>
+        <v>7761.5</v>
       </c>
       <c r="O54" t="n">
-        <v>7754.75</v>
+        <v>7757.5</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5048,7 +5052,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5078,50 +5082,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7637</v>
+        <v>7722</v>
       </c>
       <c r="C55" t="n">
-        <v>7670.25</v>
+        <v>7847.25</v>
       </c>
       <c r="D55" t="n">
-        <v>7625.25</v>
+        <v>7713.75</v>
       </c>
       <c r="E55" t="n">
-        <v>7657.35</v>
+        <v>7833.5</v>
       </c>
       <c r="F55" t="n">
-        <v>17.35</v>
+        <v>176.15</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.023</v>
       </c>
       <c r="H55" t="n">
-        <v>45</v>
+        <v>133.5</v>
       </c>
       <c r="I55" t="n">
-        <v>7448.5</v>
+        <v>7580.25</v>
       </c>
       <c r="J55" t="n">
-        <v>7555.5</v>
+        <v>7617.15</v>
       </c>
       <c r="K55" t="n">
-        <v>7588.5</v>
+        <v>7634.85</v>
       </c>
       <c r="L55" t="n">
-        <v>7621.5</v>
+        <v>7652.55</v>
       </c>
       <c r="M55" t="n">
-        <v>7691.5</v>
+        <v>7679.85</v>
       </c>
       <c r="N55" t="n">
-        <v>7761.5</v>
+        <v>7707.15</v>
       </c>
       <c r="O55" t="n">
-        <v>7757.5</v>
+        <v>7715.25</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5132,80 +5136,80 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7722</v>
+        <v>7830</v>
       </c>
       <c r="C56" t="n">
-        <v>7847.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D56" t="n">
-        <v>7713.75</v>
+        <v>7810.5</v>
       </c>
       <c r="E56" t="n">
-        <v>7833.5</v>
+        <v>7831.75</v>
       </c>
       <c r="F56" t="n">
-        <v>176.15</v>
+        <v>-1.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.023</v>
+        <v>-0.0002</v>
       </c>
       <c r="H56" t="n">
-        <v>133.5</v>
+        <v>38</v>
       </c>
       <c r="I56" t="n">
         <v>7580.25</v>
       </c>
       <c r="J56" t="n">
-        <v>7617.15</v>
+        <v>7726.5</v>
       </c>
       <c r="K56" t="n">
-        <v>7634.85</v>
+        <v>7766.75</v>
       </c>
       <c r="L56" t="n">
-        <v>7652.55</v>
+        <v>7807</v>
       </c>
       <c r="M56" t="n">
-        <v>7679.85</v>
+        <v>7900.25</v>
       </c>
       <c r="N56" t="n">
-        <v>7707.15</v>
+        <v>7993.5</v>
       </c>
       <c r="O56" t="n">
-        <v>7715.25</v>
+        <v>7980.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5216,93 +5220,97 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>7830</v>
       </c>
       <c r="C57" t="n">
-        <v>7848.5</v>
+        <v>7843.25</v>
       </c>
       <c r="D57" t="n">
-        <v>7810.5</v>
+        <v>7758.75</v>
       </c>
       <c r="E57" t="n">
-        <v>7831.75</v>
+        <v>7772.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.75</v>
+        <v>-59.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0076</v>
       </c>
       <c r="H57" t="n">
-        <v>38</v>
+        <v>84.5</v>
       </c>
       <c r="I57" t="n">
-        <v>7580.25</v>
+        <v>7772.5</v>
       </c>
       <c r="J57" t="n">
-        <v>7726.5</v>
+        <v>7794.88</v>
       </c>
       <c r="K57" t="n">
-        <v>7766.75</v>
+        <v>7812.75</v>
       </c>
       <c r="L57" t="n">
-        <v>7807</v>
+        <v>7830.62</v>
       </c>
       <c r="M57" t="n">
-        <v>7900.25</v>
+        <v>7850.75</v>
       </c>
       <c r="N57" t="n">
-        <v>7993.5</v>
+        <v>7870.88</v>
       </c>
       <c r="O57" t="n">
-        <v>7980.75</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+        <v>7886.5</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5314,83 +5322,75 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7830</v>
+        <v>7774.75</v>
       </c>
       <c r="C58" t="n">
-        <v>7843.25</v>
+        <v>7783.5</v>
       </c>
       <c r="D58" t="n">
-        <v>7758.75</v>
+        <v>7707.25</v>
       </c>
       <c r="E58" t="n">
-        <v>7772.5</v>
+        <v>7767</v>
       </c>
       <c r="F58" t="n">
-        <v>-59.25</v>
+        <v>-5.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0076</v>
+        <v>-0.0007</v>
       </c>
       <c r="H58" t="n">
-        <v>84.5</v>
+        <v>76.25</v>
       </c>
       <c r="I58" t="n">
-        <v>7772.5</v>
+        <v>7674.25</v>
       </c>
       <c r="J58" t="n">
-        <v>7794.88</v>
+        <v>7673.75</v>
       </c>
       <c r="K58" t="n">
-        <v>7812.75</v>
+        <v>7730.25</v>
       </c>
       <c r="L58" t="n">
-        <v>7830.62</v>
+        <v>7786.75</v>
       </c>
       <c r="M58" t="n">
-        <v>7850.75</v>
+        <v>7814.75</v>
       </c>
       <c r="N58" t="n">
-        <v>7870.88</v>
+        <v>7842.75</v>
       </c>
       <c r="O58" t="n">
-        <v>7886.5</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
+        <v>7927.75</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5412,50 +5412,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7774.75</v>
+        <v>7759</v>
       </c>
       <c r="C59" t="n">
-        <v>7783.5</v>
+        <v>7814.75</v>
       </c>
       <c r="D59" t="n">
-        <v>7707.25</v>
+        <v>7748.5</v>
       </c>
       <c r="E59" t="n">
-        <v>7767</v>
+        <v>7803.75</v>
       </c>
       <c r="F59" t="n">
-        <v>-5.5</v>
+        <v>36.75</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0047</v>
       </c>
       <c r="H59" t="n">
-        <v>76.25</v>
+        <v>66.25</v>
       </c>
       <c r="I59" t="n">
-        <v>7674.25</v>
+        <v>7631</v>
       </c>
       <c r="J59" t="n">
-        <v>7673.75</v>
+        <v>7701.56</v>
       </c>
       <c r="K59" t="n">
-        <v>7730.25</v>
+        <v>7728.88</v>
       </c>
       <c r="L59" t="n">
-        <v>7786.75</v>
+        <v>7756.19</v>
       </c>
       <c r="M59" t="n">
-        <v>7814.75</v>
+        <v>7805.12</v>
       </c>
       <c r="N59" t="n">
-        <v>7842.75</v>
+        <v>7854.06</v>
       </c>
       <c r="O59" t="n">
-        <v>7927.75</v>
+        <v>7859.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5463,18 +5463,18 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5487,74 +5487,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7759</v>
+        <v>7796</v>
       </c>
       <c r="C60" t="n">
-        <v>7814.75</v>
+        <v>7803</v>
       </c>
       <c r="D60" t="n">
-        <v>7748.5</v>
+        <v>7726</v>
       </c>
       <c r="E60" t="n">
-        <v>7803.75</v>
+        <v>7746.75</v>
       </c>
       <c r="F60" t="n">
-        <v>36.75</v>
+        <v>-57</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0047</v>
+        <v>-0.0073</v>
       </c>
       <c r="H60" t="n">
-        <v>66.25</v>
+        <v>77</v>
       </c>
       <c r="I60" t="n">
-        <v>7631</v>
+        <v>7682.25</v>
       </c>
       <c r="J60" t="n">
-        <v>7701.56</v>
+        <v>7748.56</v>
       </c>
       <c r="K60" t="n">
-        <v>7728.88</v>
+        <v>7770.62</v>
       </c>
       <c r="L60" t="n">
-        <v>7756.19</v>
+        <v>7792.69</v>
       </c>
       <c r="M60" t="n">
-        <v>7805.12</v>
+        <v>7836.88</v>
       </c>
       <c r="N60" t="n">
-        <v>7854.06</v>
+        <v>7881.06</v>
       </c>
       <c r="O60" t="n">
-        <v>7859.75</v>
+        <v>7881</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5567,76 +5573,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7796</v>
+        <v>7746.5</v>
       </c>
       <c r="C61" t="n">
-        <v>7803</v>
+        <v>7770.75</v>
       </c>
       <c r="D61" t="n">
-        <v>7726</v>
+        <v>7712.25</v>
       </c>
       <c r="E61" t="n">
-        <v>7746.75</v>
+        <v>7732</v>
       </c>
       <c r="F61" t="n">
-        <v>-57</v>
+        <v>-14.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0019</v>
       </c>
       <c r="H61" t="n">
-        <v>77</v>
+        <v>58.5</v>
       </c>
       <c r="I61" t="n">
-        <v>7682.25</v>
+        <v>7649</v>
       </c>
       <c r="J61" t="n">
-        <v>7748.56</v>
+        <v>7660.88</v>
       </c>
       <c r="K61" t="n">
-        <v>7770.62</v>
+        <v>7708.25</v>
       </c>
       <c r="L61" t="n">
-        <v>7792.69</v>
+        <v>7755.62</v>
       </c>
       <c r="M61" t="n">
-        <v>7836.88</v>
+        <v>7785.25</v>
       </c>
       <c r="N61" t="n">
-        <v>7881.06</v>
+        <v>7814.88</v>
       </c>
       <c r="O61" t="n">
-        <v>7881</v>
+        <v>7880</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5658,50 +5656,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7739</v>
+        <v>7719.5</v>
       </c>
       <c r="C62" t="n">
-        <v>7745.75</v>
+        <v>7726</v>
       </c>
       <c r="D62" t="n">
-        <v>7738</v>
+        <v>7717.5</v>
       </c>
       <c r="E62" t="n">
-        <v>7745</v>
+        <v>7725.25</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.75</v>
+        <v>-6.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0009</v>
       </c>
       <c r="H62" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="I62" t="n">
-        <v>7649</v>
+        <v>7653.75</v>
       </c>
       <c r="J62" t="n">
-        <v>7660.88</v>
+        <v>7668.75</v>
       </c>
       <c r="K62" t="n">
-        <v>7708.25</v>
+        <v>7702.75</v>
       </c>
       <c r="L62" t="n">
-        <v>7755.62</v>
+        <v>7736.75</v>
       </c>
       <c r="M62" t="n">
-        <v>7785.25</v>
+        <v>7761.25</v>
       </c>
       <c r="N62" t="n">
-        <v>7814.88</v>
+        <v>7785.75</v>
       </c>
       <c r="O62" t="n">
-        <v>7880</v>
+        <v>7829.25</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5712,7 +5710,7 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5660,25 +5660,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7719.5</v>
+        <v>7739</v>
       </c>
       <c r="C62" t="n">
-        <v>7726</v>
+        <v>7782</v>
       </c>
       <c r="D62" t="n">
-        <v>7717.5</v>
+        <v>7705.5</v>
       </c>
       <c r="E62" t="n">
-        <v>7725.25</v>
+        <v>7715.5</v>
       </c>
       <c r="F62" t="n">
-        <v>-6.75</v>
+        <v>-16.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0021</v>
       </c>
       <c r="H62" t="n">
-        <v>8.5</v>
+        <v>76.5</v>
       </c>
       <c r="I62" t="n">
         <v>7653.75</v>
@@ -5707,31 +5707,117 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7724</v>
+      </c>
+      <c r="C63" t="n">
+        <v>7727.25</v>
+      </c>
+      <c r="D63" t="n">
+        <v>7723.25</v>
+      </c>
+      <c r="E63" t="n">
+        <v>7726</v>
+      </c>
+      <c r="F63" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="H63" t="n">
+        <v>4</v>
+      </c>
+      <c r="I63" t="n">
+        <v>7629</v>
+      </c>
+      <c r="J63" t="n">
+        <v>7624.88</v>
+      </c>
+      <c r="K63" t="n">
+        <v>7677.25</v>
+      </c>
+      <c r="L63" t="n">
+        <v>7729.62</v>
+      </c>
+      <c r="M63" t="n">
+        <v>7753.75</v>
+      </c>
+      <c r="N63" t="n">
+        <v>7777.88</v>
+      </c>
+      <c r="O63" t="n">
+        <v>7858.5</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7597</v>
+        <v>7545</v>
       </c>
       <c r="C2" t="n">
-        <v>7601.25</v>
+        <v>7563</v>
       </c>
       <c r="D2" t="n">
-        <v>7529.5</v>
+        <v>7468.5</v>
       </c>
       <c r="E2" t="n">
-        <v>7551.25</v>
+        <v>7528.75</v>
       </c>
       <c r="F2" t="n">
-        <v>-40.25</v>
+        <v>-22.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="H2" t="n">
-        <v>71.75</v>
+        <v>94.5</v>
       </c>
       <c r="I2" t="n">
-        <v>7474</v>
+        <v>7457.75</v>
       </c>
       <c r="J2" t="n">
-        <v>7537.81</v>
+        <v>7472.44</v>
       </c>
       <c r="K2" t="n">
-        <v>7559.38</v>
+        <v>7515.38</v>
       </c>
       <c r="L2" t="n">
-        <v>7580.94</v>
+        <v>7558.31</v>
       </c>
       <c r="M2" t="n">
-        <v>7623.62</v>
+        <v>7587.12</v>
       </c>
       <c r="N2" t="n">
-        <v>7666.31</v>
+        <v>7615.94</v>
       </c>
       <c r="O2" t="n">
-        <v>7666.75</v>
+        <v>7673</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -720,72 +720,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C3" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D3" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E3" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F3" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H3" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I3" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J3" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K3" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L3" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M3" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N3" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O3" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -797,59 +795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C4" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D4" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E4" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H4" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I4" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J4" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K4" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L4" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M4" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N4" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O4" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -886,70 +880,72 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C5" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D5" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E5" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F5" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H5" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I5" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J5" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K5" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L5" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M5" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N5" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O5" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -961,77 +957,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C6" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D6" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E6" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F6" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H6" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I6" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J6" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K6" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L6" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M6" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N6" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O6" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1045,57 +1043,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C7" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D7" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E7" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F7" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H7" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I7" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J7" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K7" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L7" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M7" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N7" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O7" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1127,79 +1125,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C8" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D8" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E8" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F8" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H8" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I8" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J8" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K8" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L8" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M8" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N8" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O8" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1211,55 +1207,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C9" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D9" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E9" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F9" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H9" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I9" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J9" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K9" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L9" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M9" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N9" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O9" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1295,79 +1295,77 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C10" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D10" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E10" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F10" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H10" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I10" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J10" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K10" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L10" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M10" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N10" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O10" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1381,57 +1379,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C11" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D11" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E11" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F11" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I11" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J11" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K11" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L11" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M11" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N11" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O11" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,9 +1440,9 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
@@ -1452,8 +1450,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1465,57 +1465,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C12" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D12" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E12" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F12" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H12" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I12" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J12" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K12" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L12" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M12" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N12" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O12" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1523,23 +1523,21 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1558,65 +1556,69 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C13" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D13" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E13" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H13" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I13" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J13" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K13" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L13" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M13" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N13" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O13" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1628,83 +1630,73 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C14" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D14" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E14" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H14" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I14" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J14" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K14" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L14" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M14" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N14" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O14" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>7687.25</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1721,55 +1713,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C15" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D15" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E15" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H15" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I15" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J15" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K15" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L15" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M15" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N15" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O15" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1785,11 +1781,15 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1808,50 +1808,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C16" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D16" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E16" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F16" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H16" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I16" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J16" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K16" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L16" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M16" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N16" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O16" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1862,20 +1862,16 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1894,67 +1890,75 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C17" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D17" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E17" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H17" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I17" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J17" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K17" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L17" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M17" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N17" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O17" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1969,86 +1973,82 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C18" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D18" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E18" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F18" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H18" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I18" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J18" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K18" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L18" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M18" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N18" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O18" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2059,57 +2059,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C19" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D19" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E19" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F19" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H19" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I19" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J19" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K19" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L19" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M19" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N19" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O19" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2127,14 +2127,12 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2145,57 +2143,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C20" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D20" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E20" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F20" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H20" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I20" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J20" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K20" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L20" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M20" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N20" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O20" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2213,11 +2211,13 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2236,50 +2236,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C21" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D21" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E21" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F21" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H21" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I21" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J21" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K21" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L21" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M21" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N21" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O21" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2305,67 +2305,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C22" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D22" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E22" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F22" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H22" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I22" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J22" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K22" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L22" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M22" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N22" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O22" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2378,78 +2376,76 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C23" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D23" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E23" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F23" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H23" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I23" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J23" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K23" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L23" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M23" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N23" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O23" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2457,12 +2453,14 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2481,57 +2479,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C24" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D24" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E24" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F24" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H24" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I24" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J24" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K24" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L24" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M24" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N24" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O24" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2539,22 +2537,24 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
@@ -2563,59 +2563,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C25" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D25" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E25" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F25" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H25" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I25" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J25" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K25" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L25" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M25" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N25" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O25" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2628,18 +2624,14 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2649,72 +2641,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C26" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D26" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E26" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H26" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I26" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J26" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K26" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L26" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M26" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N26" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O26" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2729,81 +2731,77 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C27" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D27" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E27" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F27" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H27" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I27" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J27" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K27" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L27" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M27" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N27" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O27" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2817,57 +2815,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C28" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D28" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E28" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H28" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I28" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J28" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K28" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L28" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M28" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N28" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O28" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2885,12 +2883,14 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
@@ -2899,59 +2899,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C29" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D29" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E29" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F29" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H29" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I29" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J29" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K29" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L29" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M29" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N29" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O29" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2962,20 +2958,16 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2985,72 +2977,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C30" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D30" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E30" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F30" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H30" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I30" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J30" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K30" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L30" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M30" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N30" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O30" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3065,66 +3067,66 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C31" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D31" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E31" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F31" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H31" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I31" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J31" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K31" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L31" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M31" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N31" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O31" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3135,10 +3137,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3160,74 +3160,74 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C32" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D32" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E32" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F32" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H32" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I32" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J32" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K32" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L32" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M32" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N32" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O32" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
       </c>
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3239,81 +3239,81 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C33" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D33" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E33" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H33" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I33" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J33" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K33" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L33" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M33" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N33" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O33" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3325,79 +3325,77 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C34" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D34" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E34" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F34" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H34" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I34" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J34" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K34" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L34" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M34" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N34" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O34" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3411,57 +3409,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C35" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D35" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E35" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F35" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H35" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I35" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J35" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K35" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L35" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M35" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N35" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O35" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3469,18 +3467,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3495,57 +3493,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C36" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D36" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E36" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F36" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H36" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I36" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J36" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K36" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L36" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M36" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N36" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O36" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3553,21 +3551,23 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3577,59 +3577,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C37" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D37" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E37" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F37" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H37" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I37" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J37" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K37" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L37" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M37" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N37" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O37" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3642,18 +3638,14 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3663,55 +3655,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C38" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D38" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E38" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F38" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H38" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I38" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J38" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K38" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L38" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M38" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N38" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O38" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3724,76 +3720,78 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C39" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E39" t="n">
         <v>7722</v>
       </c>
-      <c r="C39" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D39" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E39" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F39" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H39" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I39" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J39" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K39" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L39" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M39" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N39" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O39" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3801,12 +3799,14 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3814,70 +3814,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C40" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D40" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E40" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F40" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H40" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I40" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J40" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K40" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L40" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M40" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N40" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O40" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3895,10 +3895,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3913,67 +3911,71 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C41" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D41" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E41" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F41" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H41" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I41" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J41" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K41" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L41" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M41" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N41" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O41" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
@@ -3990,88 +3992,80 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C42" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D42" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E42" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F42" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H42" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I42" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J42" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K42" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L42" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M42" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N42" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O42" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4083,55 +4077,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C43" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D43" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E43" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F43" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H43" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I43" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J43" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K43" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L43" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M43" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N43" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O43" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4149,14 +4147,18 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W43" s="11" t="inlineStr">
         <is>
@@ -4165,57 +4167,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C44" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D44" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E44" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F44" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H44" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I44" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J44" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K44" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L44" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M44" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N44" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O44" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4226,25 +4228,19 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
@@ -4253,57 +4249,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C45" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D45" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E45" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F45" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H45" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I45" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J45" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K45" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L45" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M45" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N45" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O45" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4311,12 +4307,14 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4333,59 +4331,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C46" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D46" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E46" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F46" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H46" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I46" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J46" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K46" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L46" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M46" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N46" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O46" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4422,50 +4416,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C47" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D47" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E47" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H47" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I47" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J47" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K47" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L47" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M47" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N47" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O47" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4502,50 +4496,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C48" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D48" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E48" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H48" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I48" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J48" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K48" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L48" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M48" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N48" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O48" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4553,22 +4547,24 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4577,55 +4573,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C49" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D49" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E49" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F49" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H49" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I49" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J49" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K49" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L49" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M49" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N49" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O49" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4633,24 +4633,22 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4659,59 +4657,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C50" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D50" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E50" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F50" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H50" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I50" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J50" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K50" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L50" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M50" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N50" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O50" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4748,56 +4742,60 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7631</v>
+        <v>7596.5</v>
       </c>
       <c r="C51" t="n">
-        <v>7633.25</v>
+        <v>7632</v>
       </c>
       <c r="D51" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E51" t="n">
-        <v>7589.25</v>
+        <v>7556.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-35.75</v>
+        <v>-32.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0043</v>
       </c>
       <c r="H51" t="n">
-        <v>56.5</v>
+        <v>122.75</v>
       </c>
       <c r="I51" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J51" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K51" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L51" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M51" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N51" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O51" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+        <v>7689.75</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
@@ -4809,8 +4807,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4828,76 +4828,70 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7596.5</v>
+        <v>7557.5</v>
       </c>
       <c r="C52" t="n">
-        <v>7632</v>
+        <v>7654.5</v>
       </c>
       <c r="D52" t="n">
-        <v>7509.25</v>
+        <v>7551.5</v>
       </c>
       <c r="E52" t="n">
-        <v>7556.5</v>
+        <v>7640</v>
       </c>
       <c r="F52" t="n">
-        <v>-32.75</v>
+        <v>83.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="H52" t="n">
-        <v>122.75</v>
+        <v>103</v>
       </c>
       <c r="I52" t="n">
-        <v>7520.25</v>
+        <v>7386.5</v>
       </c>
       <c r="J52" t="n">
-        <v>7524.88</v>
+        <v>7426.69</v>
       </c>
       <c r="K52" t="n">
-        <v>7561</v>
+        <v>7495.12</v>
       </c>
       <c r="L52" t="n">
-        <v>7597.12</v>
+        <v>7563.56</v>
       </c>
       <c r="M52" t="n">
-        <v>7617.5</v>
+        <v>7617.88</v>
       </c>
       <c r="N52" t="n">
-        <v>7637.88</v>
+        <v>7672.19</v>
       </c>
       <c r="O52" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
+        <v>7754.75</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4909,55 +4903,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7557.5</v>
+        <v>7637</v>
       </c>
       <c r="C53" t="n">
-        <v>7654.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D53" t="n">
-        <v>7551.5</v>
+        <v>7625.25</v>
       </c>
       <c r="E53" t="n">
-        <v>7640</v>
+        <v>7657.35</v>
       </c>
       <c r="F53" t="n">
-        <v>83.5</v>
+        <v>17.35</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0023</v>
       </c>
       <c r="H53" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I53" t="n">
-        <v>7386.5</v>
+        <v>7448.5</v>
       </c>
       <c r="J53" t="n">
-        <v>7426.69</v>
+        <v>7555.5</v>
       </c>
       <c r="K53" t="n">
-        <v>7495.12</v>
+        <v>7588.5</v>
       </c>
       <c r="L53" t="n">
-        <v>7563.56</v>
+        <v>7621.5</v>
       </c>
       <c r="M53" t="n">
-        <v>7617.88</v>
+        <v>7691.5</v>
       </c>
       <c r="N53" t="n">
-        <v>7672.19</v>
+        <v>7761.5</v>
       </c>
       <c r="O53" t="n">
-        <v>7754.75</v>
+        <v>7757.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4998,50 +4996,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7637</v>
+        <v>7722</v>
       </c>
       <c r="C54" t="n">
-        <v>7670.25</v>
+        <v>7847.25</v>
       </c>
       <c r="D54" t="n">
-        <v>7625.25</v>
+        <v>7713.75</v>
       </c>
       <c r="E54" t="n">
-        <v>7657.35</v>
+        <v>7833.5</v>
       </c>
       <c r="F54" t="n">
-        <v>17.35</v>
+        <v>176.15</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.023</v>
       </c>
       <c r="H54" t="n">
-        <v>45</v>
+        <v>133.5</v>
       </c>
       <c r="I54" t="n">
-        <v>7448.5</v>
+        <v>7580.25</v>
       </c>
       <c r="J54" t="n">
-        <v>7555.5</v>
+        <v>7617.15</v>
       </c>
       <c r="K54" t="n">
-        <v>7588.5</v>
+        <v>7634.85</v>
       </c>
       <c r="L54" t="n">
-        <v>7621.5</v>
+        <v>7652.55</v>
       </c>
       <c r="M54" t="n">
-        <v>7691.5</v>
+        <v>7679.85</v>
       </c>
       <c r="N54" t="n">
-        <v>7761.5</v>
+        <v>7707.15</v>
       </c>
       <c r="O54" t="n">
-        <v>7757.5</v>
+        <v>7715.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5059,73 +5057,73 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7722</v>
+        <v>7830</v>
       </c>
       <c r="C55" t="n">
-        <v>7847.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D55" t="n">
-        <v>7713.75</v>
+        <v>7810.5</v>
       </c>
       <c r="E55" t="n">
-        <v>7833.5</v>
+        <v>7831.75</v>
       </c>
       <c r="F55" t="n">
-        <v>176.15</v>
+        <v>-1.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.023</v>
+        <v>-0.0002</v>
       </c>
       <c r="H55" t="n">
-        <v>133.5</v>
+        <v>38</v>
       </c>
       <c r="I55" t="n">
         <v>7580.25</v>
       </c>
       <c r="J55" t="n">
-        <v>7617.15</v>
+        <v>7726.5</v>
       </c>
       <c r="K55" t="n">
-        <v>7634.85</v>
+        <v>7766.75</v>
       </c>
       <c r="L55" t="n">
-        <v>7652.55</v>
+        <v>7807</v>
       </c>
       <c r="M55" t="n">
-        <v>7679.85</v>
+        <v>7900.25</v>
       </c>
       <c r="N55" t="n">
-        <v>7707.15</v>
+        <v>7993.5</v>
       </c>
       <c r="O55" t="n">
-        <v>7715.25</v>
+        <v>7980.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5138,91 +5136,95 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>7830</v>
       </c>
       <c r="C56" t="n">
-        <v>7848.5</v>
+        <v>7843.25</v>
       </c>
       <c r="D56" t="n">
-        <v>7810.5</v>
+        <v>7758.75</v>
       </c>
       <c r="E56" t="n">
-        <v>7831.75</v>
+        <v>7772.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.75</v>
+        <v>-59.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0076</v>
       </c>
       <c r="H56" t="n">
-        <v>38</v>
+        <v>84.5</v>
       </c>
       <c r="I56" t="n">
-        <v>7580.25</v>
+        <v>7772.5</v>
       </c>
       <c r="J56" t="n">
-        <v>7726.5</v>
+        <v>7794.88</v>
       </c>
       <c r="K56" t="n">
-        <v>7766.75</v>
+        <v>7812.75</v>
       </c>
       <c r="L56" t="n">
-        <v>7807</v>
+        <v>7830.62</v>
       </c>
       <c r="M56" t="n">
-        <v>7900.25</v>
+        <v>7850.75</v>
       </c>
       <c r="N56" t="n">
-        <v>7993.5</v>
+        <v>7870.88</v>
       </c>
       <c r="O56" t="n">
-        <v>7980.75</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>7886.5</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5234,83 +5236,75 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7830</v>
+        <v>7774.75</v>
       </c>
       <c r="C57" t="n">
-        <v>7843.25</v>
+        <v>7783.5</v>
       </c>
       <c r="D57" t="n">
-        <v>7758.75</v>
+        <v>7707.25</v>
       </c>
       <c r="E57" t="n">
-        <v>7772.5</v>
+        <v>7767</v>
       </c>
       <c r="F57" t="n">
-        <v>-59.25</v>
+        <v>-5.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0076</v>
+        <v>-0.0007</v>
       </c>
       <c r="H57" t="n">
-        <v>84.5</v>
+        <v>76.25</v>
       </c>
       <c r="I57" t="n">
-        <v>7772.5</v>
+        <v>7674.25</v>
       </c>
       <c r="J57" t="n">
-        <v>7794.88</v>
+        <v>7673.75</v>
       </c>
       <c r="K57" t="n">
-        <v>7812.75</v>
+        <v>7730.25</v>
       </c>
       <c r="L57" t="n">
-        <v>7830.62</v>
+        <v>7786.75</v>
       </c>
       <c r="M57" t="n">
-        <v>7850.75</v>
+        <v>7814.75</v>
       </c>
       <c r="N57" t="n">
-        <v>7870.88</v>
+        <v>7842.75</v>
       </c>
       <c r="O57" t="n">
-        <v>7886.5</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
+        <v>7927.75</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5332,50 +5326,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7774.75</v>
+        <v>7759</v>
       </c>
       <c r="C58" t="n">
-        <v>7783.5</v>
+        <v>7814.75</v>
       </c>
       <c r="D58" t="n">
-        <v>7707.25</v>
+        <v>7748.5</v>
       </c>
       <c r="E58" t="n">
-        <v>7767</v>
+        <v>7803.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-5.5</v>
+        <v>36.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0047</v>
       </c>
       <c r="H58" t="n">
-        <v>76.25</v>
+        <v>66.25</v>
       </c>
       <c r="I58" t="n">
-        <v>7674.25</v>
+        <v>7631</v>
       </c>
       <c r="J58" t="n">
-        <v>7673.75</v>
+        <v>7701.56</v>
       </c>
       <c r="K58" t="n">
-        <v>7730.25</v>
+        <v>7728.88</v>
       </c>
       <c r="L58" t="n">
-        <v>7786.75</v>
+        <v>7756.19</v>
       </c>
       <c r="M58" t="n">
-        <v>7814.75</v>
+        <v>7805.12</v>
       </c>
       <c r="N58" t="n">
-        <v>7842.75</v>
+        <v>7854.06</v>
       </c>
       <c r="O58" t="n">
-        <v>7927.75</v>
+        <v>7859.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5383,18 +5377,18 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5407,75 +5401,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7759</v>
+        <v>7796</v>
       </c>
       <c r="C59" t="n">
-        <v>7814.75</v>
+        <v>7803</v>
       </c>
       <c r="D59" t="n">
-        <v>7748.5</v>
+        <v>7726</v>
       </c>
       <c r="E59" t="n">
-        <v>7803.75</v>
+        <v>7746.75</v>
       </c>
       <c r="F59" t="n">
-        <v>36.75</v>
+        <v>-57</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0047</v>
+        <v>-0.0073</v>
       </c>
       <c r="H59" t="n">
-        <v>66.25</v>
+        <v>77</v>
       </c>
       <c r="I59" t="n">
-        <v>7631</v>
+        <v>7682.25</v>
       </c>
       <c r="J59" t="n">
-        <v>7701.56</v>
+        <v>7748.56</v>
       </c>
       <c r="K59" t="n">
-        <v>7728.88</v>
+        <v>7770.62</v>
       </c>
       <c r="L59" t="n">
-        <v>7756.19</v>
+        <v>7792.69</v>
       </c>
       <c r="M59" t="n">
-        <v>7805.12</v>
+        <v>7836.88</v>
       </c>
       <c r="N59" t="n">
-        <v>7854.06</v>
+        <v>7881.06</v>
       </c>
       <c r="O59" t="n">
-        <v>7859.75</v>
+        <v>7881</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+      <c r="Q59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5487,76 +5487,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7796</v>
+        <v>7746.5</v>
       </c>
       <c r="C60" t="n">
-        <v>7803</v>
+        <v>7770.75</v>
       </c>
       <c r="D60" t="n">
-        <v>7726</v>
+        <v>7712.25</v>
       </c>
       <c r="E60" t="n">
-        <v>7746.75</v>
+        <v>7732</v>
       </c>
       <c r="F60" t="n">
-        <v>-57</v>
+        <v>-14.75</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0019</v>
       </c>
       <c r="H60" t="n">
-        <v>77</v>
+        <v>58.5</v>
       </c>
       <c r="I60" t="n">
-        <v>7682.25</v>
+        <v>7649</v>
       </c>
       <c r="J60" t="n">
-        <v>7748.56</v>
+        <v>7660.88</v>
       </c>
       <c r="K60" t="n">
-        <v>7770.62</v>
+        <v>7708.25</v>
       </c>
       <c r="L60" t="n">
-        <v>7792.69</v>
+        <v>7755.62</v>
       </c>
       <c r="M60" t="n">
-        <v>7836.88</v>
+        <v>7785.25</v>
       </c>
       <c r="N60" t="n">
-        <v>7881.06</v>
+        <v>7814.88</v>
       </c>
       <c r="O60" t="n">
-        <v>7881</v>
+        <v>7880</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5578,50 +5570,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7746.5</v>
+        <v>7739</v>
       </c>
       <c r="C61" t="n">
-        <v>7770.75</v>
+        <v>7782</v>
       </c>
       <c r="D61" t="n">
-        <v>7712.25</v>
+        <v>7705.5</v>
       </c>
       <c r="E61" t="n">
-        <v>7732</v>
+        <v>7715.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-14.75</v>
+        <v>-16.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0019</v>
+        <v>-0.0021</v>
       </c>
       <c r="H61" t="n">
-        <v>58.5</v>
+        <v>76.5</v>
       </c>
       <c r="I61" t="n">
-        <v>7649</v>
+        <v>7653.75</v>
       </c>
       <c r="J61" t="n">
-        <v>7660.88</v>
+        <v>7668.75</v>
       </c>
       <c r="K61" t="n">
-        <v>7708.25</v>
+        <v>7702.75</v>
       </c>
       <c r="L61" t="n">
-        <v>7755.62</v>
+        <v>7736.75</v>
       </c>
       <c r="M61" t="n">
-        <v>7785.25</v>
+        <v>7761.25</v>
       </c>
       <c r="N61" t="n">
-        <v>7814.88</v>
+        <v>7785.75</v>
       </c>
       <c r="O61" t="n">
-        <v>7880</v>
+        <v>7829.25</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5629,16 +5621,20 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5651,55 +5647,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7739</v>
+        <v>7719.5</v>
       </c>
       <c r="C62" t="n">
-        <v>7782</v>
+        <v>7767.75</v>
       </c>
       <c r="D62" t="n">
-        <v>7705.5</v>
+        <v>7672.75</v>
       </c>
       <c r="E62" t="n">
-        <v>7715.5</v>
+        <v>7724</v>
       </c>
       <c r="F62" t="n">
-        <v>-16.5</v>
+        <v>8.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0021</v>
+        <v>0.0011</v>
       </c>
       <c r="H62" t="n">
-        <v>76.5</v>
+        <v>95</v>
       </c>
       <c r="I62" t="n">
-        <v>7653.75</v>
+        <v>7629</v>
       </c>
       <c r="J62" t="n">
-        <v>7668.75</v>
+        <v>7624.88</v>
       </c>
       <c r="K62" t="n">
-        <v>7702.75</v>
+        <v>7677.25</v>
       </c>
       <c r="L62" t="n">
-        <v>7736.75</v>
+        <v>7729.62</v>
       </c>
       <c r="M62" t="n">
-        <v>7761.25</v>
+        <v>7753.75</v>
       </c>
       <c r="N62" t="n">
-        <v>7785.75</v>
+        <v>7777.88</v>
       </c>
       <c r="O62" t="n">
-        <v>7829.25</v>
+        <v>7858.5</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5709,12 +5709,12 @@
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
@@ -5742,50 +5742,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>7724</v>
       </c>
       <c r="C63" t="n">
-        <v>7727.25</v>
+        <v>7810.25</v>
       </c>
       <c r="D63" t="n">
         <v>7723.25</v>
       </c>
       <c r="E63" t="n">
-        <v>7726</v>
+        <v>7777.25</v>
       </c>
       <c r="F63" t="n">
-        <v>10.5</v>
+        <v>53.25</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0069</v>
       </c>
       <c r="H63" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="I63" t="n">
-        <v>7629</v>
+        <v>7577.75</v>
       </c>
       <c r="J63" t="n">
-        <v>7624.88</v>
+        <v>7630.88</v>
       </c>
       <c r="K63" t="n">
-        <v>7677.25</v>
+        <v>7676.5</v>
       </c>
       <c r="L63" t="n">
-        <v>7729.62</v>
+        <v>7722.12</v>
       </c>
       <c r="M63" t="n">
-        <v>7753.75</v>
+        <v>7771.5</v>
       </c>
       <c r="N63" t="n">
-        <v>7777.88</v>
+        <v>7820.88</v>
       </c>
       <c r="O63" t="n">
-        <v>7858.5</v>
+        <v>7862.75</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5796,13 +5796,15 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5817,7 +5819,89 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>7781.5</v>
+      </c>
+      <c r="C64" t="n">
+        <v>7787.75</v>
+      </c>
+      <c r="D64" t="n">
+        <v>7780.75</v>
+      </c>
+      <c r="E64" t="n">
+        <v>7777.25</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>7</v>
+      </c>
+      <c r="I64" t="n">
+        <v>7636.25</v>
+      </c>
+      <c r="J64" t="n">
+        <v>7695.5</v>
+      </c>
+      <c r="K64" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="L64" t="n">
+        <v>7772</v>
+      </c>
+      <c r="M64" t="n">
+        <v>7820.75</v>
+      </c>
+      <c r="N64" t="n">
+        <v>7869.5</v>
+      </c>
+      <c r="O64" t="n">
+        <v>7897.25</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ES_daily.xlsx
+++ b/three_gate/analysis/ES_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,72 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7545</v>
+        <v>7517.25</v>
       </c>
       <c r="C2" t="n">
-        <v>7563</v>
+        <v>7595</v>
       </c>
       <c r="D2" t="n">
-        <v>7468.5</v>
+        <v>7516.25</v>
       </c>
       <c r="E2" t="n">
-        <v>7528.75</v>
+        <v>7588.75</v>
       </c>
       <c r="F2" t="n">
-        <v>-22.5</v>
+        <v>60</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H2" t="n">
-        <v>94.5</v>
+        <v>78.75</v>
       </c>
       <c r="I2" t="n">
-        <v>7457.75</v>
+        <v>7374</v>
       </c>
       <c r="J2" t="n">
-        <v>7472.44</v>
+        <v>7440.75</v>
       </c>
       <c r="K2" t="n">
-        <v>7515.38</v>
+        <v>7481.5</v>
       </c>
       <c r="L2" t="n">
-        <v>7558.31</v>
+        <v>7522.25</v>
       </c>
       <c r="M2" t="n">
-        <v>7587.12</v>
+        <v>7576</v>
       </c>
       <c r="N2" t="n">
-        <v>7615.94</v>
+        <v>7629.75</v>
       </c>
       <c r="O2" t="n">
-        <v>7673</v>
+        <v>7657.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -711,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7517.25</v>
+        <v>7587.25</v>
       </c>
       <c r="C3" t="n">
-        <v>7595</v>
+        <v>7628.75</v>
       </c>
       <c r="D3" t="n">
-        <v>7516.25</v>
+        <v>7552.75</v>
       </c>
       <c r="E3" t="n">
-        <v>7588.75</v>
+        <v>7620.25</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>31.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0042</v>
       </c>
       <c r="H3" t="n">
-        <v>78.75</v>
+        <v>76</v>
       </c>
       <c r="I3" t="n">
-        <v>7374</v>
+        <v>7437.5</v>
       </c>
       <c r="J3" t="n">
-        <v>7440.75</v>
+        <v>7526.56</v>
       </c>
       <c r="K3" t="n">
-        <v>7481.5</v>
+        <v>7549.38</v>
       </c>
       <c r="L3" t="n">
-        <v>7522.25</v>
+        <v>7572.19</v>
       </c>
       <c r="M3" t="n">
-        <v>7576</v>
+        <v>7628.12</v>
       </c>
       <c r="N3" t="n">
-        <v>7629.75</v>
+        <v>7684.06</v>
       </c>
       <c r="O3" t="n">
-        <v>7657.5</v>
+        <v>7673.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,7 +768,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -800,69 +794,71 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7587.25</v>
+        <v>7607</v>
       </c>
       <c r="C4" t="n">
-        <v>7628.75</v>
+        <v>7615.25</v>
       </c>
       <c r="D4" t="n">
-        <v>7552.75</v>
+        <v>7547.25</v>
       </c>
       <c r="E4" t="n">
-        <v>7620.25</v>
+        <v>7563</v>
       </c>
       <c r="F4" t="n">
-        <v>31.5</v>
+        <v>-57.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0075</v>
       </c>
       <c r="H4" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I4" t="n">
-        <v>7437.5</v>
+        <v>7476.75</v>
       </c>
       <c r="J4" t="n">
-        <v>7526.56</v>
+        <v>7559</v>
       </c>
       <c r="K4" t="n">
-        <v>7549.38</v>
+        <v>7582.25</v>
       </c>
       <c r="L4" t="n">
-        <v>7572.19</v>
+        <v>7605.5</v>
       </c>
       <c r="M4" t="n">
-        <v>7628.12</v>
+        <v>7658.25</v>
       </c>
       <c r="N4" t="n">
-        <v>7684.06</v>
+        <v>7711</v>
       </c>
       <c r="O4" t="n">
-        <v>7673.75</v>
+        <v>7704.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -875,77 +871,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7607</v>
+        <v>7557</v>
       </c>
       <c r="C5" t="n">
-        <v>7615.25</v>
+        <v>7613.75</v>
       </c>
       <c r="D5" t="n">
-        <v>7547.25</v>
+        <v>7531.5</v>
       </c>
       <c r="E5" t="n">
-        <v>7563</v>
+        <v>7591.25</v>
       </c>
       <c r="F5" t="n">
-        <v>-57.25</v>
+        <v>28.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0037</v>
       </c>
       <c r="H5" t="n">
-        <v>68</v>
+        <v>82.25</v>
       </c>
       <c r="I5" t="n">
-        <v>7476.75</v>
+        <v>7479.25</v>
       </c>
       <c r="J5" t="n">
-        <v>7559</v>
+        <v>7485.88</v>
       </c>
       <c r="K5" t="n">
-        <v>7582.25</v>
+        <v>7529</v>
       </c>
       <c r="L5" t="n">
-        <v>7605.5</v>
+        <v>7572.12</v>
       </c>
       <c r="M5" t="n">
-        <v>7658.25</v>
+        <v>7597</v>
       </c>
       <c r="N5" t="n">
-        <v>7711</v>
+        <v>7621.88</v>
       </c>
       <c r="O5" t="n">
-        <v>7704.75</v>
+        <v>7683.25</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -959,57 +957,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7557</v>
+        <v>7589.75</v>
       </c>
       <c r="C6" t="n">
-        <v>7613.75</v>
+        <v>7626.25</v>
       </c>
       <c r="D6" t="n">
-        <v>7531.5</v>
+        <v>7571.75</v>
       </c>
       <c r="E6" t="n">
-        <v>7591.25</v>
+        <v>7614.75</v>
       </c>
       <c r="F6" t="n">
-        <v>28.25</v>
+        <v>23.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="H6" t="n">
-        <v>82.25</v>
+        <v>54.5</v>
       </c>
       <c r="I6" t="n">
-        <v>7479.25</v>
+        <v>7449.25</v>
       </c>
       <c r="J6" t="n">
-        <v>7485.88</v>
+        <v>7518.31</v>
       </c>
       <c r="K6" t="n">
-        <v>7529</v>
+        <v>7550.12</v>
       </c>
       <c r="L6" t="n">
-        <v>7572.12</v>
+        <v>7581.94</v>
       </c>
       <c r="M6" t="n">
-        <v>7597</v>
+        <v>7632.38</v>
       </c>
       <c r="N6" t="n">
-        <v>7621.88</v>
+        <v>7682.81</v>
       </c>
       <c r="O6" t="n">
-        <v>7683.25</v>
+        <v>7696</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,7 +1018,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1041,78 +1039,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7589.75</v>
+        <v>7615</v>
       </c>
       <c r="C7" t="n">
-        <v>7626.25</v>
+        <v>7632</v>
       </c>
       <c r="D7" t="n">
-        <v>7571.75</v>
+        <v>7548.25</v>
       </c>
       <c r="E7" t="n">
-        <v>7614.75</v>
+        <v>7577.75</v>
       </c>
       <c r="F7" t="n">
-        <v>23.5</v>
+        <v>-37</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0049</v>
       </c>
       <c r="H7" t="n">
-        <v>54.5</v>
+        <v>83.75</v>
       </c>
       <c r="I7" t="n">
-        <v>7449.25</v>
+        <v>7517.25</v>
       </c>
       <c r="J7" t="n">
-        <v>7518.31</v>
+        <v>7568.12</v>
       </c>
       <c r="K7" t="n">
-        <v>7550.12</v>
+        <v>7587.5</v>
       </c>
       <c r="L7" t="n">
-        <v>7581.94</v>
+        <v>7606.88</v>
       </c>
       <c r="M7" t="n">
-        <v>7632.38</v>
+        <v>7642</v>
       </c>
       <c r="N7" t="n">
-        <v>7682.81</v>
+        <v>7677.12</v>
       </c>
       <c r="O7" t="n">
-        <v>7696</v>
+        <v>7680.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1125,55 +1121,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7615</v>
+        <v>7572.75</v>
       </c>
       <c r="C8" t="n">
-        <v>7632</v>
+        <v>7575</v>
       </c>
       <c r="D8" t="n">
-        <v>7548.25</v>
+        <v>7473</v>
       </c>
       <c r="E8" t="n">
-        <v>7577.75</v>
+        <v>7497.75</v>
       </c>
       <c r="F8" t="n">
-        <v>-37</v>
+        <v>-80</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0106</v>
       </c>
       <c r="H8" t="n">
-        <v>83.75</v>
+        <v>102</v>
       </c>
       <c r="I8" t="n">
-        <v>7517.25</v>
+        <v>7464.5</v>
       </c>
       <c r="J8" t="n">
-        <v>7568.12</v>
+        <v>7487.81</v>
       </c>
       <c r="K8" t="n">
-        <v>7587.5</v>
+        <v>7535.88</v>
       </c>
       <c r="L8" t="n">
-        <v>7606.88</v>
+        <v>7583.94</v>
       </c>
       <c r="M8" t="n">
-        <v>7642</v>
+        <v>7619.62</v>
       </c>
       <c r="N8" t="n">
-        <v>7677.12</v>
+        <v>7655.31</v>
       </c>
       <c r="O8" t="n">
-        <v>7680.75</v>
+        <v>7715.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,7 +1188,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1209,79 +1209,77 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7572.75</v>
+        <v>7485</v>
       </c>
       <c r="C9" t="n">
-        <v>7575</v>
+        <v>7552</v>
       </c>
       <c r="D9" t="n">
-        <v>7473</v>
+        <v>7476.75</v>
       </c>
       <c r="E9" t="n">
-        <v>7497.75</v>
+        <v>7484.25</v>
       </c>
       <c r="F9" t="n">
-        <v>-80</v>
+        <v>-13.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0106</v>
+        <v>-0.0018</v>
       </c>
       <c r="H9" t="n">
-        <v>102</v>
+        <v>75.25</v>
       </c>
       <c r="I9" t="n">
-        <v>7464.5</v>
+        <v>7371</v>
       </c>
       <c r="J9" t="n">
-        <v>7487.81</v>
+        <v>7382.62</v>
       </c>
       <c r="K9" t="n">
-        <v>7535.88</v>
+        <v>7446.75</v>
       </c>
       <c r="L9" t="n">
-        <v>7583.94</v>
+        <v>7510.88</v>
       </c>
       <c r="M9" t="n">
-        <v>7619.62</v>
+        <v>7548.75</v>
       </c>
       <c r="N9" t="n">
-        <v>7655.31</v>
+        <v>7586.62</v>
       </c>
       <c r="O9" t="n">
-        <v>7715.75</v>
+        <v>7677</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1295,57 +1293,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="C10" t="n">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D10" t="n">
-        <v>7476.75</v>
+        <v>7473</v>
       </c>
       <c r="E10" t="n">
-        <v>7484.25</v>
+        <v>7545.75</v>
       </c>
       <c r="F10" t="n">
-        <v>-13.5</v>
+        <v>61.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>75.25</v>
+        <v>81</v>
       </c>
       <c r="I10" t="n">
-        <v>7371</v>
+        <v>7401.5</v>
       </c>
       <c r="J10" t="n">
-        <v>7382.62</v>
+        <v>7393.94</v>
       </c>
       <c r="K10" t="n">
-        <v>7446.75</v>
+        <v>7446.62</v>
       </c>
       <c r="L10" t="n">
-        <v>7510.88</v>
+        <v>7499.31</v>
       </c>
       <c r="M10" t="n">
-        <v>7548.75</v>
+        <v>7521.88</v>
       </c>
       <c r="N10" t="n">
-        <v>7586.62</v>
+        <v>7544.44</v>
       </c>
       <c r="O10" t="n">
-        <v>7677</v>
+        <v>7627.25</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1358,7 +1356,7 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
@@ -1366,8 +1364,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1379,57 +1379,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7484</v>
+        <v>7545</v>
       </c>
       <c r="C11" t="n">
-        <v>7554</v>
+        <v>7563.5</v>
       </c>
       <c r="D11" t="n">
-        <v>7473</v>
+        <v>7504</v>
       </c>
       <c r="E11" t="n">
-        <v>7545.75</v>
+        <v>7540.25</v>
       </c>
       <c r="F11" t="n">
-        <v>61.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H11" t="n">
-        <v>81</v>
+        <v>59.5</v>
       </c>
       <c r="I11" t="n">
-        <v>7401.5</v>
+        <v>7392</v>
       </c>
       <c r="J11" t="n">
-        <v>7393.94</v>
+        <v>7480.88</v>
       </c>
       <c r="K11" t="n">
-        <v>7446.62</v>
+        <v>7505.25</v>
       </c>
       <c r="L11" t="n">
-        <v>7499.31</v>
+        <v>7529.62</v>
       </c>
       <c r="M11" t="n">
-        <v>7521.88</v>
+        <v>7586.25</v>
       </c>
       <c r="N11" t="n">
-        <v>7544.44</v>
+        <v>7642.88</v>
       </c>
       <c r="O11" t="n">
-        <v>7627.25</v>
+        <v>7635</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1437,23 +1437,21 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1472,56 +1470,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7545</v>
+        <v>7530.25</v>
       </c>
       <c r="C12" t="n">
-        <v>7563.5</v>
+        <v>7549.5</v>
       </c>
       <c r="D12" t="n">
-        <v>7504</v>
+        <v>7411.75</v>
       </c>
       <c r="E12" t="n">
-        <v>7540.25</v>
+        <v>7445</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.5</v>
+        <v>-95.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0126</v>
       </c>
       <c r="H12" t="n">
-        <v>59.5</v>
+        <v>137.75</v>
       </c>
       <c r="I12" t="n">
-        <v>7392</v>
+        <v>7444.5</v>
       </c>
       <c r="J12" t="n">
-        <v>7480.88</v>
+        <v>7484</v>
       </c>
       <c r="K12" t="n">
-        <v>7505.25</v>
+        <v>7510.5</v>
       </c>
       <c r="L12" t="n">
-        <v>7529.62</v>
+        <v>7537</v>
       </c>
       <c r="M12" t="n">
-        <v>7586.25</v>
+        <v>7570</v>
       </c>
       <c r="N12" t="n">
-        <v>7642.88</v>
+        <v>7603</v>
       </c>
       <c r="O12" t="n">
-        <v>7635</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+        <v>7623</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
@@ -1530,7 +1532,7 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1542,83 +1544,73 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7530.25</v>
+        <v>7450.5</v>
       </c>
       <c r="C13" t="n">
-        <v>7549.5</v>
+        <v>7496.5</v>
       </c>
       <c r="D13" t="n">
-        <v>7411.75</v>
+        <v>7431.5</v>
       </c>
       <c r="E13" t="n">
-        <v>7445</v>
+        <v>7447.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-95.25</v>
+        <v>2.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="H13" t="n">
-        <v>137.75</v>
+        <v>65</v>
       </c>
       <c r="I13" t="n">
-        <v>7444.5</v>
+        <v>7274</v>
       </c>
       <c r="J13" t="n">
-        <v>7484</v>
+        <v>7289.44</v>
       </c>
       <c r="K13" t="n">
-        <v>7510.5</v>
+        <v>7376.12</v>
       </c>
       <c r="L13" t="n">
-        <v>7537</v>
+        <v>7462.81</v>
       </c>
       <c r="M13" t="n">
-        <v>7570</v>
+        <v>7513.88</v>
       </c>
       <c r="N13" t="n">
-        <v>7603</v>
+        <v>7564.94</v>
       </c>
       <c r="O13" t="n">
-        <v>7623</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>7687.25</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1635,55 +1627,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7450.5</v>
+        <v>7490</v>
       </c>
       <c r="C14" t="n">
-        <v>7496.5</v>
+        <v>7524.75</v>
       </c>
       <c r="D14" t="n">
-        <v>7431.5</v>
+        <v>7416.25</v>
       </c>
       <c r="E14" t="n">
-        <v>7447.5</v>
+        <v>7448.25</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H14" t="n">
-        <v>65</v>
+        <v>108.5</v>
       </c>
       <c r="I14" t="n">
-        <v>7274</v>
+        <v>7366.5</v>
       </c>
       <c r="J14" t="n">
-        <v>7289.44</v>
+        <v>7374.25</v>
       </c>
       <c r="K14" t="n">
-        <v>7376.12</v>
+        <v>7415</v>
       </c>
       <c r="L14" t="n">
-        <v>7462.81</v>
+        <v>7455.75</v>
       </c>
       <c r="M14" t="n">
-        <v>7513.88</v>
+        <v>7480</v>
       </c>
       <c r="N14" t="n">
-        <v>7564.94</v>
+        <v>7504.25</v>
       </c>
       <c r="O14" t="n">
-        <v>7687.25</v>
+        <v>7561.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,16 +1690,20 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1722,50 +1722,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7490</v>
+        <v>7453</v>
       </c>
       <c r="C15" t="n">
-        <v>7524.75</v>
+        <v>7485.75</v>
       </c>
       <c r="D15" t="n">
-        <v>7416.25</v>
+        <v>7417</v>
       </c>
       <c r="E15" t="n">
-        <v>7448.25</v>
+        <v>7465.25</v>
       </c>
       <c r="F15" t="n">
-        <v>0.75</v>
+        <v>17</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0023</v>
       </c>
       <c r="H15" t="n">
-        <v>108.5</v>
+        <v>68.75</v>
       </c>
       <c r="I15" t="n">
-        <v>7366.5</v>
+        <v>7307.75</v>
       </c>
       <c r="J15" t="n">
-        <v>7374.25</v>
+        <v>7328.62</v>
       </c>
       <c r="K15" t="n">
-        <v>7415</v>
+        <v>7394</v>
       </c>
       <c r="L15" t="n">
-        <v>7455.75</v>
+        <v>7459.38</v>
       </c>
       <c r="M15" t="n">
-        <v>7480</v>
+        <v>7502.5</v>
       </c>
       <c r="N15" t="n">
-        <v>7504.25</v>
+        <v>7545.62</v>
       </c>
       <c r="O15" t="n">
-        <v>7561.5</v>
+        <v>7633.25</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1778,18 +1778,14 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1808,67 +1804,75 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7453</v>
+        <v>7464</v>
       </c>
       <c r="C16" t="n">
-        <v>7485.75</v>
+        <v>7501</v>
       </c>
       <c r="D16" t="n">
-        <v>7417</v>
+        <v>7324</v>
       </c>
       <c r="E16" t="n">
-        <v>7465.25</v>
+        <v>7351.25</v>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>-114</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0153</v>
       </c>
       <c r="H16" t="n">
-        <v>68.75</v>
+        <v>177</v>
       </c>
       <c r="I16" t="n">
-        <v>7307.75</v>
+        <v>7348.25</v>
       </c>
       <c r="J16" t="n">
-        <v>7328.62</v>
+        <v>7403.44</v>
       </c>
       <c r="K16" t="n">
-        <v>7394</v>
+        <v>7430.88</v>
       </c>
       <c r="L16" t="n">
-        <v>7459.38</v>
+        <v>7458.31</v>
       </c>
       <c r="M16" t="n">
-        <v>7502.5</v>
+        <v>7499.62</v>
       </c>
       <c r="N16" t="n">
-        <v>7545.62</v>
+        <v>7540.94</v>
       </c>
       <c r="O16" t="n">
-        <v>7633.25</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+        <v>7554.5</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1883,86 +1887,82 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7464</v>
+        <v>7338</v>
       </c>
       <c r="C17" t="n">
-        <v>7501</v>
+        <v>7498</v>
       </c>
       <c r="D17" t="n">
-        <v>7324</v>
+        <v>7331</v>
       </c>
       <c r="E17" t="n">
-        <v>7351.25</v>
+        <v>7472.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-114</v>
+        <v>121.25</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0153</v>
+        <v>0.0165</v>
       </c>
       <c r="H17" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I17" t="n">
-        <v>7348.25</v>
+        <v>7147</v>
       </c>
       <c r="J17" t="n">
-        <v>7403.44</v>
+        <v>7143.62</v>
       </c>
       <c r="K17" t="n">
-        <v>7430.88</v>
+        <v>7262.75</v>
       </c>
       <c r="L17" t="n">
-        <v>7458.31</v>
+        <v>7381.88</v>
       </c>
       <c r="M17" t="n">
-        <v>7499.62</v>
+        <v>7439.75</v>
       </c>
       <c r="N17" t="n">
-        <v>7540.94</v>
+        <v>7497.62</v>
       </c>
       <c r="O17" t="n">
-        <v>7554.5</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>7678</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7338</v>
+        <v>7479.5</v>
       </c>
       <c r="C18" t="n">
-        <v>7498</v>
+        <v>7541</v>
       </c>
       <c r="D18" t="n">
-        <v>7331</v>
+        <v>7427.5</v>
       </c>
       <c r="E18" t="n">
-        <v>7472.5</v>
+        <v>7519.25</v>
       </c>
       <c r="F18" t="n">
-        <v>121.25</v>
+        <v>46.75</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0063</v>
       </c>
       <c r="H18" t="n">
-        <v>167</v>
+        <v>113.5</v>
       </c>
       <c r="I18" t="n">
-        <v>7147</v>
+        <v>7164</v>
       </c>
       <c r="J18" t="n">
-        <v>7143.62</v>
+        <v>7334.5</v>
       </c>
       <c r="K18" t="n">
-        <v>7262.75</v>
+        <v>7389</v>
       </c>
       <c r="L18" t="n">
-        <v>7381.88</v>
+        <v>7443.5</v>
       </c>
       <c r="M18" t="n">
-        <v>7439.75</v>
+        <v>7556</v>
       </c>
       <c r="N18" t="n">
-        <v>7497.62</v>
+        <v>7668.5</v>
       </c>
       <c r="O18" t="n">
-        <v>7678</v>
+        <v>7665</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2034,21 +2034,19 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2059,57 +2057,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7479.5</v>
+        <v>7550</v>
       </c>
       <c r="C19" t="n">
-        <v>7541</v>
+        <v>7637.75</v>
       </c>
       <c r="D19" t="n">
-        <v>7427.5</v>
+        <v>7542.75</v>
       </c>
       <c r="E19" t="n">
-        <v>7519.25</v>
+        <v>7628.25</v>
       </c>
       <c r="F19" t="n">
-        <v>46.75</v>
+        <v>109</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0063</v>
+        <v>0.0145</v>
       </c>
       <c r="H19" t="n">
-        <v>113.5</v>
+        <v>95</v>
       </c>
       <c r="I19" t="n">
-        <v>7164</v>
+        <v>7314</v>
       </c>
       <c r="J19" t="n">
-        <v>7334.5</v>
+        <v>7423.25</v>
       </c>
       <c r="K19" t="n">
-        <v>7389</v>
+        <v>7462.5</v>
       </c>
       <c r="L19" t="n">
-        <v>7443.5</v>
+        <v>7501.75</v>
       </c>
       <c r="M19" t="n">
-        <v>7556</v>
+        <v>7576</v>
       </c>
       <c r="N19" t="n">
-        <v>7668.5</v>
+        <v>7650.25</v>
       </c>
       <c r="O19" t="n">
-        <v>7665</v>
+        <v>7654.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2120,18 +2118,20 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2150,50 +2150,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7550</v>
+        <v>7631</v>
       </c>
       <c r="C20" t="n">
-        <v>7637.75</v>
+        <v>7786</v>
       </c>
       <c r="D20" t="n">
-        <v>7542.75</v>
+        <v>7629</v>
       </c>
       <c r="E20" t="n">
-        <v>7628.25</v>
+        <v>7765.5</v>
       </c>
       <c r="F20" t="n">
-        <v>109</v>
+        <v>137.25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.018</v>
       </c>
       <c r="H20" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="I20" t="n">
-        <v>7314</v>
+        <v>7447.75</v>
       </c>
       <c r="J20" t="n">
-        <v>7423.25</v>
+        <v>7552.25</v>
       </c>
       <c r="K20" t="n">
-        <v>7462.5</v>
+        <v>7580.75</v>
       </c>
       <c r="L20" t="n">
-        <v>7501.75</v>
+        <v>7609.25</v>
       </c>
       <c r="M20" t="n">
-        <v>7576</v>
+        <v>7675.75</v>
       </c>
       <c r="N20" t="n">
-        <v>7650.25</v>
+        <v>7742.25</v>
       </c>
       <c r="O20" t="n">
-        <v>7654.5</v>
+        <v>7732.75</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2204,7 +2204,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2219,67 +2219,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7631</v>
+        <v>7772</v>
       </c>
       <c r="C21" t="n">
-        <v>7786</v>
+        <v>7820.25</v>
       </c>
       <c r="D21" t="n">
-        <v>7629</v>
+        <v>7745.75</v>
       </c>
       <c r="E21" t="n">
-        <v>7765.5</v>
+        <v>7749.5</v>
       </c>
       <c r="F21" t="n">
-        <v>137.25</v>
+        <v>-16</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.018</v>
+        <v>-0.0021</v>
       </c>
       <c r="H21" t="n">
-        <v>157</v>
+        <v>74.5</v>
       </c>
       <c r="I21" t="n">
-        <v>7447.75</v>
+        <v>7472</v>
       </c>
       <c r="J21" t="n">
-        <v>7552.25</v>
+        <v>7637.5</v>
       </c>
       <c r="K21" t="n">
-        <v>7580.75</v>
+        <v>7687</v>
       </c>
       <c r="L21" t="n">
-        <v>7609.25</v>
+        <v>7736.5</v>
       </c>
       <c r="M21" t="n">
-        <v>7675.75</v>
+        <v>7844</v>
       </c>
       <c r="N21" t="n">
-        <v>7742.25</v>
+        <v>7951.5</v>
       </c>
       <c r="O21" t="n">
-        <v>7732.75</v>
+        <v>7943</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2290,80 +2288,78 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7772</v>
+        <v>7756.75</v>
       </c>
       <c r="C22" t="n">
-        <v>7820.25</v>
+        <v>7770.75</v>
       </c>
       <c r="D22" t="n">
-        <v>7745.75</v>
+        <v>7724.25</v>
       </c>
       <c r="E22" t="n">
-        <v>7749.5</v>
+        <v>7734.75</v>
       </c>
       <c r="F22" t="n">
-        <v>-16</v>
+        <v>-14.75</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0019</v>
       </c>
       <c r="H22" t="n">
-        <v>74.5</v>
+        <v>46.5</v>
       </c>
       <c r="I22" t="n">
-        <v>7472</v>
+        <v>7671.25</v>
       </c>
       <c r="J22" t="n">
-        <v>7637.5</v>
+        <v>7658.25</v>
       </c>
       <c r="K22" t="n">
-        <v>7687</v>
+        <v>7712.25</v>
       </c>
       <c r="L22" t="n">
-        <v>7736.5</v>
+        <v>7766.25</v>
       </c>
       <c r="M22" t="n">
-        <v>7844</v>
+        <v>7786.75</v>
       </c>
       <c r="N22" t="n">
-        <v>7951.5</v>
+        <v>7807.25</v>
       </c>
       <c r="O22" t="n">
-        <v>7943</v>
+        <v>7894.75</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2371,12 +2367,14 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2395,57 +2393,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7756.75</v>
+        <v>7735</v>
       </c>
       <c r="C23" t="n">
-        <v>7770.75</v>
+        <v>7786.75</v>
       </c>
       <c r="D23" t="n">
-        <v>7724.25</v>
+        <v>7725.5</v>
       </c>
       <c r="E23" t="n">
-        <v>7734.75</v>
+        <v>7779.75</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.75</v>
+        <v>45</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0058</v>
       </c>
       <c r="H23" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I23" t="n">
-        <v>7671.25</v>
+        <v>7677.75</v>
       </c>
       <c r="J23" t="n">
-        <v>7658.25</v>
+        <v>7681.88</v>
       </c>
       <c r="K23" t="n">
-        <v>7712.25</v>
+        <v>7711.5</v>
       </c>
       <c r="L23" t="n">
-        <v>7766.25</v>
+        <v>7741.12</v>
       </c>
       <c r="M23" t="n">
-        <v>7786.75</v>
+        <v>7758</v>
       </c>
       <c r="N23" t="n">
-        <v>7807.25</v>
+        <v>7774.88</v>
       </c>
       <c r="O23" t="n">
-        <v>7894.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2453,22 +2451,24 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2477,59 +2477,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7735</v>
+        <v>7776.75</v>
       </c>
       <c r="C24" t="n">
-        <v>7786.75</v>
+        <v>7798</v>
       </c>
       <c r="D24" t="n">
-        <v>7725.5</v>
+        <v>7763</v>
       </c>
       <c r="E24" t="n">
-        <v>7779.75</v>
+        <v>7776.75</v>
       </c>
       <c r="F24" t="n">
-        <v>45</v>
+        <v>-3</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0004</v>
       </c>
       <c r="H24" t="n">
-        <v>61.25</v>
+        <v>35</v>
       </c>
       <c r="I24" t="n">
-        <v>7677.75</v>
+        <v>7664.25</v>
       </c>
       <c r="J24" t="n">
-        <v>7681.88</v>
+        <v>7730.31</v>
       </c>
       <c r="K24" t="n">
-        <v>7711.5</v>
+        <v>7749.12</v>
       </c>
       <c r="L24" t="n">
-        <v>7741.12</v>
+        <v>7767.94</v>
       </c>
       <c r="M24" t="n">
-        <v>7758</v>
+        <v>7810.38</v>
       </c>
       <c r="N24" t="n">
-        <v>7774.88</v>
+        <v>7852.81</v>
       </c>
       <c r="O24" t="n">
-        <v>7817.25</v>
+        <v>7848</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2540,20 +2536,16 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2563,72 +2555,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7776.75</v>
+        <v>7778.25</v>
       </c>
       <c r="C25" t="n">
-        <v>7798</v>
+        <v>7796</v>
       </c>
       <c r="D25" t="n">
-        <v>7763</v>
+        <v>7738</v>
       </c>
       <c r="E25" t="n">
-        <v>7776.75</v>
+        <v>7747.5</v>
       </c>
       <c r="F25" t="n">
-        <v>-3</v>
+        <v>-29.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0038</v>
       </c>
       <c r="H25" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I25" t="n">
-        <v>7664.25</v>
+        <v>7728</v>
       </c>
       <c r="J25" t="n">
-        <v>7730.31</v>
+        <v>7739.88</v>
       </c>
       <c r="K25" t="n">
-        <v>7749.12</v>
+        <v>7759.25</v>
       </c>
       <c r="L25" t="n">
-        <v>7767.94</v>
+        <v>7778.62</v>
       </c>
       <c r="M25" t="n">
-        <v>7810.38</v>
+        <v>7794.25</v>
       </c>
       <c r="N25" t="n">
-        <v>7852.81</v>
+        <v>7809.88</v>
       </c>
       <c r="O25" t="n">
-        <v>7848</v>
+        <v>7833</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2643,81 +2645,77 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7778.25</v>
+        <v>7756</v>
       </c>
       <c r="C26" t="n">
-        <v>7796</v>
+        <v>7794</v>
       </c>
       <c r="D26" t="n">
-        <v>7738</v>
+        <v>7748.5</v>
       </c>
       <c r="E26" t="n">
-        <v>7747.5</v>
+        <v>7770.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-29.25</v>
+        <v>23</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.003</v>
       </c>
       <c r="H26" t="n">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="I26" t="n">
-        <v>7728</v>
+        <v>7680</v>
       </c>
       <c r="J26" t="n">
-        <v>7739.88</v>
+        <v>7679.75</v>
       </c>
       <c r="K26" t="n">
-        <v>7759.25</v>
+        <v>7718.5</v>
       </c>
       <c r="L26" t="n">
-        <v>7778.62</v>
+        <v>7757.25</v>
       </c>
       <c r="M26" t="n">
-        <v>7794.25</v>
+        <v>7776.5</v>
       </c>
       <c r="N26" t="n">
-        <v>7809.88</v>
+        <v>7795.75</v>
       </c>
       <c r="O26" t="n">
-        <v>7833</v>
+        <v>7854</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2731,57 +2729,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7756</v>
+        <v>7770</v>
       </c>
       <c r="C27" t="n">
-        <v>7794</v>
+        <v>7838.5</v>
       </c>
       <c r="D27" t="n">
-        <v>7748.5</v>
+        <v>7764.25</v>
       </c>
       <c r="E27" t="n">
-        <v>7770.5</v>
+        <v>7822.5</v>
       </c>
       <c r="F27" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0067</v>
       </c>
       <c r="H27" t="n">
-        <v>45.5</v>
+        <v>74.25</v>
       </c>
       <c r="I27" t="n">
-        <v>7680</v>
+        <v>7703</v>
       </c>
       <c r="J27" t="n">
-        <v>7679.75</v>
+        <v>7724.62</v>
       </c>
       <c r="K27" t="n">
-        <v>7718.5</v>
+        <v>7747.75</v>
       </c>
       <c r="L27" t="n">
-        <v>7757.25</v>
+        <v>7770.88</v>
       </c>
       <c r="M27" t="n">
-        <v>7776.5</v>
+        <v>7793.25</v>
       </c>
       <c r="N27" t="n">
-        <v>7795.75</v>
+        <v>7815.62</v>
       </c>
       <c r="O27" t="n">
-        <v>7854</v>
+        <v>7839.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2792,19 +2790,21 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
@@ -2813,59 +2813,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7770</v>
+        <v>7825</v>
       </c>
       <c r="C28" t="n">
-        <v>7838.5</v>
+        <v>7831.75</v>
       </c>
       <c r="D28" t="n">
-        <v>7764.25</v>
+        <v>7796.5</v>
       </c>
       <c r="E28" t="n">
-        <v>7822.5</v>
+        <v>7805</v>
       </c>
       <c r="F28" t="n">
-        <v>52</v>
+        <v>-17.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0022</v>
       </c>
       <c r="H28" t="n">
-        <v>74.25</v>
+        <v>35.25</v>
       </c>
       <c r="I28" t="n">
-        <v>7703</v>
+        <v>7690</v>
       </c>
       <c r="J28" t="n">
-        <v>7724.62</v>
+        <v>7758.81</v>
       </c>
       <c r="K28" t="n">
-        <v>7747.75</v>
+        <v>7785.38</v>
       </c>
       <c r="L28" t="n">
-        <v>7770.88</v>
+        <v>7811.94</v>
       </c>
       <c r="M28" t="n">
-        <v>7793.25</v>
+        <v>7859.62</v>
       </c>
       <c r="N28" t="n">
-        <v>7815.62</v>
+        <v>7907.31</v>
       </c>
       <c r="O28" t="n">
-        <v>7839.5</v>
+        <v>7912.75</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2878,18 +2874,14 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2899,72 +2891,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7825</v>
+        <v>7809.25</v>
       </c>
       <c r="C29" t="n">
-        <v>7831.75</v>
+        <v>7824.5</v>
       </c>
       <c r="D29" t="n">
-        <v>7796.5</v>
+        <v>7763.5</v>
       </c>
       <c r="E29" t="n">
-        <v>7805</v>
+        <v>7768.75</v>
       </c>
       <c r="F29" t="n">
-        <v>-17.5</v>
+        <v>-36.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0046</v>
       </c>
       <c r="H29" t="n">
-        <v>35.25</v>
+        <v>61</v>
       </c>
       <c r="I29" t="n">
-        <v>7690</v>
+        <v>7761.25</v>
       </c>
       <c r="J29" t="n">
-        <v>7758.81</v>
+        <v>7765.19</v>
       </c>
       <c r="K29" t="n">
-        <v>7785.38</v>
+        <v>7787.38</v>
       </c>
       <c r="L29" t="n">
-        <v>7811.94</v>
+        <v>7809.56</v>
       </c>
       <c r="M29" t="n">
-        <v>7859.62</v>
+        <v>7822.62</v>
       </c>
       <c r="N29" t="n">
-        <v>7907.31</v>
+        <v>7835.69</v>
       </c>
       <c r="O29" t="n">
-        <v>7912.75</v>
+        <v>7867</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2979,80 +2981,78 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7809.25</v>
+        <v>7766</v>
       </c>
       <c r="C30" t="n">
-        <v>7824.5</v>
+        <v>7770.5</v>
       </c>
       <c r="D30" t="n">
-        <v>7763.5</v>
+        <v>7710.25</v>
       </c>
       <c r="E30" t="n">
-        <v>7768.75</v>
+        <v>7714</v>
       </c>
       <c r="F30" t="n">
-        <v>-36.25</v>
+        <v>-54.75</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.007</v>
       </c>
       <c r="H30" t="n">
-        <v>61</v>
+        <v>60.25</v>
       </c>
       <c r="I30" t="n">
-        <v>7761.25</v>
+        <v>7702.5</v>
       </c>
       <c r="J30" t="n">
-        <v>7765.19</v>
+        <v>7695.12</v>
       </c>
       <c r="K30" t="n">
-        <v>7787.38</v>
+        <v>7738.25</v>
       </c>
       <c r="L30" t="n">
-        <v>7809.56</v>
+        <v>7781.38</v>
       </c>
       <c r="M30" t="n">
-        <v>7822.62</v>
+        <v>7799.25</v>
       </c>
       <c r="N30" t="n">
-        <v>7835.69</v>
+        <v>7817.12</v>
       </c>
       <c r="O30" t="n">
-        <v>7867</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
+        <v>7885.5</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3074,74 +3074,74 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7766</v>
+        <v>7714</v>
       </c>
       <c r="C31" t="n">
-        <v>7770.5</v>
+        <v>7764.75</v>
       </c>
       <c r="D31" t="n">
-        <v>7710.25</v>
+        <v>7698.25</v>
       </c>
       <c r="E31" t="n">
-        <v>7714</v>
+        <v>7729</v>
       </c>
       <c r="F31" t="n">
-        <v>-54.75</v>
+        <v>15</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H31" t="n">
-        <v>60.25</v>
+        <v>66.5</v>
       </c>
       <c r="I31" t="n">
-        <v>7702.5</v>
+        <v>7650</v>
       </c>
       <c r="J31" t="n">
-        <v>7695.12</v>
+        <v>7640.56</v>
       </c>
       <c r="K31" t="n">
-        <v>7738.25</v>
+        <v>7683.88</v>
       </c>
       <c r="L31" t="n">
-        <v>7781.38</v>
+        <v>7727.19</v>
       </c>
       <c r="M31" t="n">
-        <v>7799.25</v>
+        <v>7744.12</v>
       </c>
       <c r="N31" t="n">
-        <v>7817.12</v>
+        <v>7761.06</v>
       </c>
       <c r="O31" t="n">
-        <v>7885.5</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>7830.75</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
       </c>
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3153,81 +3153,81 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7714</v>
+        <v>7733</v>
       </c>
       <c r="C32" t="n">
-        <v>7764.75</v>
+        <v>7746.5</v>
       </c>
       <c r="D32" t="n">
-        <v>7698.25</v>
+        <v>7657.75</v>
       </c>
       <c r="E32" t="n">
-        <v>7729</v>
+        <v>7662.5</v>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>-66.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="H32" t="n">
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="I32" t="n">
-        <v>7650</v>
+        <v>7631.75</v>
       </c>
       <c r="J32" t="n">
-        <v>7640.56</v>
+        <v>7661.25</v>
       </c>
       <c r="K32" t="n">
-        <v>7683.88</v>
+        <v>7695.75</v>
       </c>
       <c r="L32" t="n">
-        <v>7727.19</v>
+        <v>7730.25</v>
       </c>
       <c r="M32" t="n">
-        <v>7744.12</v>
+        <v>7762.25</v>
       </c>
       <c r="N32" t="n">
-        <v>7761.06</v>
+        <v>7794.25</v>
       </c>
       <c r="O32" t="n">
-        <v>7830.75</v>
+        <v>7831.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3239,79 +3239,77 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7733</v>
+        <v>7669</v>
       </c>
       <c r="C33" t="n">
-        <v>7746.5</v>
+        <v>7714</v>
       </c>
       <c r="D33" t="n">
-        <v>7657.75</v>
+        <v>7661.25</v>
       </c>
       <c r="E33" t="n">
-        <v>7662.5</v>
+        <v>7691.25</v>
       </c>
       <c r="F33" t="n">
-        <v>-66.5</v>
+        <v>28.75</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="H33" t="n">
-        <v>88.75</v>
+        <v>52.75</v>
       </c>
       <c r="I33" t="n">
-        <v>7631.75</v>
+        <v>7569</v>
       </c>
       <c r="J33" t="n">
-        <v>7661.25</v>
+        <v>7553.94</v>
       </c>
       <c r="K33" t="n">
-        <v>7695.75</v>
+        <v>7618.12</v>
       </c>
       <c r="L33" t="n">
-        <v>7730.25</v>
+        <v>7682.31</v>
       </c>
       <c r="M33" t="n">
-        <v>7762.25</v>
+        <v>7706.88</v>
       </c>
       <c r="N33" t="n">
-        <v>7794.25</v>
+        <v>7731.44</v>
       </c>
       <c r="O33" t="n">
-        <v>7831.25</v>
+        <v>7835.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3325,57 +3323,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7669</v>
+        <v>7693.5</v>
       </c>
       <c r="C34" t="n">
-        <v>7714</v>
+        <v>7703.25</v>
       </c>
       <c r="D34" t="n">
-        <v>7661.25</v>
+        <v>7655</v>
       </c>
       <c r="E34" t="n">
-        <v>7691.25</v>
+        <v>7669.75</v>
       </c>
       <c r="F34" t="n">
-        <v>28.75</v>
+        <v>-21.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="H34" t="n">
-        <v>52.75</v>
+        <v>48.25</v>
       </c>
       <c r="I34" t="n">
-        <v>7569</v>
+        <v>7608.5</v>
       </c>
       <c r="J34" t="n">
-        <v>7553.94</v>
+        <v>7640.31</v>
       </c>
       <c r="K34" t="n">
-        <v>7618.12</v>
+        <v>7664.88</v>
       </c>
       <c r="L34" t="n">
-        <v>7682.31</v>
+        <v>7689.44</v>
       </c>
       <c r="M34" t="n">
-        <v>7706.88</v>
+        <v>7717.62</v>
       </c>
       <c r="N34" t="n">
-        <v>7731.44</v>
+        <v>7745.81</v>
       </c>
       <c r="O34" t="n">
-        <v>7835.25</v>
+        <v>7766.75</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3383,18 +3381,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3409,57 +3407,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7693.5</v>
+        <v>7676</v>
       </c>
       <c r="C35" t="n">
-        <v>7703.25</v>
+        <v>7714</v>
       </c>
       <c r="D35" t="n">
-        <v>7655</v>
+        <v>7660.25</v>
       </c>
       <c r="E35" t="n">
-        <v>7669.75</v>
+        <v>7692</v>
       </c>
       <c r="F35" t="n">
-        <v>-21.5</v>
+        <v>22.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="H35" t="n">
-        <v>48.25</v>
+        <v>53.75</v>
       </c>
       <c r="I35" t="n">
-        <v>7608.5</v>
+        <v>7606.75</v>
       </c>
       <c r="J35" t="n">
-        <v>7640.31</v>
+        <v>7616.81</v>
       </c>
       <c r="K35" t="n">
-        <v>7664.88</v>
+        <v>7645.62</v>
       </c>
       <c r="L35" t="n">
-        <v>7689.44</v>
+        <v>7674.44</v>
       </c>
       <c r="M35" t="n">
-        <v>7717.62</v>
+        <v>7693.88</v>
       </c>
       <c r="N35" t="n">
-        <v>7745.81</v>
+        <v>7713.31</v>
       </c>
       <c r="O35" t="n">
-        <v>7766.75</v>
+        <v>7751.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3467,21 +3465,23 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3491,59 +3491,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7676</v>
+        <v>7691.5</v>
       </c>
       <c r="C36" t="n">
-        <v>7714</v>
+        <v>7710.25</v>
       </c>
       <c r="D36" t="n">
-        <v>7660.25</v>
+        <v>7670.75</v>
       </c>
       <c r="E36" t="n">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F36" t="n">
-        <v>22.25</v>
+        <v>-2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H36" t="n">
-        <v>53.75</v>
+        <v>39.5</v>
       </c>
       <c r="I36" t="n">
-        <v>7606.75</v>
+        <v>7606.5</v>
       </c>
       <c r="J36" t="n">
-        <v>7616.81</v>
+        <v>7640.69</v>
       </c>
       <c r="K36" t="n">
-        <v>7645.62</v>
+        <v>7665.12</v>
       </c>
       <c r="L36" t="n">
-        <v>7674.44</v>
+        <v>7689.56</v>
       </c>
       <c r="M36" t="n">
-        <v>7693.88</v>
+        <v>7718.88</v>
       </c>
       <c r="N36" t="n">
-        <v>7713.31</v>
+        <v>7748.19</v>
       </c>
       <c r="O36" t="n">
-        <v>7751.5</v>
+        <v>7767.75</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3554,20 +3550,16 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3577,55 +3569,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7691.5</v>
+        <v>7722</v>
       </c>
       <c r="C37" t="n">
-        <v>7710.25</v>
+        <v>7755.5</v>
       </c>
       <c r="D37" t="n">
-        <v>7670.75</v>
+        <v>7702.75</v>
       </c>
       <c r="E37" t="n">
-        <v>7690</v>
+        <v>7742.5</v>
       </c>
       <c r="F37" t="n">
-        <v>-2</v>
+        <v>52.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0003</v>
+        <v>0.0068</v>
       </c>
       <c r="H37" t="n">
-        <v>39.5</v>
+        <v>52.75</v>
       </c>
       <c r="I37" t="n">
-        <v>7606.5</v>
+        <v>7631.25</v>
       </c>
       <c r="J37" t="n">
-        <v>7640.69</v>
+        <v>7650.25</v>
       </c>
       <c r="K37" t="n">
-        <v>7665.12</v>
+        <v>7670.25</v>
       </c>
       <c r="L37" t="n">
-        <v>7689.56</v>
+        <v>7690.25</v>
       </c>
       <c r="M37" t="n">
-        <v>7718.88</v>
+        <v>7709.75</v>
       </c>
       <c r="N37" t="n">
-        <v>7748.19</v>
+        <v>7729.25</v>
       </c>
       <c r="O37" t="n">
-        <v>7767.75</v>
+        <v>7749.75</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3636,78 +3632,80 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>7733.75</v>
+      </c>
+      <c r="C38" t="n">
+        <v>7782.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7711.75</v>
+      </c>
+      <c r="E38" t="n">
         <v>7722</v>
       </c>
-      <c r="C38" t="n">
-        <v>7755.5</v>
-      </c>
-      <c r="D38" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E38" t="n">
-        <v>7742.5</v>
-      </c>
       <c r="F38" t="n">
-        <v>52.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0026</v>
       </c>
       <c r="H38" t="n">
-        <v>52.75</v>
+        <v>70.75</v>
       </c>
       <c r="I38" t="n">
-        <v>7631.25</v>
+        <v>7650</v>
       </c>
       <c r="J38" t="n">
-        <v>7650.25</v>
+        <v>7696.44</v>
       </c>
       <c r="K38" t="n">
-        <v>7670.25</v>
+        <v>7716.12</v>
       </c>
       <c r="L38" t="n">
-        <v>7690.25</v>
+        <v>7735.81</v>
       </c>
       <c r="M38" t="n">
-        <v>7709.75</v>
+        <v>7768.88</v>
       </c>
       <c r="N38" t="n">
-        <v>7729.25</v>
+        <v>7801.94</v>
       </c>
       <c r="O38" t="n">
-        <v>7749.75</v>
+        <v>7808.25</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3715,12 +3713,14 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3728,70 +3728,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7733.75</v>
+        <v>7723.5</v>
       </c>
       <c r="C39" t="n">
-        <v>7782.5</v>
+        <v>7724</v>
       </c>
       <c r="D39" t="n">
-        <v>7711.75</v>
+        <v>7674.75</v>
       </c>
       <c r="E39" t="n">
-        <v>7722</v>
+        <v>7699</v>
       </c>
       <c r="F39" t="n">
-        <v>-20.5</v>
+        <v>-23</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.003</v>
       </c>
       <c r="H39" t="n">
-        <v>70.75</v>
+        <v>49.25</v>
       </c>
       <c r="I39" t="n">
-        <v>7650</v>
+        <v>7641</v>
       </c>
       <c r="J39" t="n">
-        <v>7696.44</v>
+        <v>7638.69</v>
       </c>
       <c r="K39" t="n">
-        <v>7716.12</v>
+        <v>7686.62</v>
       </c>
       <c r="L39" t="n">
-        <v>7735.81</v>
+        <v>7734.56</v>
       </c>
       <c r="M39" t="n">
-        <v>7768.88</v>
+        <v>7757.38</v>
       </c>
       <c r="N39" t="n">
-        <v>7801.94</v>
+        <v>7780.19</v>
       </c>
       <c r="O39" t="n">
-        <v>7808.25</v>
+        <v>7853.25</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3804,15 +3804,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3827,70 +3825,74 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7723.5</v>
+        <v>7701.25</v>
       </c>
       <c r="C40" t="n">
-        <v>7724</v>
+        <v>7708</v>
       </c>
       <c r="D40" t="n">
-        <v>7674.75</v>
+        <v>7621.5</v>
       </c>
       <c r="E40" t="n">
-        <v>7699</v>
+        <v>7642.75</v>
       </c>
       <c r="F40" t="n">
-        <v>-23</v>
+        <v>-56.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0073</v>
       </c>
       <c r="H40" t="n">
-        <v>49.25</v>
+        <v>86.5</v>
       </c>
       <c r="I40" t="n">
-        <v>7641</v>
+        <v>7625.5</v>
       </c>
       <c r="J40" t="n">
-        <v>7638.69</v>
+        <v>7649.56</v>
       </c>
       <c r="K40" t="n">
-        <v>7686.62</v>
+        <v>7674.38</v>
       </c>
       <c r="L40" t="n">
-        <v>7734.56</v>
+        <v>7699.19</v>
       </c>
       <c r="M40" t="n">
-        <v>7757.38</v>
+        <v>7723.62</v>
       </c>
       <c r="N40" t="n">
-        <v>7780.19</v>
+        <v>7748.06</v>
       </c>
       <c r="O40" t="n">
-        <v>7853.25</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>7773.25</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3904,88 +3906,80 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7701.25</v>
+        <v>7645</v>
       </c>
       <c r="C41" t="n">
-        <v>7708</v>
+        <v>7691.25</v>
       </c>
       <c r="D41" t="n">
-        <v>7621.5</v>
+        <v>7618.5</v>
       </c>
       <c r="E41" t="n">
-        <v>7642.75</v>
+        <v>7676.5</v>
       </c>
       <c r="F41" t="n">
-        <v>-56.25</v>
+        <v>33.75</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0044</v>
       </c>
       <c r="H41" t="n">
-        <v>86.5</v>
+        <v>72.75</v>
       </c>
       <c r="I41" t="n">
-        <v>7625.5</v>
+        <v>7535</v>
       </c>
       <c r="J41" t="n">
-        <v>7649.56</v>
+        <v>7545.25</v>
       </c>
       <c r="K41" t="n">
-        <v>7674.38</v>
+        <v>7599.5</v>
       </c>
       <c r="L41" t="n">
-        <v>7699.19</v>
+        <v>7653.75</v>
       </c>
       <c r="M41" t="n">
-        <v>7723.62</v>
+        <v>7686</v>
       </c>
       <c r="N41" t="n">
-        <v>7748.06</v>
+        <v>7718.25</v>
       </c>
       <c r="O41" t="n">
-        <v>7773.25</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>7794.5</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3997,55 +3991,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7645</v>
+        <v>7673.5</v>
       </c>
       <c r="C42" t="n">
-        <v>7691.25</v>
+        <v>7766.5</v>
       </c>
       <c r="D42" t="n">
-        <v>7618.5</v>
+        <v>7661.25</v>
       </c>
       <c r="E42" t="n">
-        <v>7676.5</v>
+        <v>7754.75</v>
       </c>
       <c r="F42" t="n">
-        <v>33.75</v>
+        <v>78.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0102</v>
       </c>
       <c r="H42" t="n">
-        <v>72.75</v>
+        <v>105.25</v>
       </c>
       <c r="I42" t="n">
-        <v>7535</v>
+        <v>7545.75</v>
       </c>
       <c r="J42" t="n">
-        <v>7545.25</v>
+        <v>7614.56</v>
       </c>
       <c r="K42" t="n">
-        <v>7599.5</v>
+        <v>7640.12</v>
       </c>
       <c r="L42" t="n">
-        <v>7653.75</v>
+        <v>7665.69</v>
       </c>
       <c r="M42" t="n">
-        <v>7686</v>
+        <v>7712.88</v>
       </c>
       <c r="N42" t="n">
-        <v>7718.25</v>
+        <v>7760.06</v>
       </c>
       <c r="O42" t="n">
-        <v>7794.5</v>
+        <v>7764</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4056,21 +4054,25 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W42" s="11" t="inlineStr">
         <is>
@@ -4079,57 +4081,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7673.5</v>
+        <v>7749.75</v>
       </c>
       <c r="C43" t="n">
-        <v>7766.5</v>
+        <v>7764.5</v>
       </c>
       <c r="D43" t="n">
-        <v>7661.25</v>
+        <v>7711.75</v>
       </c>
       <c r="E43" t="n">
-        <v>7754.75</v>
+        <v>7722</v>
       </c>
       <c r="F43" t="n">
-        <v>78.25</v>
+        <v>-32.75</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0042</v>
       </c>
       <c r="H43" t="n">
-        <v>105.25</v>
+        <v>52.75</v>
       </c>
       <c r="I43" t="n">
-        <v>7545.75</v>
+        <v>7556</v>
       </c>
       <c r="J43" t="n">
-        <v>7614.56</v>
+        <v>7669.94</v>
       </c>
       <c r="K43" t="n">
-        <v>7640.12</v>
+        <v>7702.12</v>
       </c>
       <c r="L43" t="n">
-        <v>7665.69</v>
+        <v>7734.31</v>
       </c>
       <c r="M43" t="n">
-        <v>7712.88</v>
+        <v>7807.38</v>
       </c>
       <c r="N43" t="n">
-        <v>7760.06</v>
+        <v>7880.44</v>
       </c>
       <c r="O43" t="n">
-        <v>7764</v>
+        <v>7871.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4142,23 +4144,17 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="11" t="inlineStr">
         <is>
@@ -4167,57 +4163,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7749.75</v>
+        <v>7715.5</v>
       </c>
       <c r="C44" t="n">
-        <v>7764.5</v>
+        <v>7728.5</v>
       </c>
       <c r="D44" t="n">
-        <v>7711.75</v>
+        <v>7672.25</v>
       </c>
       <c r="E44" t="n">
-        <v>7722</v>
+        <v>7680.5</v>
       </c>
       <c r="F44" t="n">
-        <v>-32.75</v>
+        <v>-41.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0054</v>
       </c>
       <c r="H44" t="n">
-        <v>52.75</v>
+        <v>56.25</v>
       </c>
       <c r="I44" t="n">
-        <v>7556</v>
+        <v>7659</v>
       </c>
       <c r="J44" t="n">
-        <v>7669.94</v>
+        <v>7661.19</v>
       </c>
       <c r="K44" t="n">
-        <v>7702.12</v>
+        <v>7695.62</v>
       </c>
       <c r="L44" t="n">
-        <v>7734.31</v>
+        <v>7730.06</v>
       </c>
       <c r="M44" t="n">
-        <v>7807.38</v>
+        <v>7748.38</v>
       </c>
       <c r="N44" t="n">
-        <v>7880.44</v>
+        <v>7766.69</v>
       </c>
       <c r="O44" t="n">
-        <v>7871.75</v>
+        <v>7817.25</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4225,12 +4221,14 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4247,59 +4245,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7715.5</v>
+        <v>7681</v>
       </c>
       <c r="C45" t="n">
-        <v>7728.5</v>
+        <v>7691.25</v>
       </c>
       <c r="D45" t="n">
-        <v>7672.25</v>
+        <v>7628.75</v>
       </c>
       <c r="E45" t="n">
-        <v>7680.5</v>
+        <v>7643.75</v>
       </c>
       <c r="F45" t="n">
-        <v>-41.5</v>
+        <v>-36.75</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H45" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="I45" t="n">
-        <v>7659</v>
+        <v>7616</v>
       </c>
       <c r="J45" t="n">
-        <v>7661.19</v>
+        <v>7614.31</v>
       </c>
       <c r="K45" t="n">
-        <v>7695.62</v>
+        <v>7652.38</v>
       </c>
       <c r="L45" t="n">
-        <v>7730.06</v>
+        <v>7690.44</v>
       </c>
       <c r="M45" t="n">
-        <v>7748.38</v>
+        <v>7708.62</v>
       </c>
       <c r="N45" t="n">
-        <v>7766.69</v>
+        <v>7726.81</v>
       </c>
       <c r="O45" t="n">
-        <v>7817.25</v>
+        <v>7784.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4312,7 +4306,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4336,50 +4330,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7681</v>
+        <v>7646.5</v>
       </c>
       <c r="C46" t="n">
-        <v>7691.25</v>
+        <v>7666.25</v>
       </c>
       <c r="D46" t="n">
-        <v>7628.75</v>
+        <v>7585.5</v>
       </c>
       <c r="E46" t="n">
-        <v>7643.75</v>
+        <v>7598.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-36.75</v>
+        <v>-45.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0059</v>
       </c>
       <c r="H46" t="n">
-        <v>62.5</v>
+        <v>80.75</v>
       </c>
       <c r="I46" t="n">
-        <v>7616</v>
+        <v>7566.25</v>
       </c>
       <c r="J46" t="n">
-        <v>7614.31</v>
+        <v>7573.12</v>
       </c>
       <c r="K46" t="n">
-        <v>7652.38</v>
+        <v>7612.5</v>
       </c>
       <c r="L46" t="n">
-        <v>7690.44</v>
+        <v>7651.88</v>
       </c>
       <c r="M46" t="n">
-        <v>7708.62</v>
+        <v>7675</v>
       </c>
       <c r="N46" t="n">
-        <v>7726.81</v>
+        <v>7698.12</v>
       </c>
       <c r="O46" t="n">
-        <v>7784.75</v>
+        <v>7753.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4392,7 +4386,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4416,50 +4410,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7646.5</v>
+        <v>7599.5</v>
       </c>
       <c r="C47" t="n">
-        <v>7666.25</v>
+        <v>7683.5</v>
       </c>
       <c r="D47" t="n">
-        <v>7585.5</v>
+        <v>7594.25</v>
       </c>
       <c r="E47" t="n">
-        <v>7598.5</v>
+        <v>7659.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-45.25</v>
+        <v>61</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.008</v>
       </c>
       <c r="H47" t="n">
-        <v>80.75</v>
+        <v>89.25</v>
       </c>
       <c r="I47" t="n">
-        <v>7566.25</v>
+        <v>7504.75</v>
       </c>
       <c r="J47" t="n">
-        <v>7573.12</v>
+        <v>7504.06</v>
       </c>
       <c r="K47" t="n">
-        <v>7612.5</v>
+        <v>7558.12</v>
       </c>
       <c r="L47" t="n">
-        <v>7651.88</v>
+        <v>7612.19</v>
       </c>
       <c r="M47" t="n">
-        <v>7675</v>
+        <v>7638.88</v>
       </c>
       <c r="N47" t="n">
-        <v>7698.12</v>
+        <v>7665.56</v>
       </c>
       <c r="O47" t="n">
-        <v>7753.75</v>
+        <v>7747</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4467,22 +4461,24 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4491,55 +4487,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7599.5</v>
+        <v>7609.25</v>
       </c>
       <c r="C48" t="n">
-        <v>7683.5</v>
+        <v>7652</v>
       </c>
       <c r="D48" t="n">
-        <v>7594.25</v>
+        <v>7593.75</v>
       </c>
       <c r="E48" t="n">
-        <v>7659.5</v>
+        <v>7625</v>
       </c>
       <c r="F48" t="n">
-        <v>61</v>
+        <v>-34.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.008</v>
+        <v>-0.0045</v>
       </c>
       <c r="H48" t="n">
-        <v>89.25</v>
+        <v>58.25</v>
       </c>
       <c r="I48" t="n">
-        <v>7504.75</v>
+        <v>7505</v>
       </c>
       <c r="J48" t="n">
-        <v>7504.06</v>
+        <v>7580.56</v>
       </c>
       <c r="K48" t="n">
-        <v>7558.12</v>
+        <v>7614.88</v>
       </c>
       <c r="L48" t="n">
-        <v>7612.19</v>
+        <v>7649.19</v>
       </c>
       <c r="M48" t="n">
-        <v>7638.88</v>
+        <v>7704.12</v>
       </c>
       <c r="N48" t="n">
-        <v>7665.56</v>
+        <v>7759.06</v>
       </c>
       <c r="O48" t="n">
-        <v>7747</v>
+        <v>7772.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4547,23 +4547,21 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4573,59 +4571,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7609.25</v>
+        <v>7631</v>
       </c>
       <c r="C49" t="n">
-        <v>7652</v>
+        <v>7633.25</v>
       </c>
       <c r="D49" t="n">
-        <v>7593.75</v>
+        <v>7576.75</v>
       </c>
       <c r="E49" t="n">
-        <v>7625</v>
+        <v>7589.25</v>
       </c>
       <c r="F49" t="n">
-        <v>-34.5</v>
+        <v>-35.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0047</v>
       </c>
       <c r="H49" t="n">
-        <v>58.25</v>
+        <v>56.5</v>
       </c>
       <c r="I49" t="n">
-        <v>7505</v>
+        <v>7535.5</v>
       </c>
       <c r="J49" t="n">
-        <v>7580.56</v>
+        <v>7567.81</v>
       </c>
       <c r="K49" t="n">
-        <v>7614.88</v>
+        <v>7595.88</v>
       </c>
       <c r="L49" t="n">
-        <v>7649.19</v>
+        <v>7623.94</v>
       </c>
       <c r="M49" t="n">
-        <v>7704.12</v>
+        <v>7654.12</v>
       </c>
       <c r="N49" t="n">
-        <v>7759.06</v>
+        <v>7684.31</v>
       </c>
       <c r="O49" t="n">
-        <v>7772.75</v>
+        <v>7710.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4638,7 +4632,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4662,69 +4656,75 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>7631</v>
+        <v>7596.5</v>
       </c>
       <c r="C50" t="n">
-        <v>7633.25</v>
+        <v>7632</v>
       </c>
       <c r="D50" t="n">
-        <v>7576.75</v>
+        <v>7509.25</v>
       </c>
       <c r="E50" t="n">
-        <v>7589.25</v>
+        <v>7556.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-35.75</v>
+        <v>-32.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0043</v>
       </c>
       <c r="H50" t="n">
-        <v>56.5</v>
+        <v>122.75</v>
       </c>
       <c r="I50" t="n">
-        <v>7535.5</v>
+        <v>7520.25</v>
       </c>
       <c r="J50" t="n">
-        <v>7567.81</v>
+        <v>7524.88</v>
       </c>
       <c r="K50" t="n">
-        <v>7595.88</v>
+        <v>7561</v>
       </c>
       <c r="L50" t="n">
-        <v>7623.94</v>
+        <v>7597.12</v>
       </c>
       <c r="M50" t="n">
-        <v>7654.12</v>
+        <v>7617.5</v>
       </c>
       <c r="N50" t="n">
-        <v>7684.31</v>
+        <v>7637.88</v>
       </c>
       <c r="O50" t="n">
-        <v>7710.25</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+        <v>7689.75</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4742,76 +4742,70 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7596.5</v>
+        <v>7557.5</v>
       </c>
       <c r="C51" t="n">
-        <v>7632</v>
+        <v>7654.5</v>
       </c>
       <c r="D51" t="n">
-        <v>7509.25</v>
+        <v>7551.5</v>
       </c>
       <c r="E51" t="n">
-        <v>7556.5</v>
+        <v>7640</v>
       </c>
       <c r="F51" t="n">
-        <v>-32.75</v>
+        <v>83.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="H51" t="n">
-        <v>122.75</v>
+        <v>103</v>
       </c>
       <c r="I51" t="n">
-        <v>7520.25</v>
+        <v>7386.5</v>
       </c>
       <c r="J51" t="n">
-        <v>7524.88</v>
+        <v>7426.69</v>
       </c>
       <c r="K51" t="n">
-        <v>7561</v>
+        <v>7495.12</v>
       </c>
       <c r="L51" t="n">
-        <v>7597.12</v>
+        <v>7563.56</v>
       </c>
       <c r="M51" t="n">
-        <v>7617.5</v>
+        <v>7617.88</v>
       </c>
       <c r="N51" t="n">
-        <v>7637.88</v>
+        <v>7672.19</v>
       </c>
       <c r="O51" t="n">
-        <v>7689.75</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
+        <v>7754.75</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4823,55 +4817,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7557.5</v>
+        <v>7637</v>
       </c>
       <c r="C52" t="n">
-        <v>7654.5</v>
+        <v>7670.25</v>
       </c>
       <c r="D52" t="n">
-        <v>7551.5</v>
+        <v>7625.25</v>
       </c>
       <c r="E52" t="n">
-        <v>7640</v>
+        <v>7657.35</v>
       </c>
       <c r="F52" t="n">
-        <v>83.5</v>
+        <v>17.35</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0023</v>
       </c>
       <c r="H52" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="I52" t="n">
-        <v>7386.5</v>
+        <v>7448.5</v>
       </c>
       <c r="J52" t="n">
-        <v>7426.69</v>
+        <v>7555.5</v>
       </c>
       <c r="K52" t="n">
-        <v>7495.12</v>
+        <v>7588.5</v>
       </c>
       <c r="L52" t="n">
-        <v>7563.56</v>
+        <v>7621.5</v>
       </c>
       <c r="M52" t="n">
-        <v>7617.88</v>
+        <v>7691.5</v>
       </c>
       <c r="N52" t="n">
-        <v>7672.19</v>
+        <v>7761.5</v>
       </c>
       <c r="O52" t="n">
-        <v>7754.75</v>
+        <v>7757.5</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4882,7 +4880,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4912,50 +4910,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7637</v>
+        <v>7722</v>
       </c>
       <c r="C53" t="n">
-        <v>7670.25</v>
+        <v>7847.25</v>
       </c>
       <c r="D53" t="n">
-        <v>7625.25</v>
+        <v>7713.75</v>
       </c>
       <c r="E53" t="n">
-        <v>7657.35</v>
+        <v>7833.5</v>
       </c>
       <c r="F53" t="n">
-        <v>17.35</v>
+        <v>176.15</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0023</v>
+        <v>0.023</v>
       </c>
       <c r="H53" t="n">
-        <v>45</v>
+        <v>133.5</v>
       </c>
       <c r="I53" t="n">
-        <v>7448.5</v>
+        <v>7580.25</v>
       </c>
       <c r="J53" t="n">
-        <v>7555.5</v>
+        <v>7617.15</v>
       </c>
       <c r="K53" t="n">
-        <v>7588.5</v>
+        <v>7634.85</v>
       </c>
       <c r="L53" t="n">
-        <v>7621.5</v>
+        <v>7652.55</v>
       </c>
       <c r="M53" t="n">
-        <v>7691.5</v>
+        <v>7679.85</v>
       </c>
       <c r="N53" t="n">
-        <v>7761.5</v>
+        <v>7707.15</v>
       </c>
       <c r="O53" t="n">
-        <v>7757.5</v>
+        <v>7715.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4966,80 +4964,80 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7722</v>
+        <v>7830</v>
       </c>
       <c r="C54" t="n">
-        <v>7847.25</v>
+        <v>7848.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7713.75</v>
+        <v>7810.5</v>
       </c>
       <c r="E54" t="n">
-        <v>7833.5</v>
+        <v>7831.75</v>
       </c>
       <c r="F54" t="n">
-        <v>176.15</v>
+        <v>-1.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.023</v>
+        <v>-0.0002</v>
       </c>
       <c r="H54" t="n">
-        <v>133.5</v>
+        <v>38</v>
       </c>
       <c r="I54" t="n">
         <v>7580.25</v>
       </c>
       <c r="J54" t="n">
-        <v>7617.15</v>
+        <v>7726.5</v>
       </c>
       <c r="K54" t="n">
-        <v>7634.85</v>
+        <v>7766.75</v>
       </c>
       <c r="L54" t="n">
-        <v>7652.55</v>
+        <v>7807</v>
       </c>
       <c r="M54" t="n">
-        <v>7679.85</v>
+        <v>7900.25</v>
       </c>
       <c r="N54" t="n">
-        <v>7707.15</v>
+        <v>7993.5</v>
       </c>
       <c r="O54" t="n">
-        <v>7715.25</v>
+        <v>7980.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5050,93 +5048,97 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>7830</v>
       </c>
       <c r="C55" t="n">
-        <v>7848.5</v>
+        <v>7843.25</v>
       </c>
       <c r="D55" t="n">
-        <v>7810.5</v>
+        <v>7758.75</v>
       </c>
       <c r="E55" t="n">
-        <v>7831.75</v>
+        <v>7772.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.75</v>
+        <v>-59.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0076</v>
       </c>
       <c r="H55" t="n">
-        <v>38</v>
+        <v>84.5</v>
       </c>
       <c r="I55" t="n">
-        <v>7580.25</v>
+        <v>7772.5</v>
       </c>
       <c r="J55" t="n">
-        <v>7726.5</v>
+        <v>7794.88</v>
       </c>
       <c r="K55" t="n">
-        <v>7766.75</v>
+        <v>7812.75</v>
       </c>
       <c r="L55" t="n">
-        <v>7807</v>
+        <v>7830.62</v>
       </c>
       <c r="M55" t="n">
-        <v>7900.25</v>
+        <v>7850.75</v>
       </c>
       <c r="N55" t="n">
-        <v>7993.5</v>
+        <v>7870.88</v>
       </c>
       <c r="O55" t="n">
-        <v>7980.75</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+        <v>7886.5</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5148,83 +5150,75 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7830</v>
+        <v>7774.75</v>
       </c>
       <c r="C56" t="n">
-        <v>7843.25</v>
+        <v>7783.5</v>
       </c>
       <c r="D56" t="n">
-        <v>7758.75</v>
+        <v>7707.25</v>
       </c>
       <c r="E56" t="n">
-        <v>7772.5</v>
+        <v>7767</v>
       </c>
       <c r="F56" t="n">
-        <v>-59.25</v>
+        <v>-5.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0076</v>
+        <v>-0.0007</v>
       </c>
       <c r="H56" t="n">
-        <v>84.5</v>
+        <v>76.25</v>
       </c>
       <c r="I56" t="n">
-        <v>7772.5</v>
+        <v>7674.25</v>
       </c>
       <c r="J56" t="n">
-        <v>7794.88</v>
+        <v>7673.75</v>
       </c>
       <c r="K56" t="n">
-        <v>7812.75</v>
+        <v>7730.25</v>
       </c>
       <c r="L56" t="n">
-        <v>7830.62</v>
+        <v>7786.75</v>
       </c>
       <c r="M56" t="n">
-        <v>7850.75</v>
+        <v>7814.75</v>
       </c>
       <c r="N56" t="n">
-        <v>7870.88</v>
+        <v>7842.75</v>
       </c>
       <c r="O56" t="n">
-        <v>7886.5</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
+        <v>7927.75</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="